--- a/research/traditional_assets/database/data/united_states/united_states_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ30"/>
+  <dimension ref="A1:AQ28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.16</v>
+        <v>0.1455</v>
       </c>
       <c r="E2">
-        <v>0.307</v>
+        <v>0.244</v>
       </c>
       <c r="F2">
-        <v>0.2215</v>
+        <v>0.225</v>
       </c>
       <c r="G2">
-        <v>0.01419102024739344</v>
+        <v>0.008677203682533429</v>
       </c>
       <c r="H2">
-        <v>0.009423864664387206</v>
+        <v>0.004291323140389774</v>
       </c>
       <c r="I2">
-        <v>0.01006720935250984</v>
+        <v>0.003138139706038804</v>
       </c>
       <c r="J2">
-        <v>0.00842205050886651</v>
+        <v>0.002583538736016828</v>
       </c>
       <c r="K2">
-        <v>47207.93</v>
+        <v>38423.549</v>
       </c>
       <c r="L2">
-        <v>0.2034236166154457</v>
+        <v>0.1600542272952828</v>
       </c>
       <c r="M2">
-        <v>26005.78</v>
+        <v>32541.531</v>
       </c>
       <c r="N2">
-        <v>0.04574268059997526</v>
+        <v>0.06338447532263279</v>
       </c>
       <c r="O2">
-        <v>0.5508773631887693</v>
+        <v>0.8469163272762753</v>
       </c>
       <c r="P2">
-        <v>8290.280000000001</v>
+        <v>11022.991</v>
       </c>
       <c r="Q2">
-        <v>0.01458212867002501</v>
+        <v>0.02147060938900211</v>
       </c>
       <c r="R2">
-        <v>0.1756120211159439</v>
+        <v>0.2868811259470072</v>
       </c>
       <c r="S2">
-        <v>17715.5</v>
+        <v>21518.54</v>
       </c>
       <c r="T2">
-        <v>0.6812139455151893</v>
+        <v>0.6612639091873089</v>
       </c>
       <c r="U2">
-        <v>398458.468</v>
+        <v>475486.795</v>
       </c>
       <c r="V2">
-        <v>0.7008656704040204</v>
+        <v>0.9261543663669436</v>
       </c>
       <c r="W2">
-        <v>0.258018330565947</v>
+        <v>0.1474608823175952</v>
       </c>
       <c r="X2">
-        <v>0.03692184336247488</v>
+        <v>0.07848212275421709</v>
       </c>
       <c r="Y2">
-        <v>0.2210964872034721</v>
+        <v>0.06897875956337809</v>
       </c>
       <c r="Z2">
-        <v>0.3009892285518124</v>
+        <v>0.2650458496014069</v>
       </c>
       <c r="AA2">
-        <v>-0.0006299106526914857</v>
+        <v>-5.921668609696061e-05</v>
       </c>
       <c r="AB2">
-        <v>0.03347596398385473</v>
+        <v>0.06522890974559541</v>
       </c>
       <c r="AC2">
-        <v>-0.03458209144159852</v>
+        <v>-0.06579062347050191</v>
       </c>
       <c r="AD2">
-        <v>1023540.316</v>
+        <v>1020465.273</v>
       </c>
       <c r="AE2">
-        <v>13942.01430033454</v>
+        <v>11937.82462235758</v>
       </c>
       <c r="AF2">
-        <v>1037482.330300334</v>
+        <v>1032403.097622358</v>
       </c>
       <c r="AG2">
-        <v>639023.8623003345</v>
+        <v>556916.3026223576</v>
       </c>
       <c r="AH2">
-        <v>0.6460016744961896</v>
+        <v>0.6678753050728022</v>
       </c>
       <c r="AI2">
-        <v>0.7603363611749686</v>
+        <v>0.7653757897975896</v>
       </c>
       <c r="AJ2">
-        <v>0.5291916366296344</v>
+        <v>0.520329161166977</v>
       </c>
       <c r="AK2">
-        <v>0.6614839147245498</v>
+        <v>0.6376438449465098</v>
       </c>
       <c r="AL2">
-        <v>195.195</v>
+        <v>117.37</v>
       </c>
       <c r="AM2">
-        <v>194.993</v>
+        <v>116.06</v>
       </c>
       <c r="AN2">
-        <v>186.297408138155</v>
+        <v>298.9813699408756</v>
       </c>
       <c r="AO2">
-        <v>15.55906145136914</v>
+        <v>8.364871773025476</v>
       </c>
       <c r="AP2">
-        <v>116.3105032835713</v>
+        <v>163.168314989235</v>
       </c>
       <c r="AQ2">
-        <v>15.57517962183258</v>
+        <v>8.45928829915561</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BlackStar Enterprise Group, Inc. (OTCPK:BEGI)</t>
+          <t>Perella Weinberg Partners (NasdaqGS:PWP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,92 +724,101 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="G3">
+        <v>0.00170015455950541</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0.01712848757673131</v>
+      </c>
+      <c r="J3">
+        <v>0.01712848757673131</v>
+      </c>
       <c r="K3">
-        <v>-2.44</v>
+        <v>18.9</v>
+      </c>
+      <c r="L3">
+        <v>0.02921174652241113</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>144</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.3434295253994753</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>7.61904761904762</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>78.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.187932268065824</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>4.169312169312169</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>65.2</v>
+      </c>
+      <c r="T3">
+        <v>0.4527777777777778</v>
       </c>
       <c r="U3">
-        <v>0.5590000000000001</v>
+        <v>142.9</v>
       </c>
       <c r="V3">
-        <v>0.2852040816326531</v>
+        <v>0.3408061054137849</v>
       </c>
       <c r="W3">
-        <v>8</v>
+        <v>0.1509584664536741</v>
       </c>
       <c r="X3">
-        <v>0.03635599494809021</v>
+        <v>0.06772690118667012</v>
       </c>
       <c r="Y3">
-        <v>7.96364400505191</v>
-      </c>
-      <c r="Z3">
-        <v>-0</v>
-      </c>
-      <c r="AA3">
-        <v>12.30434782608696</v>
+        <v>0.083231565267004</v>
       </c>
       <c r="AB3">
-        <v>0.04229966352294618</v>
-      </c>
-      <c r="AC3">
-        <v>12.26204816256401</v>
+        <v>0.06541635223312067</v>
       </c>
       <c r="AD3">
-        <v>0.457</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>40.08934268927422</v>
       </c>
       <c r="AF3">
-        <v>0.457</v>
+        <v>40.08934268927422</v>
       </c>
       <c r="AG3">
-        <v>-0.102</v>
+        <v>-102.8106573107258</v>
       </c>
       <c r="AH3">
-        <v>0.1890773686388085</v>
+        <v>0.08726659276549695</v>
       </c>
       <c r="AI3">
-        <v>0.7838765008576331</v>
+        <v>0.1275555268474662</v>
       </c>
       <c r="AJ3">
-        <v>-0.05489773950484394</v>
+        <v>-0.3248471384126959</v>
       </c>
       <c r="AK3">
-        <v>-4.250000000000007</v>
+        <v>-0.5998661042601678</v>
       </c>
       <c r="AL3">
-        <v>0.995</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.995</v>
-      </c>
-      <c r="AO3">
-        <v>-0.8532663316582915</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.8532663316582915</v>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-5.38275692726313</v>
       </c>
     </row>
     <row r="4">
@@ -829,124 +838,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.122</v>
+        <v>0.149</v>
       </c>
       <c r="E4">
-        <v>0.212</v>
+        <v>0.24</v>
       </c>
       <c r="F4">
-        <v>0.209</v>
+        <v>0.526</v>
       </c>
       <c r="G4">
-        <v>0.1260977538534108</v>
+        <v>0.1232031380803176</v>
       </c>
       <c r="H4">
-        <v>0.1260977538534108</v>
+        <v>0.1232031380803176</v>
       </c>
       <c r="I4">
-        <v>0.1039131701170423</v>
+        <v>0.1171648206785676</v>
       </c>
       <c r="J4">
-        <v>0.07884535164629171</v>
+        <v>0.08970387416729413</v>
       </c>
       <c r="K4">
-        <v>463.3</v>
+        <v>634.7</v>
       </c>
       <c r="L4">
-        <v>0.06427669640255831</v>
+        <v>0.07590470951230598</v>
       </c>
       <c r="M4">
-        <v>139.3</v>
+        <v>331</v>
       </c>
       <c r="N4">
-        <v>0.01085685782426387</v>
+        <v>0.01923635729644912</v>
       </c>
       <c r="O4">
-        <v>0.3006691128858192</v>
+        <v>0.5215062234126359</v>
       </c>
       <c r="P4">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="Q4">
-        <v>0.006227300360076692</v>
+        <v>0.004649270645667461</v>
       </c>
       <c r="R4">
-        <v>0.1724584502482193</v>
+        <v>0.1260438002205767</v>
       </c>
       <c r="S4">
-        <v>59.40000000000001</v>
+        <v>251</v>
       </c>
       <c r="T4">
-        <v>0.4264178033022254</v>
+        <v>0.7583081570996979</v>
       </c>
       <c r="U4">
-        <v>977.8</v>
+        <v>1219.4</v>
       </c>
       <c r="V4">
-        <v>0.07620843920003741</v>
+        <v>0.07086650781658628</v>
       </c>
       <c r="W4">
-        <v>0.3837170780188836</v>
+        <v>0.3926627072506805</v>
       </c>
       <c r="X4">
-        <v>0.03636291573638623</v>
+        <v>0.06927171737826272</v>
       </c>
       <c r="Y4">
-        <v>0.3473541622824973</v>
+        <v>0.3233909898724178</v>
       </c>
       <c r="Z4">
-        <v>4.727975905407193</v>
+        <v>4.260451117164931</v>
       </c>
       <c r="AA4">
-        <v>0.3727789228370246</v>
+        <v>0.3821789709100706</v>
       </c>
       <c r="AB4">
-        <v>0.03270326474154295</v>
+        <v>0.06516091343620253</v>
       </c>
       <c r="AC4">
-        <v>0.3400756580954816</v>
+        <v>0.3170180574738681</v>
       </c>
       <c r="AD4">
-        <v>2831.8</v>
+        <v>2824.8</v>
       </c>
       <c r="AE4">
-        <v>166.5213055668529</v>
+        <v>133.4560122497693</v>
       </c>
       <c r="AF4">
-        <v>2998.321305566853</v>
+        <v>2958.256012249769</v>
       </c>
       <c r="AG4">
-        <v>2020.521305566853</v>
+        <v>1738.856012249769</v>
       </c>
       <c r="AH4">
-        <v>0.1894204442416665</v>
+        <v>0.1467006424541657</v>
       </c>
       <c r="AI4">
-        <v>0.6497296601530202</v>
+        <v>0.596692536893793</v>
       </c>
       <c r="AJ4">
-        <v>0.1360517676742343</v>
+        <v>0.09178028224881905</v>
       </c>
       <c r="AK4">
-        <v>0.5555581591699942</v>
+        <v>0.4651392233783838</v>
       </c>
       <c r="AL4">
-        <v>102.3</v>
+        <v>116.3</v>
       </c>
       <c r="AM4">
-        <v>102.3</v>
+        <v>116.3</v>
       </c>
       <c r="AN4">
-        <v>2.838328154755939</v>
+        <v>2.21015569986699</v>
       </c>
       <c r="AO4">
-        <v>7.432062561094819</v>
+        <v>8.446259673258814</v>
       </c>
       <c r="AP4">
-        <v>2.025179217767719</v>
+        <v>1.360500752875181</v>
       </c>
       <c r="AQ4">
-        <v>7.432062561094819</v>
+        <v>8.446259673258814</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Perella Weinberg Partners (NasdaqGS:PWP)</t>
+          <t>Piper Sandler Companies (NYSE:PIPR)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,92 +974,101 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.143</v>
+      </c>
       <c r="G5">
-        <v>0.001808785529715762</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.01065960000291676</v>
+        <v>0.003329028548106124</v>
       </c>
       <c r="J5">
-        <v>0.009306650771777326</v>
+        <v>0.002411821143063838</v>
       </c>
       <c r="K5">
-        <v>-6.11</v>
+        <v>186.1</v>
       </c>
       <c r="L5">
-        <v>-0.00789405684754522</v>
+        <v>0.1105894937009746</v>
       </c>
       <c r="M5">
-        <v>182.1</v>
+        <v>188.74</v>
       </c>
       <c r="N5">
-        <v>0.3332113449222324</v>
+        <v>0.1061350728223584</v>
       </c>
       <c r="O5">
-        <v>-29.80360065466448</v>
+        <v>1.014185921547555</v>
       </c>
       <c r="P5">
-        <v>57.6</v>
+        <v>1.44</v>
       </c>
       <c r="Q5">
-        <v>0.1053979871912168</v>
+        <v>0.0008097621323736152</v>
       </c>
       <c r="R5">
-        <v>-9.427168576104746</v>
+        <v>0.007737775389575497</v>
       </c>
       <c r="S5">
-        <v>124.5</v>
+        <v>187.3</v>
       </c>
       <c r="T5">
-        <v>0.6836902800658978</v>
+        <v>0.9923704567129384</v>
       </c>
       <c r="U5">
-        <v>415.8</v>
+        <v>274.5</v>
       </c>
       <c r="V5">
-        <v>0.7608417200365966</v>
+        <v>0.1543609064837204</v>
+      </c>
+      <c r="W5">
+        <v>0.1898592124056315</v>
       </c>
       <c r="X5">
-        <v>0.03468967649878787</v>
+        <v>0.06826951455807484</v>
+      </c>
+      <c r="Y5">
+        <v>0.1215896978475567</v>
       </c>
       <c r="Z5">
-        <v>13.17506281557966</v>
+        <v>3.714875952210061</v>
       </c>
       <c r="AA5">
-        <v>0.1226157085208292</v>
+        <v>0.008959616365399633</v>
       </c>
       <c r="AB5">
-        <v>0.03330399948573444</v>
+        <v>0.06532267244822948</v>
       </c>
       <c r="AC5">
-        <v>0.08931170903509478</v>
+        <v>-0.05636305608282985</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>126.7</v>
       </c>
       <c r="AE5">
-        <v>58.74734798871214</v>
+        <v>90.98955379623507</v>
       </c>
       <c r="AF5">
-        <v>58.74734798871214</v>
+        <v>217.6895537962351</v>
       </c>
       <c r="AG5">
-        <v>-357.0526520112879</v>
+        <v>-56.81044620376491</v>
       </c>
       <c r="AH5">
-        <v>0.09706337117202499</v>
+        <v>0.1090634734947407</v>
       </c>
       <c r="AI5">
-        <v>0.1831577045206921</v>
+        <v>0.1543361687510118</v>
       </c>
       <c r="AJ5">
-        <v>-1.884706520318048</v>
+        <v>-0.03300074989039946</v>
       </c>
       <c r="AK5">
-        <v>3.756367070840764</v>
+        <v>-0.05000965547078889</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1059,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>5.323529411764706</v>
       </c>
       <c r="AP5">
-        <v>-17.85263260056439</v>
+        <v>-2.386993537973316</v>
       </c>
     </row>
     <row r="6">
@@ -1073,7 +1091,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc. (NYSE:JEF)</t>
+          <t>Virtu Financial, Inc. (NasdaqGS:VIRT)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,116 +1099,113 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.302</v>
+      </c>
       <c r="G6">
-        <v>0.1392223655344997</v>
+        <v>0.01766182535413304</v>
       </c>
       <c r="H6">
-        <v>0.1392223655344997</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.2491677397632651</v>
+        <v>0.004756425931517675</v>
       </c>
       <c r="J6">
-        <v>0.1829142138309237</v>
+        <v>0.003928637787274241</v>
       </c>
       <c r="K6">
-        <v>1656.3</v>
+        <v>341.5</v>
       </c>
       <c r="L6">
-        <v>0.1825908654959156</v>
+        <v>0.1530840953917877</v>
       </c>
       <c r="M6">
-        <v>571.78</v>
+        <v>657.6</v>
       </c>
       <c r="N6">
-        <v>0.06001175507462374</v>
+        <v>0.3228435367470175</v>
       </c>
       <c r="O6">
-        <v>0.3452152387852442</v>
+        <v>1.925622254758419</v>
       </c>
       <c r="P6">
-        <v>196.48</v>
+        <v>105.9</v>
       </c>
       <c r="Q6">
-        <v>0.02062175948277672</v>
+        <v>0.05199077028818302</v>
       </c>
       <c r="R6">
-        <v>0.1186258528044437</v>
+        <v>0.3101024890190337</v>
       </c>
       <c r="S6">
-        <v>375.3</v>
+        <v>551.7</v>
       </c>
       <c r="T6">
-        <v>0.6563713316310469</v>
+        <v>0.8389598540145986</v>
       </c>
       <c r="U6">
-        <v>2294.3</v>
+        <v>836.3</v>
       </c>
       <c r="V6">
-        <v>0.240800604546695</v>
+        <v>0.4105748932200893</v>
       </c>
       <c r="W6">
-        <v>0.1760017852019509</v>
+        <v>0.2299198815054198</v>
       </c>
       <c r="X6">
-        <v>0.06561253837835927</v>
+        <v>0.1025838905167693</v>
       </c>
       <c r="Y6">
-        <v>0.1103892468235917</v>
+        <v>0.1273359909886504</v>
       </c>
       <c r="Z6">
-        <v>0.2998901823003276</v>
+        <v>0.6346972089230191</v>
       </c>
       <c r="AA6">
-        <v>0.05485417693107681</v>
+        <v>0.002493495438452467</v>
       </c>
       <c r="AB6">
-        <v>0.03513206630185565</v>
+        <v>0.05929367322665077</v>
       </c>
       <c r="AC6">
-        <v>0.01972211062922116</v>
+        <v>-0.05680017778819831</v>
       </c>
       <c r="AD6">
-        <v>22655.7</v>
+        <v>3422.1</v>
       </c>
       <c r="AE6">
-        <v>587.8725791672275</v>
+        <v>279.9468251598518</v>
       </c>
       <c r="AF6">
-        <v>23243.57257916723</v>
+        <v>3702.046825159852</v>
       </c>
       <c r="AG6">
-        <v>20949.27257916723</v>
+        <v>2865.746825159852</v>
       </c>
       <c r="AH6">
-        <v>0.7092645424910635</v>
+        <v>0.6450742510681367</v>
       </c>
       <c r="AI6">
-        <v>0.6875256283111639</v>
+        <v>0.6887597115995193</v>
       </c>
       <c r="AJ6">
-        <v>0.6873781110291813</v>
+        <v>0.5845305459192267</v>
       </c>
       <c r="AK6">
-        <v>0.6647761677730785</v>
+        <v>0.6314099632678336</v>
       </c>
       <c r="AL6">
-        <v>55.2</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>55.2</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>8.960843254360638</v>
-      </c>
-      <c r="AO6">
-        <v>41.76268115942029</v>
+        <v>51.38288288288289</v>
       </c>
       <c r="AP6">
-        <v>8.285912502142637</v>
-      </c>
-      <c r="AQ6">
-        <v>41.76268115942029</v>
+        <v>43.02923160900679</v>
       </c>
     </row>
     <row r="7">
@@ -1201,7 +1216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Piper Sandler Companies (NYSE:PIPR)</t>
+          <t>Interactive Brokers Group, Inc. (NasdaqGS:IBKR)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,10 +1225,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.199</v>
+        <v>0.148</v>
       </c>
       <c r="E7">
-        <v>0.489</v>
+        <v>0.306</v>
+      </c>
+      <c r="F7">
+        <v>0.225</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1222,91 +1240,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.00161545092772512</v>
+        <v>0.0005020384678623753</v>
       </c>
       <c r="J7">
-        <v>0.001199349931189862</v>
+        <v>0.0004617440605131359</v>
       </c>
       <c r="K7">
-        <v>207.2</v>
+        <v>311</v>
       </c>
       <c r="L7">
-        <v>0.1158383183317493</v>
+        <v>0.10997171145686</v>
       </c>
       <c r="M7">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="N7">
-        <v>0.02976750015667105</v>
+        <v>0.008061482237867469</v>
       </c>
       <c r="O7">
-        <v>0.4584942084942085</v>
+        <v>0.1929260450160772</v>
       </c>
       <c r="P7">
-        <v>26.4</v>
+        <v>40</v>
       </c>
       <c r="Q7">
-        <v>0.008272231622485429</v>
+        <v>0.005374321491911646</v>
       </c>
       <c r="R7">
-        <v>0.1274131274131274</v>
+        <v>0.1286173633440514</v>
       </c>
       <c r="S7">
-        <v>68.59999999999999</v>
+        <v>20</v>
       </c>
       <c r="T7">
-        <v>0.7221052631578947</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="U7">
-        <v>571.1</v>
+        <v>3184</v>
       </c>
       <c r="V7">
-        <v>0.1789496772576299</v>
+        <v>0.427795990756167</v>
       </c>
       <c r="W7">
-        <v>0.2692657569850552</v>
+        <v>0.1334191334191334</v>
       </c>
       <c r="X7">
-        <v>0.03445860187074302</v>
+        <v>0.09267176364362968</v>
       </c>
       <c r="Y7">
-        <v>0.2348071551143122</v>
+        <v>0.04074736977550374</v>
       </c>
       <c r="Z7">
-        <v>3.162749528223296</v>
+        <v>0.2758243692626253</v>
       </c>
       <c r="AA7">
-        <v>0.003793243429045378</v>
+        <v>0.0001273602642517992</v>
       </c>
       <c r="AB7">
-        <v>0.03329809098398591</v>
+        <v>0.06004566921106316</v>
       </c>
       <c r="AC7">
-        <v>-0.02950484755494053</v>
+        <v>-0.05991830894681136</v>
       </c>
       <c r="AD7">
-        <v>180.4</v>
+        <v>9765</v>
       </c>
       <c r="AE7">
-        <v>107.0522146278904</v>
+        <v>117.901176064426</v>
       </c>
       <c r="AF7">
-        <v>287.4522146278904</v>
+        <v>9882.901176064426</v>
       </c>
       <c r="AG7">
-        <v>-283.6477853721096</v>
+        <v>6698.901176064426</v>
       </c>
       <c r="AH7">
-        <v>0.08262846389944656</v>
+        <v>0.5704185403888715</v>
       </c>
       <c r="AI7">
-        <v>0.2050956158663046</v>
+        <v>0.4755303935836696</v>
       </c>
       <c r="AJ7">
-        <v>-0.09754881586717611</v>
+        <v>0.473698396866331</v>
       </c>
       <c r="AK7">
-        <v>-0.3415582261999346</v>
+        <v>0.3806431497652443</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1315,10 +1333,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>7.423868312757202</v>
+        <v>390.6</v>
       </c>
       <c r="AP7">
-        <v>-11.67274836922262</v>
+        <v>267.956047042577</v>
       </c>
     </row>
     <row r="8">
@@ -1329,7 +1347,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Virtu Financial, Inc. (NasdaqGS:VIRT)</t>
+          <t>Raymond James Financial, Inc. (NYSE:RJF)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,103 +1356,103 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.329</v>
+        <v>0.111</v>
       </c>
       <c r="E8">
-        <v>0.703</v>
+        <v>0.189</v>
       </c>
       <c r="G8">
-        <v>0.01134164279631493</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.001662158538288731</v>
+        <v>0.002446273747595416</v>
       </c>
       <c r="J8">
-        <v>0.001354590591184308</v>
+        <v>0.00182563159501557</v>
       </c>
       <c r="K8">
-        <v>485.1</v>
+        <v>1509</v>
       </c>
       <c r="L8">
-        <v>0.1877757993342107</v>
+        <v>0.1397092861772058</v>
       </c>
       <c r="M8">
-        <v>479.7</v>
+        <v>508.536</v>
       </c>
       <c r="N8">
-        <v>0.1481149844073239</v>
+        <v>0.02212998542178899</v>
       </c>
       <c r="O8">
-        <v>0.9888682745825602</v>
+        <v>0.3370019880715706</v>
       </c>
       <c r="P8">
-        <v>120.5</v>
+        <v>292.536</v>
       </c>
       <c r="Q8">
-        <v>0.03720628647296755</v>
+        <v>0.01273030309623795</v>
       </c>
       <c r="R8">
-        <v>0.2484023912595341</v>
+        <v>0.1938608349900597</v>
       </c>
       <c r="S8">
-        <v>359.2</v>
+        <v>216</v>
       </c>
       <c r="T8">
-        <v>0.7488013341671879</v>
+        <v>0.4247486903582047</v>
       </c>
       <c r="U8">
-        <v>683.8</v>
+        <v>6178</v>
       </c>
       <c r="V8">
-        <v>0.2111340970142341</v>
+        <v>0.268848321329881</v>
       </c>
       <c r="W8">
-        <v>0.3472938144329897</v>
+        <v>0.1830200121285628</v>
       </c>
       <c r="X8">
-        <v>0.04936978428126203</v>
+        <v>0.07000044424286712</v>
       </c>
       <c r="Y8">
-        <v>0.2979240301517277</v>
+        <v>0.1130195678856956</v>
       </c>
       <c r="Z8">
-        <v>0.8628792549841933</v>
+        <v>2.549276139880989</v>
       </c>
       <c r="AA8">
-        <v>0.001168848120129714</v>
+        <v>0.004654039065386066</v>
       </c>
       <c r="AB8">
-        <v>0.03163992589426395</v>
+        <v>0.06529690605498828</v>
       </c>
       <c r="AC8">
-        <v>-0.03047107777413424</v>
+        <v>-0.06064286698960222</v>
       </c>
       <c r="AD8">
-        <v>3582.2</v>
+        <v>4325</v>
       </c>
       <c r="AE8">
-        <v>351.5298981609244</v>
+        <v>452.8889862611096</v>
       </c>
       <c r="AF8">
-        <v>3933.729898160924</v>
+        <v>4777.888986261109</v>
       </c>
       <c r="AG8">
-        <v>3249.929898160924</v>
+        <v>-1400.111013738891</v>
       </c>
       <c r="AH8">
-        <v>0.5484514946837706</v>
+        <v>0.1721303465764013</v>
       </c>
       <c r="AI8">
-        <v>0.6859844776239223</v>
+        <v>0.3362368974789762</v>
       </c>
       <c r="AJ8">
-        <v>0.5008653520340333</v>
+        <v>-0.06488186549815174</v>
       </c>
       <c r="AK8">
-        <v>0.6434702133578061</v>
+        <v>-0.1743190196146685</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1443,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>48.01876675603217</v>
+        <v>36.96581196581197</v>
       </c>
       <c r="AP8">
-        <v>43.56474394317593</v>
+        <v>-11.9667608011871</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1475,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Raymond James Financial, Inc. (NYSE:RJF)</t>
+          <t>B. Riley Financial, Inc. (NasdaqGM:RILY)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1466,10 +1484,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.128</v>
-      </c>
-      <c r="E9">
-        <v>0.215</v>
+        <v>0.232</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1478,103 +1493,106 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.001153648261626582</v>
+        <v>0.003327310374051481</v>
       </c>
       <c r="J9">
-        <v>0.0009037233450932968</v>
+        <v>0.003327310374051481</v>
       </c>
       <c r="K9">
-        <v>1403</v>
+        <v>-38.2</v>
       </c>
       <c r="L9">
-        <v>0.1429736064404362</v>
+        <v>-0.04594659610295887</v>
       </c>
       <c r="M9">
-        <v>346</v>
+        <v>123.84</v>
       </c>
       <c r="N9">
-        <v>0.01672556062048929</v>
+        <v>0.126690537084399</v>
       </c>
       <c r="O9">
-        <v>0.2466143977191732</v>
+        <v>-3.241884816753926</v>
       </c>
       <c r="P9">
-        <v>218</v>
+        <v>118</v>
       </c>
       <c r="Q9">
-        <v>0.01053806998631984</v>
+        <v>0.1207161125319693</v>
       </c>
       <c r="R9">
-        <v>0.1553813257305773</v>
+        <v>-3.089005235602094</v>
       </c>
       <c r="S9">
-        <v>128</v>
+        <v>5.840000000000003</v>
       </c>
       <c r="T9">
-        <v>0.3699421965317919</v>
+        <v>0.04715762273901811</v>
       </c>
       <c r="U9">
-        <v>7201</v>
+        <v>231.8</v>
       </c>
       <c r="V9">
-        <v>0.348094687942611</v>
+        <v>0.2371355498721228</v>
       </c>
       <c r="W9">
-        <v>0.1972167556929997</v>
+        <v>-0.05405405405405406</v>
       </c>
       <c r="X9">
-        <v>0.03573422452866627</v>
+        <v>0.161572298490447</v>
       </c>
       <c r="Y9">
-        <v>0.1614825311643334</v>
+        <v>-0.2156263525445011</v>
       </c>
       <c r="Z9">
-        <v>1.855922941964393</v>
+        <v>0.2598800386984869</v>
       </c>
       <c r="AA9">
-        <v>0.001677240889347454</v>
+        <v>0.0008647015487703758</v>
       </c>
       <c r="AB9">
-        <v>0.03345876584373829</v>
+        <v>0.06224343342801249</v>
       </c>
       <c r="AC9">
-        <v>-0.03178152495439084</v>
+        <v>-0.06137873187924211</v>
       </c>
       <c r="AD9">
-        <v>3400</v>
+        <v>4558.3</v>
       </c>
       <c r="AE9">
-        <v>453.3962480432918</v>
+        <v>66.668370775068</v>
       </c>
       <c r="AF9">
-        <v>3853.396248043292</v>
+        <v>4624.968370775068</v>
       </c>
       <c r="AG9">
-        <v>-3347.603751956708</v>
+        <v>4393.168370775068</v>
       </c>
       <c r="AH9">
-        <v>0.1570232163904924</v>
+        <v>0.8255233344825169</v>
       </c>
       <c r="AI9">
-        <v>0.3169850808921714</v>
+        <v>0.8594249844320753</v>
       </c>
       <c r="AJ9">
-        <v>-0.1930645687153813</v>
+        <v>0.8179928581479455</v>
       </c>
       <c r="AK9">
-        <v>-0.6755471377851078</v>
+        <v>0.8530973364628254</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>-1.31</v>
       </c>
       <c r="AN9">
-        <v>33.33333333333334</v>
+        <v>283.1242236024844</v>
       </c>
       <c r="AP9">
-        <v>-32.81964462702655</v>
+        <v>272.8676006692589</v>
+      </c>
+      <c r="AQ9">
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -1585,7 +1603,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Interactive Brokers Group, Inc. (NasdaqGS:IBKR)</t>
+          <t>Morgan Stanley (NYSE:MS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1594,13 +1612,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.146</v>
+        <v>0.0808</v>
       </c>
       <c r="E10">
-        <v>0.263</v>
+        <v>0.119</v>
       </c>
       <c r="F10">
-        <v>0.234</v>
+        <v>0.03</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1609,91 +1627,91 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>-0.001672777118372226</v>
+        <v>-0.0008835960393987392</v>
       </c>
       <c r="J10">
-        <v>-0.001554219271665888</v>
+        <v>-0.0006897171878093007</v>
       </c>
       <c r="K10">
-        <v>312</v>
+        <v>12489</v>
       </c>
       <c r="L10">
-        <v>0.1139934234563391</v>
+        <v>0.2260493402595522</v>
       </c>
       <c r="M10">
-        <v>64</v>
+        <v>16958.795</v>
       </c>
       <c r="N10">
-        <v>0.008208390514178713</v>
+        <v>0.1180209418545497</v>
       </c>
       <c r="O10">
-        <v>0.2051282051282051</v>
+        <v>1.357898550724637</v>
       </c>
       <c r="P10">
-        <v>37</v>
+        <v>4985.795</v>
       </c>
       <c r="Q10">
-        <v>0.004745475766009568</v>
+        <v>0.03469752549008964</v>
       </c>
       <c r="R10">
-        <v>0.1185897435897436</v>
+        <v>0.3992149091200256</v>
       </c>
       <c r="S10">
-        <v>27</v>
+        <v>11973</v>
       </c>
       <c r="T10">
-        <v>0.421875</v>
+        <v>0.7060053500263432</v>
       </c>
       <c r="U10">
-        <v>2838</v>
+        <v>111696</v>
       </c>
       <c r="V10">
-        <v>0.3639908168631123</v>
+        <v>0.777323337028709</v>
       </c>
       <c r="W10">
-        <v>0.1939092604101927</v>
+        <v>0.1272401251107964</v>
       </c>
       <c r="X10">
-        <v>0.05158025022195639</v>
+        <v>0.115703982564252</v>
       </c>
       <c r="Y10">
-        <v>0.1423290101882363</v>
+        <v>0.01153614254654441</v>
       </c>
       <c r="Z10">
-        <v>0.5655084918267327</v>
+        <v>0.1717129488538522</v>
       </c>
       <c r="AA10">
-        <v>-0.0008789241962878194</v>
+        <v>-0.0001184333721939212</v>
       </c>
       <c r="AB10">
-        <v>0.03154630512524899</v>
+        <v>0.06273370426669804</v>
       </c>
       <c r="AC10">
-        <v>-0.03242522932153681</v>
+        <v>-0.06285213763889196</v>
       </c>
       <c r="AD10">
-        <v>10642</v>
+        <v>349616</v>
       </c>
       <c r="AE10">
-        <v>127.8919548649239</v>
+        <v>4674.088987903705</v>
       </c>
       <c r="AF10">
-        <v>10769.89195486492</v>
+        <v>354290.0889879037</v>
       </c>
       <c r="AG10">
-        <v>7931.891954864925</v>
+        <v>242594.0889879037</v>
       </c>
       <c r="AH10">
-        <v>0.5800620797090887</v>
+        <v>0.7114498979533014</v>
       </c>
       <c r="AI10">
-        <v>0.5182593691481867</v>
+        <v>0.7763065783176015</v>
       </c>
       <c r="AJ10">
-        <v>0.5042912372180997</v>
+        <v>0.6280148446639279</v>
       </c>
       <c r="AK10">
-        <v>0.4420631843973357</v>
+        <v>0.7038177872324258</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1702,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>506.7619047619048</v>
+        <v>394.6004514672686</v>
       </c>
       <c r="AP10">
-        <v>377.7091407078536</v>
+        <v>273.8082268486498</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1734,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Morgan Group Holding Co. (OTCPK:MGHL)</t>
+          <t>Siebert Financial Corp. (NasdaqCM:SIEB)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1724,6 +1742,9 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.363</v>
+      </c>
       <c r="G11">
         <v>0</v>
       </c>
@@ -1731,16 +1752,16 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.01537165889890015</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.01537165889890015</v>
       </c>
       <c r="K11">
-        <v>-2.2</v>
+        <v>1.28</v>
       </c>
       <c r="L11">
-        <v>-0.8661417322834646</v>
+        <v>0.0252465483234714</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1749,7 +1770,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1758,67 +1779,73 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2.93</v>
+        <v>4.49</v>
       </c>
       <c r="V11">
-        <v>2.271317829457364</v>
+        <v>0.1018140589569161</v>
       </c>
       <c r="W11">
-        <v>-0.4247104247104247</v>
+        <v>0.03004694835680751</v>
       </c>
       <c r="X11">
-        <v>0.03326426946963817</v>
+        <v>0.3559046855725448</v>
       </c>
       <c r="Y11">
-        <v>-0.4579746941800629</v>
+        <v>-0.3258577372157373</v>
       </c>
       <c r="Z11">
-        <v>-11.04347826086954</v>
+        <v>0.06051178761222373</v>
       </c>
       <c r="AA11">
-        <v>-0</v>
+        <v>0.0009301665585377947</v>
       </c>
       <c r="AB11">
-        <v>0.03326426946963817</v>
+        <v>0.06443799709247988</v>
       </c>
       <c r="AC11">
-        <v>-0.03326426946963817</v>
+        <v>-0.06350783053394209</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>629.2</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>2.803284469128813</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>632.0032844691289</v>
       </c>
       <c r="AG11">
-        <v>-2.93</v>
+        <v>627.5132844691288</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.9347732794485283</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.9210146596107726</v>
       </c>
       <c r="AJ11">
-        <v>1.786585365853659</v>
+        <v>0.9343372130662089</v>
       </c>
       <c r="AK11">
-        <v>-58.60000000000021</v>
+        <v>0.9204944347795609</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>469.5522388059701</v>
+      </c>
+      <c r="AP11">
+        <v>468.2934958724842</v>
       </c>
     </row>
     <row r="12">
@@ -1829,7 +1856,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Armada Mercantile Ltd. (OTCPK:AAMT.F)</t>
+          <t>The Goldman Sachs Group, Inc. (NYSE:GS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1838,7 +1865,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0238</v>
+        <v>0.07870000000000001</v>
+      </c>
+      <c r="E12">
+        <v>0.101</v>
+      </c>
+      <c r="F12">
+        <v>-0.04769999999999999</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1847,94 +1880,103 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-0.003137245700963243</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-0.002562487360718461</v>
       </c>
       <c r="K12">
-        <v>4.31</v>
+        <v>13870</v>
       </c>
       <c r="L12">
-        <v>20.92233009708738</v>
+        <v>0.2930859606119516</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>7078.05</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.05868343750854999</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.5103136265320837</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>2986.05</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.0247570557671118</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.2152883922134103</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>4092</v>
+      </c>
+      <c r="T12">
+        <v>0.5781253311293365</v>
       </c>
       <c r="U12">
-        <v>0.113</v>
+        <v>284251</v>
       </c>
       <c r="V12">
-        <v>0.03112947658402204</v>
+        <v>2.356697931668022</v>
       </c>
       <c r="W12">
-        <v>205.2380952380952</v>
+        <v>0.1439632981815162</v>
       </c>
       <c r="X12">
-        <v>0.0333555912100847</v>
+        <v>0.163801466915972</v>
       </c>
       <c r="Y12">
-        <v>205.2047396468851</v>
+        <v>-0.01983816873445579</v>
       </c>
       <c r="Z12">
-        <v>-4.382978723404255</v>
+        <v>0.1015008643350825</v>
       </c>
       <c r="AA12">
-        <v>-0</v>
+        <v>-0.0002600946819606482</v>
       </c>
       <c r="AB12">
-        <v>0.03328228197042169</v>
+        <v>0.06341035532459104</v>
       </c>
       <c r="AC12">
-        <v>-0.03328228197042169</v>
+        <v>-0.06367045000655168</v>
       </c>
       <c r="AD12">
-        <v>0.025</v>
+        <v>581691</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>2267.335077761923</v>
       </c>
       <c r="AF12">
-        <v>0.025</v>
+        <v>583958.3350777619</v>
       </c>
       <c r="AG12">
-        <v>-0.08799999999999999</v>
+        <v>299707.3350777619</v>
       </c>
       <c r="AH12">
-        <v>0.006839945280437757</v>
+        <v>0.828812349170759</v>
       </c>
       <c r="AI12">
-        <v>0.00572737686139748</v>
+        <v>0.8294010515457423</v>
       </c>
       <c r="AJ12">
-        <v>-0.02484472049689441</v>
+        <v>0.7130431856807738</v>
       </c>
       <c r="AK12">
-        <v>-0.02069614299153339</v>
+        <v>0.7138925777134415</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>1907.183606557377</v>
+      </c>
+      <c r="AP12">
+        <v>982.6470002549571</v>
       </c>
     </row>
     <row r="13">
@@ -1945,7 +1987,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Financial Gravity Companies, Inc. (OTCPK:FGCO)</t>
+          <t>The Charles Schwab Corporation (NYSE:SCHW)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1953,6 +1995,15 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D13">
+        <v>0.19</v>
+      </c>
+      <c r="E13">
+        <v>0.244</v>
+      </c>
+      <c r="F13">
+        <v>0.228</v>
+      </c>
       <c r="G13">
         <v>0</v>
       </c>
@@ -1960,94 +2011,103 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.001214553696770631</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>0.0009364452932663608</v>
       </c>
       <c r="K13">
-        <v>-7.42</v>
+        <v>6795</v>
       </c>
       <c r="L13">
-        <v>-1.114114114114114</v>
+        <v>0.3409946304009635</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>2976</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.01914753575203941</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>0.4379690949227373</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>1521</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.009786089341012078</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>0.223841059602649</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1455</v>
+      </c>
+      <c r="T13">
+        <v>0.4889112903225806</v>
       </c>
       <c r="U13">
-        <v>0.306</v>
+        <v>46486</v>
       </c>
       <c r="V13">
-        <v>0.02217391304347826</v>
+        <v>0.2990901703525887</v>
       </c>
       <c r="W13">
-        <v>-0.9919786096256684</v>
+        <v>0.1430887803234501</v>
       </c>
       <c r="X13">
-        <v>0.03377544886755329</v>
+        <v>0.06934219589242689</v>
       </c>
       <c r="Y13">
-        <v>-1.025754058493222</v>
+        <v>0.07374658443102323</v>
       </c>
       <c r="Z13">
-        <v>-15.74468085106383</v>
+        <v>0.455120717331752</v>
       </c>
       <c r="AA13">
-        <v>-0</v>
+        <v>0.000426195653613329</v>
       </c>
       <c r="AB13">
-        <v>0.03336202159711102</v>
+        <v>0.06492620862649429</v>
       </c>
       <c r="AC13">
-        <v>-0.03336202159711102</v>
+        <v>-0.06450001297288095</v>
       </c>
       <c r="AD13">
-        <v>0.532</v>
+        <v>26428</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>833.9879424222581</v>
       </c>
       <c r="AF13">
-        <v>0.532</v>
+        <v>27261.98794242226</v>
       </c>
       <c r="AG13">
-        <v>0.226</v>
+        <v>-19224.01205757774</v>
       </c>
       <c r="AH13">
-        <v>0.03711973206809936</v>
+        <v>0.1492281033143174</v>
       </c>
       <c r="AI13">
-        <v>0.1983594332587621</v>
+        <v>0.4239614489894778</v>
       </c>
       <c r="AJ13">
-        <v>0.01611293312419792</v>
+        <v>-0.1411447500595925</v>
       </c>
       <c r="AK13">
-        <v>0.09511784511784514</v>
+        <v>-1.078970930423394</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>138.3664921465969</v>
+      </c>
+      <c r="AP13">
+        <v>-100.6492777883651</v>
       </c>
     </row>
     <row r="14">
@@ -2058,7 +2118,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Siebert Financial Corp. (NasdaqCM:SIEB)</t>
+          <t>Jefferies Financial Group Inc. (NYSE:JEF)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2066,9 +2126,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D14">
-        <v>0.464</v>
-      </c>
       <c r="G14">
         <v>0</v>
       </c>
@@ -2076,88 +2133,91 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0.01315358473682592</v>
+        <v>-0.003364945190256922</v>
       </c>
       <c r="J14">
-        <v>0.0100856396934601</v>
+        <v>-0.002548320225394539</v>
       </c>
       <c r="K14">
-        <v>5.49</v>
+        <v>968.8</v>
       </c>
       <c r="L14">
-        <v>0.08157503714710253</v>
+        <v>0.1550377672513122</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>1048.9</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.1336212387576754</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>1.082679603633361</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>222.8</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.02838288873601875</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.2299752270850537</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>826.1000000000001</v>
+      </c>
+      <c r="T14">
+        <v>0.7875869959004672</v>
       </c>
       <c r="U14">
-        <v>4.26</v>
+        <v>9477.5</v>
       </c>
       <c r="V14">
-        <v>0.05933147632311978</v>
+        <v>1.207355601416596</v>
       </c>
       <c r="W14">
-        <v>0.1512396694214876</v>
+        <v>0.09331625232375576</v>
       </c>
       <c r="X14">
-        <v>0.1812515549355395</v>
+        <v>0.1287240081767549</v>
       </c>
       <c r="Y14">
-        <v>-0.03001188551405184</v>
+        <v>-0.0354077558529991</v>
       </c>
       <c r="Z14">
-        <v>0.2170310916686914</v>
+        <v>0.2444849799501619</v>
       </c>
       <c r="AA14">
-        <v>0.002188897392848731</v>
+        <v>-0.0006230260192121761</v>
       </c>
       <c r="AB14">
-        <v>0.03568114119753509</v>
+        <v>0.06469593935343568</v>
       </c>
       <c r="AC14">
-        <v>-0.03349224380468636</v>
+        <v>-0.06531896537264785</v>
       </c>
       <c r="AD14">
-        <v>798.7</v>
+        <v>23921.1</v>
       </c>
       <c r="AE14">
-        <v>2.623818736058079</v>
+        <v>482.1343475243873</v>
       </c>
       <c r="AF14">
-        <v>801.3238187360581</v>
+        <v>24403.23434752439</v>
       </c>
       <c r="AG14">
-        <v>797.0638187360581</v>
+        <v>14925.73434752439</v>
       </c>
       <c r="AH14">
-        <v>0.9177665315511169</v>
+        <v>0.7566182482113495</v>
       </c>
       <c r="AI14">
-        <v>0.9495215100531208</v>
+        <v>0.6991923194086054</v>
       </c>
       <c r="AJ14">
-        <v>0.9173633445751627</v>
+        <v>0.6553406879407313</v>
       </c>
       <c r="AK14">
-        <v>0.9492654095014769</v>
+        <v>0.5870602837207015</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2166,10 +2226,10 @@
         <v>0</v>
       </c>
       <c r="AN14">
-        <v>566.45390070922</v>
+        <v>317.2559681697612</v>
       </c>
       <c r="AP14">
-        <v>565.2934884652894</v>
+        <v>197.9540364393155</v>
       </c>
     </row>
     <row r="15">
@@ -2180,7 +2240,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B. Riley Financial, Inc. (NasdaqGM:RILY)</t>
+          <t>Armada Mercantile Ltd. (OTCPK:AAMT.F)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2188,12 +2248,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D15">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="E15">
-        <v>1.328</v>
-      </c>
       <c r="G15">
         <v>0</v>
       </c>
@@ -2201,106 +2255,94 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>-0.0008587712702870382</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>-0.0006295085942214993</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>552.5</v>
+        <v>0.117</v>
       </c>
       <c r="L15">
-        <v>0.3466340422862162</v>
+        <v>0.420863309352518</v>
       </c>
       <c r="M15">
-        <v>97.09999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.03963588864397093</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.1757466063348416</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>54.4</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.02220589435872316</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.09846153846153846</v>
+        <v>-0</v>
       </c>
       <c r="S15">
-        <v>42.7</v>
-      </c>
-      <c r="T15">
-        <v>0.4397528321318229</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>378.2</v>
+        <v>0.216</v>
       </c>
       <c r="V15">
-        <v>0.1543799493836231</v>
+        <v>0.04705882352941176</v>
       </c>
       <c r="W15">
-        <v>1.477667825621824</v>
+        <v>0.02702078521939954</v>
       </c>
       <c r="X15">
-        <v>0.0500859497292413</v>
+        <v>0.06581346300979396</v>
       </c>
       <c r="Y15">
-        <v>1.427581875892583</v>
+        <v>-0.03879267779039442</v>
       </c>
       <c r="Z15">
-        <v>0.9765682573581007</v>
+        <v>0.06553512494106555</v>
       </c>
       <c r="AA15">
-        <v>-0.0006147581108508374</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.03349316212397118</v>
+        <v>0.06578983573774848</v>
       </c>
       <c r="AC15">
-        <v>-0.03410792023482202</v>
+        <v>-0.06578983573774848</v>
       </c>
       <c r="AD15">
-        <v>3042</v>
+        <v>0.005</v>
       </c>
       <c r="AE15">
-        <v>65.84397763855256</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>3107.843977638553</v>
+        <v>0.005</v>
       </c>
       <c r="AG15">
-        <v>2729.643977638553</v>
+        <v>-0.211</v>
       </c>
       <c r="AH15">
-        <v>0.5592017031215227</v>
+        <v>0.001088139281828074</v>
       </c>
       <c r="AI15">
-        <v>0.7399551038477262</v>
+        <v>0.001158748551564311</v>
       </c>
       <c r="AJ15">
-        <v>0.5270148667353808</v>
+        <v>-0.04818451701301667</v>
       </c>
       <c r="AK15">
-        <v>0.7142217195703393</v>
+        <v>-0.05147596974871921</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-0.202</v>
-      </c>
-      <c r="AN15">
-        <v>257.7966101694915</v>
-      </c>
-      <c r="AP15">
-        <v>231.3257608168265</v>
-      </c>
-      <c r="AQ15">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2311,7 +2353,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation (NYSE:SCHW)</t>
+          <t>Morgan Group Holding Co. (OTCPK:MGHL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2319,15 +2361,6 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D16">
-        <v>0.204</v>
-      </c>
-      <c r="E16">
-        <v>0.249</v>
-      </c>
-      <c r="F16">
-        <v>0.314</v>
-      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2335,103 +2368,94 @@
         <v>0</v>
       </c>
       <c r="I16">
-        <v>-0.001187513851025749</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>-0.0008965182715670248</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>5410</v>
+        <v>-0.828</v>
       </c>
       <c r="L16">
-        <v>0.3007560595952857</v>
+        <v>-0.3136363636363636</v>
       </c>
       <c r="M16">
-        <v>1364</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.008578643329067073</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>0.2521256931608133</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>1364</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.008578643329067073</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>0.2521256931608133</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>34323</v>
+        <v>2.39</v>
       </c>
       <c r="V16">
-        <v>0.2158686033603879</v>
+        <v>1.991666666666667</v>
       </c>
       <c r="W16">
-        <v>0.2075341414761393</v>
+        <v>-0.2778523489932886</v>
       </c>
       <c r="X16">
-        <v>0.0359996408540831</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="Y16">
-        <v>0.1715345006220562</v>
+        <v>-0.343643760196544</v>
       </c>
       <c r="Z16">
-        <v>1.449031945172497</v>
+        <v>52.80000000000019</v>
       </c>
       <c r="AA16">
-        <v>-0.001299083614931451</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03314897058443463</v>
+        <v>0.06579141120325535</v>
       </c>
       <c r="AC16">
-        <v>-0.03444805419936608</v>
+        <v>-0.06579141120325535</v>
       </c>
       <c r="AD16">
-        <v>31783</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1016.804995761256</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>32799.80499576125</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>-1523.195004238747</v>
+        <v>-2.39</v>
       </c>
       <c r="AH16">
-        <v>0.1710110732491243</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>0.3634657462503315</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>-0.009672534571342314</v>
+        <v>2.008403361344538</v>
       </c>
       <c r="AK16">
-        <v>-0.02723940549792164</v>
+        <v>9.958333333333325</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>174.6318681318681</v>
-      </c>
-      <c r="AP16">
-        <v>-8.369203319993115</v>
       </c>
     </row>
     <row r="17">
@@ -2442,7 +2466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc. (NYSE:GS)</t>
+          <t>BGC Partners, Inc. (NasdaqGS:BGCP)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2451,106 +2475,103 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.144</v>
+        <v>-0.109</v>
       </c>
       <c r="E17">
-        <v>0.307</v>
-      </c>
-      <c r="F17">
-        <v>0.09619999999999999</v>
+        <v>-0.106</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.02078128548716784</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.003738515501700704</v>
+        <v>-0.0007504389977988244</v>
       </c>
       <c r="J17">
-        <v>-0.003012245109969732</v>
+        <v>-0.000539074075686992</v>
       </c>
       <c r="K17">
-        <v>22206</v>
+        <v>122.9</v>
       </c>
       <c r="L17">
-        <v>0.3819729938935237</v>
+        <v>0.06978196684079037</v>
       </c>
       <c r="M17">
-        <v>7603.2</v>
+        <v>232.4</v>
       </c>
       <c r="N17">
-        <v>0.05958144411653614</v>
+        <v>0.1665114279572974</v>
       </c>
       <c r="O17">
-        <v>0.3423939475817346</v>
+        <v>1.890968266883645</v>
       </c>
       <c r="P17">
-        <v>1918.2</v>
+        <v>14.8</v>
       </c>
       <c r="Q17">
-        <v>0.0150317137658275</v>
+        <v>0.01060399799383822</v>
       </c>
       <c r="R17">
-        <v>0.08638205890299919</v>
+        <v>0.1204231082180635</v>
       </c>
       <c r="S17">
-        <v>5685</v>
+        <v>217.6</v>
       </c>
       <c r="T17">
-        <v>0.7477114898989899</v>
+        <v>0.9363166953528399</v>
       </c>
       <c r="U17">
-        <v>211830</v>
+        <v>473.3</v>
       </c>
       <c r="V17">
-        <v>1.659977023780231</v>
+        <v>0.3391129898975425</v>
       </c>
       <c r="W17">
-        <v>0.2726435596154554</v>
+        <v>0.1948010778253289</v>
       </c>
       <c r="X17">
-        <v>0.09318169741159003</v>
+        <v>0.08356502001618692</v>
       </c>
       <c r="Y17">
-        <v>0.1794618622038654</v>
+        <v>0.111236057809142</v>
       </c>
       <c r="Z17">
-        <v>0.1452929339375177</v>
+        <v>1.442414359565002</v>
       </c>
       <c r="AA17">
-        <v>-0.0004376579297664431</v>
+        <v>-0.0007775681876401481</v>
       </c>
       <c r="AB17">
-        <v>0.03427847075406451</v>
+        <v>0.06585085446916708</v>
       </c>
       <c r="AC17">
-        <v>-0.03471612868383096</v>
+        <v>-0.06662842265680723</v>
       </c>
       <c r="AD17">
-        <v>573834</v>
+        <v>1057.3</v>
       </c>
       <c r="AE17">
-        <v>2796.692993456852</v>
+        <v>168.1083658146164</v>
       </c>
       <c r="AF17">
-        <v>576630.6929934568</v>
+        <v>1225.408365814616</v>
       </c>
       <c r="AG17">
-        <v>364800.6929934568</v>
+        <v>752.1083658146165</v>
       </c>
       <c r="AH17">
-        <v>0.8187975147856323</v>
+        <v>0.4675153388531385</v>
       </c>
       <c r="AI17">
-        <v>0.8423799119530911</v>
+        <v>0.6275429486898366</v>
       </c>
       <c r="AJ17">
-        <v>0.7408461067458642</v>
+        <v>0.350174800408396</v>
       </c>
       <c r="AK17">
-        <v>0.7717453287616617</v>
+        <v>0.5083845564172392</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2559,10 +2580,10 @@
         <v>0</v>
       </c>
       <c r="AN17">
-        <v>1677.877192982456</v>
+        <v>32.73374613003096</v>
       </c>
       <c r="AP17">
-        <v>1066.668692963324</v>
+        <v>23.28508872491073</v>
       </c>
     </row>
     <row r="18">
@@ -2573,7 +2594,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Morgan Stanley (NYSE:MS)</t>
+          <t>Robinhood Markets, Inc. (NasdaqGS:HOOD)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2581,107 +2602,98 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D18">
-        <v>0.118</v>
-      </c>
-      <c r="E18">
-        <v>0.23</v>
-      </c>
-      <c r="F18">
-        <v>0.0487</v>
-      </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.7276116620684513</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>-0.004242086051646638</v>
+        <v>-0.005989766247608192</v>
       </c>
       <c r="J18">
-        <v>-0.00327109123249696</v>
+        <v>-0.005989766247608192</v>
       </c>
       <c r="K18">
-        <v>14723</v>
+        <v>-1284.4</v>
       </c>
       <c r="L18">
-        <v>0.2526729478796615</v>
+        <v>-0.9577212735813886</v>
       </c>
       <c r="M18">
-        <v>13046.24</v>
+        <v>19.1</v>
       </c>
       <c r="N18">
-        <v>0.07406765660172761</v>
+        <v>0.002646089052672411</v>
       </c>
       <c r="O18">
-        <v>0.8861128846023228</v>
+        <v>-0.01487075677359078</v>
       </c>
       <c r="P18">
-        <v>3768.24</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.02139349776739459</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.2559424030428581</v>
+        <v>0</v>
       </c>
       <c r="S18">
-        <v>9278</v>
+        <v>19.1</v>
       </c>
       <c r="T18">
-        <v>0.7111627564723629</v>
+        <v>1</v>
       </c>
       <c r="U18">
-        <v>123863</v>
+        <v>6187</v>
       </c>
       <c r="V18">
-        <v>0.7032096718793911</v>
+        <v>0.8571388988944613</v>
       </c>
       <c r="W18">
-        <v>0.1843278163106893</v>
+        <v>-0.1739295290198521</v>
       </c>
       <c r="X18">
-        <v>0.06016290898333414</v>
+        <v>0.07035201544660906</v>
       </c>
       <c r="Y18">
-        <v>0.1241649073273552</v>
+        <v>-0.2442815444664612</v>
       </c>
       <c r="Z18">
-        <v>0.1972012238985247</v>
+        <v>0.3010214408139252</v>
       </c>
       <c r="AA18">
-        <v>-0.000645063194532134</v>
+        <v>-0.001803048065993637</v>
       </c>
       <c r="AB18">
-        <v>0.03409392891983015</v>
+        <v>0.06500118877161749</v>
       </c>
       <c r="AC18">
-        <v>-0.03473899211436229</v>
+        <v>-0.06680423683761114</v>
       </c>
       <c r="AD18">
-        <v>351870</v>
+        <v>1423</v>
       </c>
       <c r="AE18">
-        <v>5440.910560716989</v>
+        <v>203.1643775733367</v>
       </c>
       <c r="AF18">
-        <v>357310.910560717</v>
+        <v>1626.164377573337</v>
       </c>
       <c r="AG18">
-        <v>233447.910560717</v>
+        <v>-4560.835622426664</v>
       </c>
       <c r="AH18">
-        <v>0.6698109205411289</v>
+        <v>0.1838644709954288</v>
       </c>
       <c r="AI18">
-        <v>0.7693537871609674</v>
+        <v>0.1895260167536851</v>
       </c>
       <c r="AJ18">
-        <v>0.5699587061065462</v>
+        <v>-1.716300429447146</v>
       </c>
       <c r="AK18">
-        <v>0.6854685623343828</v>
+        <v>-1.905776161958144</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2690,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AN18">
-        <v>418.3947681331748</v>
+        <v>43.65030674846626</v>
       </c>
       <c r="AP18">
-        <v>277.5837224265363</v>
+        <v>-139.9029332032719</v>
       </c>
     </row>
     <row r="19">
@@ -2704,7 +2716,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cowen Inc. (NasdaqGS:COWN)</t>
+          <t>Evercore Inc. (NYSE:EVR)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2713,10 +2725,10 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.364</v>
+        <v>0.136</v>
       </c>
       <c r="E19">
-        <v>0.893</v>
+        <v>0.274</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2725,91 +2737,91 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0.004666185993594678</v>
+        <v>-0.003263493553030856</v>
       </c>
       <c r="J19">
-        <v>0.003507224322883906</v>
+        <v>-0.002495310528637088</v>
       </c>
       <c r="K19">
-        <v>322.8</v>
+        <v>631.9</v>
       </c>
       <c r="L19">
-        <v>0.1744016424442163</v>
+        <v>0.2074183489249959</v>
       </c>
       <c r="M19">
-        <v>137.3</v>
+        <v>813.8</v>
       </c>
       <c r="N19">
-        <v>0.1393767130240585</v>
+        <v>0.1920970635445189</v>
       </c>
       <c r="O19">
-        <v>0.4253407682775713</v>
+        <v>1.287862003481564</v>
       </c>
       <c r="P19">
-        <v>10.5</v>
+        <v>125.9</v>
       </c>
       <c r="Q19">
-        <v>0.01065881636382093</v>
+        <v>0.02971862902464357</v>
       </c>
       <c r="R19">
-        <v>0.03252788104089219</v>
+        <v>0.199240386137047</v>
       </c>
       <c r="S19">
-        <v>126.8</v>
+        <v>687.9</v>
       </c>
       <c r="T19">
-        <v>0.9235251274581209</v>
+        <v>0.8452936839518309</v>
       </c>
       <c r="U19">
-        <v>1057.5</v>
+        <v>473.1</v>
       </c>
       <c r="V19">
-        <v>1.073495076641965</v>
+        <v>0.1116750070814843</v>
       </c>
       <c r="W19">
-        <v>0.398567724410421</v>
+        <v>0.5172724296005239</v>
       </c>
       <c r="X19">
-        <v>0.08728812314054107</v>
+        <v>0.06920330024341603</v>
       </c>
       <c r="Y19">
-        <v>0.31127960126988</v>
+        <v>0.4480691293571079</v>
       </c>
       <c r="Z19">
-        <v>0.8356144365465439</v>
+        <v>2.281490695655996</v>
       </c>
       <c r="AA19">
-        <v>0.002930687276408969</v>
+        <v>-0.005693027753857962</v>
       </c>
       <c r="AB19">
-        <v>0.04246470931423132</v>
+        <v>0.06433857645313538</v>
       </c>
       <c r="AC19">
-        <v>-0.03953402203782236</v>
+        <v>-0.07003160420699335</v>
       </c>
       <c r="AD19">
-        <v>3932.7</v>
+        <v>369.3</v>
       </c>
       <c r="AE19">
-        <v>80.81678172227805</v>
+        <v>344.7111655465425</v>
       </c>
       <c r="AF19">
-        <v>4013.516781722278</v>
+        <v>714.0111655465425</v>
       </c>
       <c r="AG19">
-        <v>2956.016781722278</v>
+        <v>240.9111655465425</v>
       </c>
       <c r="AH19">
-        <v>0.8029254805845343</v>
+        <v>0.1442326993999726</v>
       </c>
       <c r="AI19">
-        <v>0.7633718751954264</v>
+        <v>0.3101953697305172</v>
       </c>
       <c r="AJ19">
-        <v>0.7500454681859214</v>
+        <v>0.05380710802509851</v>
       </c>
       <c r="AK19">
-        <v>0.7037939503458638</v>
+        <v>0.1317382263997617</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2818,10 +2830,10 @@
         <v>0</v>
       </c>
       <c r="AN19">
-        <v>158.5766129032258</v>
+        <v>6.259322033898306</v>
       </c>
       <c r="AP19">
-        <v>119.1942250694467</v>
+        <v>4.083240094009195</v>
       </c>
     </row>
     <row r="20">
@@ -2832,7 +2844,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BGC Partners, Inc. (NasdaqGS:BGCP)</t>
+          <t>Oppenheimer Holdings Inc. (NYSE:OPY)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2841,103 +2853,100 @@
         </is>
       </c>
       <c r="D20">
-        <v>-0.0663</v>
-      </c>
-      <c r="E20">
-        <v>-0.25</v>
+        <v>0.0616</v>
       </c>
       <c r="G20">
-        <v>0.01726163117307594</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>-0.003334882859663831</v>
+        <v>0.00453720450522413</v>
       </c>
       <c r="J20">
-        <v>-0.003315234090382568</v>
+        <v>0.003072770961560372</v>
       </c>
       <c r="K20">
-        <v>47.4</v>
+        <v>72.8</v>
       </c>
       <c r="L20">
-        <v>0.02420713957407691</v>
+        <v>0.06346438845785024</v>
       </c>
       <c r="M20">
-        <v>242.2</v>
+        <v>72.24000000000001</v>
       </c>
       <c r="N20">
-        <v>0.1412574361367083</v>
+        <v>0.1556225764756571</v>
       </c>
       <c r="O20">
-        <v>5.109704641350211</v>
+        <v>0.9923076923076924</v>
       </c>
       <c r="P20">
-        <v>15.1</v>
+        <v>7.34</v>
       </c>
       <c r="Q20">
-        <v>0.008806718768225825</v>
+        <v>0.01581214993537268</v>
       </c>
       <c r="R20">
-        <v>0.3185654008438819</v>
+        <v>0.1008241758241758</v>
       </c>
       <c r="S20">
-        <v>227.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="T20">
-        <v>0.9376548307184146</v>
+        <v>0.8983942414174972</v>
       </c>
       <c r="U20">
-        <v>450.8</v>
+        <v>36.6</v>
       </c>
       <c r="V20">
-        <v>0.2629184649480928</v>
+        <v>0.07884532529082293</v>
       </c>
       <c r="W20">
-        <v>0.06498491911159858</v>
+        <v>0.09393548387096774</v>
       </c>
       <c r="X20">
-        <v>0.04544342618131968</v>
+        <v>0.09389240360020656</v>
       </c>
       <c r="Y20">
-        <v>0.0195414929302789</v>
+        <v>4.308027076117826e-05</v>
       </c>
       <c r="Z20">
-        <v>1.601521062217632</v>
+        <v>0.9410350879422312</v>
       </c>
       <c r="AA20">
-        <v>-0.005309417221929596</v>
+        <v>0.0028915852920383</v>
       </c>
       <c r="AB20">
-        <v>0.03508050795885979</v>
+        <v>0.0729712812980399</v>
       </c>
       <c r="AC20">
-        <v>-0.04038992518078938</v>
+        <v>-0.0700796960060016</v>
       </c>
       <c r="AD20">
-        <v>1359.7</v>
+        <v>461.9</v>
       </c>
       <c r="AE20">
-        <v>215.1501706375387</v>
+        <v>182.476863560287</v>
       </c>
       <c r="AF20">
-        <v>1574.850170637539</v>
+        <v>644.376863560287</v>
       </c>
       <c r="AG20">
-        <v>1124.050170637539</v>
+        <v>607.776863560287</v>
       </c>
       <c r="AH20">
-        <v>0.4787578740955094</v>
+        <v>0.5812649395287008</v>
       </c>
       <c r="AI20">
-        <v>0.6911329307723068</v>
+        <v>0.4171596524564231</v>
       </c>
       <c r="AJ20">
-        <v>0.3959805199895716</v>
+        <v>0.5669682660330161</v>
       </c>
       <c r="AK20">
-        <v>0.6149574996321934</v>
+        <v>0.4030145135476979</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2946,10 +2955,10 @@
         <v>0</v>
       </c>
       <c r="AN20">
-        <v>37.25205479452055</v>
+        <v>11.07673860911271</v>
       </c>
       <c r="AP20">
-        <v>30.79589508595997</v>
+        <v>14.57498473765676</v>
       </c>
     </row>
     <row r="21">
@@ -2960,7 +2969,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oppenheimer Holdings Inc. (NYSE:OPY)</t>
+          <t>Cowen Inc. (NasdaqGS:COWN)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2969,7 +2978,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.113</v>
+        <v>0.219</v>
+      </c>
+      <c r="E21">
+        <v>0.5770000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2978,91 +2990,91 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>-0.001327875256057467</v>
+        <v>0.005465006621529797</v>
       </c>
       <c r="J21">
-        <v>-0.0009588713816561018</v>
+        <v>0.00378401172301901</v>
       </c>
       <c r="K21">
-        <v>177.9</v>
+        <v>128.5</v>
       </c>
       <c r="L21">
-        <v>0.1234131113423517</v>
+        <v>0.09220061706249551</v>
       </c>
       <c r="M21">
-        <v>17.02</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="N21">
-        <v>0.02932460372157133</v>
+        <v>0.07924021488871832</v>
       </c>
       <c r="O21">
-        <v>0.09567172568858909</v>
+        <v>0.6428015564202334</v>
       </c>
       <c r="P21">
-        <v>6.42</v>
+        <v>14.6</v>
       </c>
       <c r="Q21">
-        <v>0.01106133700895934</v>
+        <v>0.01400613967766692</v>
       </c>
       <c r="R21">
-        <v>0.03608768971332209</v>
+        <v>0.1136186770428016</v>
       </c>
       <c r="S21">
-        <v>10.6</v>
+        <v>68</v>
       </c>
       <c r="T21">
-        <v>0.6227967097532315</v>
+        <v>0.8232445520581114</v>
       </c>
       <c r="U21">
-        <v>140.8</v>
+        <v>909.9</v>
       </c>
       <c r="V21">
-        <v>0.2425913163335631</v>
+        <v>0.8728894858019953</v>
       </c>
       <c r="W21">
-        <v>0.2891742522756827</v>
+        <v>0.1308820533713587</v>
       </c>
       <c r="X21">
-        <v>0.05050788783788871</v>
+        <v>0.1140799320781667</v>
       </c>
       <c r="Y21">
-        <v>0.238666364437794</v>
+        <v>0.01680212129319204</v>
       </c>
       <c r="Z21">
-        <v>1.207720704950428</v>
+        <v>0.3574398931272527</v>
       </c>
       <c r="AA21">
-        <v>-0.001158048821010499</v>
+        <v>0.001352556745868186</v>
       </c>
       <c r="AB21">
-        <v>0.03974183148180709</v>
+        <v>0.07449488152208145</v>
       </c>
       <c r="AC21">
-        <v>-0.04089988030281758</v>
+        <v>-0.07314232477621326</v>
       </c>
       <c r="AD21">
-        <v>540.2</v>
+        <v>2398.6</v>
       </c>
       <c r="AE21">
-        <v>214.5706609080342</v>
+        <v>87.9171013578696</v>
       </c>
       <c r="AF21">
-        <v>754.7706609080342</v>
+        <v>2486.51710135787</v>
       </c>
       <c r="AG21">
-        <v>613.9706609080342</v>
+        <v>1576.61710135787</v>
       </c>
       <c r="AH21">
-        <v>0.5652990160783815</v>
+        <v>0.7046119333324941</v>
       </c>
       <c r="AI21">
-        <v>0.4933881137843374</v>
+        <v>0.6527118884626012</v>
       </c>
       <c r="AJ21">
-        <v>0.514053702927746</v>
+        <v>0.6019880895548365</v>
       </c>
       <c r="AK21">
-        <v>0.4420328507922934</v>
+        <v>0.5437328606661725</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3071,10 +3083,10 @@
         <v>0</v>
       </c>
       <c r="AN21">
-        <v>13.17560975609756</v>
+        <v>95.18253968253968</v>
       </c>
       <c r="AP21">
-        <v>14.97489416848864</v>
+        <v>62.56417068880435</v>
       </c>
     </row>
     <row r="22">
@@ -3094,10 +3106,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.236</v>
+        <v>0.175</v>
       </c>
       <c r="E22">
-        <v>0.163</v>
+        <v>1.004</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3106,25 +3118,25 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>-0.0002922271158098239</v>
+        <v>-0.0001096350229081626</v>
       </c>
       <c r="J22">
-        <v>-0.0002205451886351883</v>
+        <v>-8.190986018860201e-05</v>
       </c>
       <c r="K22">
-        <v>116.3</v>
+        <v>207.1</v>
       </c>
       <c r="L22">
-        <v>0.00274012623900592</v>
+        <v>0.003144749589254097</v>
       </c>
       <c r="M22">
-        <v>11.7</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.009576035357669013</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.1006018916595013</v>
+        <v>-0</v>
       </c>
       <c r="P22">
         <v>-0</v>
@@ -3136,61 +3148,58 @@
         <v>-0</v>
       </c>
       <c r="S22">
-        <v>11.7</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>1109.6</v>
+        <v>1108.5</v>
       </c>
       <c r="V22">
-        <v>0.9081682763136356</v>
+        <v>0.5703627476202727</v>
       </c>
       <c r="W22">
-        <v>0.1515309446254072</v>
+        <v>0.2290929203539823</v>
       </c>
       <c r="X22">
-        <v>0.1175535750459225</v>
+        <v>0.1253232064344696</v>
       </c>
       <c r="Y22">
-        <v>0.03397736957948468</v>
+        <v>0.1037697139195126</v>
       </c>
       <c r="Z22">
-        <v>7.764943340247007</v>
+        <v>8.807783268930462</v>
       </c>
       <c r="AA22">
-        <v>-0.001712520893716326</v>
+        <v>-0.0007214442961296022</v>
       </c>
       <c r="AB22">
-        <v>0.0431653368109045</v>
+        <v>0.0750091139677535</v>
       </c>
       <c r="AC22">
-        <v>-0.04487785770462083</v>
+        <v>-0.07573055826388311</v>
       </c>
       <c r="AD22">
-        <v>7618.6</v>
+        <v>5593.3</v>
       </c>
       <c r="AE22">
-        <v>148.0154157222555</v>
+        <v>122.1005107081769</v>
       </c>
       <c r="AF22">
-        <v>7766.615415722255</v>
+        <v>5715.400510708177</v>
       </c>
       <c r="AG22">
-        <v>6657.015415722255</v>
+        <v>4606.900510708177</v>
       </c>
       <c r="AH22">
-        <v>0.8640694779345796</v>
+        <v>0.7462429499792138</v>
       </c>
       <c r="AI22">
-        <v>0.895739811229455</v>
+        <v>0.8422960843770805</v>
       </c>
       <c r="AJ22">
-        <v>0.8449259266105047</v>
+        <v>0.7033005849302054</v>
       </c>
       <c r="AK22">
-        <v>0.880439339123653</v>
+        <v>0.811502571123336</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3199,10 +3208,10 @@
         <v>0</v>
       </c>
       <c r="AN22">
-        <v>442.9418604651163</v>
+        <v>325.1918604651163</v>
       </c>
       <c r="AP22">
-        <v>387.0357799838521</v>
+        <v>267.8430529481498</v>
       </c>
     </row>
     <row r="23">
@@ -3213,7 +3222,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Houlihan Lokey, Inc. (NYSE:HLI)</t>
+          <t>Stifel Financial Corp. (NYSE:SF)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3222,10 +3231,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.209</v>
+        <v>0.103</v>
       </c>
       <c r="E23">
-        <v>0.3720000000000001</v>
+        <v>0.287</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3234,91 +3243,91 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>-0.003766055292623576</v>
+        <v>-0.01096175204431182</v>
       </c>
       <c r="J23">
-        <v>-0.002789397867821266</v>
+        <v>-0.008439679004119681</v>
       </c>
       <c r="K23">
-        <v>416.7</v>
+        <v>746.9</v>
       </c>
       <c r="L23">
-        <v>0.2139007237821467</v>
+        <v>0.1646024330042313</v>
       </c>
       <c r="M23">
-        <v>328.8</v>
+        <v>334.1</v>
       </c>
       <c r="N23">
-        <v>0.04649978786593126</v>
+        <v>0.0538558256496228</v>
       </c>
       <c r="O23">
-        <v>0.7890568754499639</v>
+        <v>0.4473155710269113</v>
       </c>
       <c r="P23">
-        <v>103.1</v>
+        <v>119.6</v>
       </c>
       <c r="Q23">
-        <v>0.01458068165747419</v>
+        <v>0.019279128248114</v>
       </c>
       <c r="R23">
-        <v>0.2474202063834893</v>
+        <v>0.1601285312625519</v>
       </c>
       <c r="S23">
-        <v>225.7</v>
+        <v>214.5</v>
       </c>
       <c r="T23">
-        <v>0.6864355231143552</v>
+        <v>0.642023346303502</v>
       </c>
       <c r="U23">
-        <v>923</v>
+        <v>1414.5</v>
       </c>
       <c r="V23">
-        <v>0.1305331636260783</v>
+        <v>0.228012766780579</v>
       </c>
       <c r="W23">
-        <v>0.3332000639692947</v>
+        <v>0.1818912402893115</v>
       </c>
       <c r="X23">
-        <v>0.03360724255347033</v>
+        <v>0.07339922549224728</v>
       </c>
       <c r="Y23">
-        <v>0.2995928214158244</v>
+        <v>0.1084920147970642</v>
       </c>
       <c r="Z23">
-        <v>5.384715676186887</v>
+        <v>1.218932928378174</v>
       </c>
       <c r="AA23">
-        <v>-0.01502011442597945</v>
+        <v>-0.01028740264306339</v>
       </c>
       <c r="AB23">
-        <v>0.03318959562198635</v>
+        <v>0.06582614242779825</v>
       </c>
       <c r="AC23">
-        <v>-0.0482097100479658</v>
+        <v>-0.07611354507086164</v>
       </c>
       <c r="AD23">
-        <v>0.711</v>
+        <v>1584.2</v>
       </c>
       <c r="AE23">
-        <v>182.1832615778</v>
+        <v>747.2002303813467</v>
       </c>
       <c r="AF23">
-        <v>182.8942615778</v>
+        <v>2331.400230381347</v>
       </c>
       <c r="AG23">
-        <v>-740.1057384222</v>
+        <v>916.9002303813468</v>
       </c>
       <c r="AH23">
-        <v>0.02521325166628752</v>
+        <v>0.2731576060282284</v>
       </c>
       <c r="AI23">
-        <v>0.112856293468382</v>
+        <v>0.3084352224326117</v>
       </c>
       <c r="AJ23">
-        <v>-0.1169038224052962</v>
+        <v>0.1287690753058569</v>
       </c>
       <c r="AK23">
-        <v>-1.060940118326445</v>
+        <v>0.1492277714307654</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3327,10 +3336,10 @@
         <v>0</v>
       </c>
       <c r="AN23">
-        <v>0.02443298969072165</v>
+        <v>15.88966900702106</v>
       </c>
       <c r="AP23">
-        <v>-25.43318688736083</v>
+        <v>9.196592080053628</v>
       </c>
     </row>
     <row r="24">
@@ -3341,7 +3350,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. (NasdaqGS:HOOD)</t>
+          <t>Moelis &amp; Company (NYSE:MC)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3349,92 +3358,104 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="F24">
-        <v>0.54</v>
+      <c r="D24">
+        <v>0.108</v>
+      </c>
+      <c r="E24">
+        <v>0.271</v>
       </c>
       <c r="G24">
-        <v>0.5843502824858757</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>-0.0005384135297344764</v>
+        <v>-0.01444394795648625</v>
       </c>
       <c r="J24">
-        <v>-0.0005384135297344764</v>
+        <v>-0.01098857957991258</v>
       </c>
       <c r="K24">
-        <v>-3250.1</v>
+        <v>229.3</v>
       </c>
       <c r="L24">
-        <v>-1.836214689265537</v>
+        <v>0.1905909733189261</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>303.6</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.1236962190352021</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>1.324029655473179</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>153.2</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.06241851368970013</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>0.6681203663323156</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>150.4</v>
+      </c>
+      <c r="T24">
+        <v>0.4953886693017129</v>
       </c>
       <c r="U24">
-        <v>6166.7</v>
+        <v>148.2</v>
       </c>
       <c r="V24">
-        <v>0.4038864583060439</v>
+        <v>0.06038135593220338</v>
+      </c>
+      <c r="W24">
+        <v>0.4436919504643964</v>
       </c>
       <c r="X24">
-        <v>0.03603938665447177</v>
+        <v>0.06745655249742369</v>
+      </c>
+      <c r="Y24">
+        <v>0.3762353979669727</v>
       </c>
       <c r="Z24">
-        <v>26.91402848944841</v>
+        <v>2.734395435124837</v>
       </c>
       <c r="AA24">
-        <v>-0.01449087707837818</v>
+        <v>-0.03004712184181896</v>
       </c>
       <c r="AB24">
-        <v>0.03372002592608174</v>
+        <v>0.06502583755529896</v>
       </c>
       <c r="AC24">
-        <v>-0.04821090300445992</v>
+        <v>-0.09507295939711793</v>
       </c>
       <c r="AD24">
-        <v>3129.7</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>65.76495973815011</v>
+        <v>201.887568932243</v>
       </c>
       <c r="AF24">
-        <v>3195.46495973815</v>
+        <v>201.887568932243</v>
       </c>
       <c r="AG24">
-        <v>-2971.23504026185</v>
+        <v>53.68756893224301</v>
       </c>
       <c r="AH24">
-        <v>0.1730658757906919</v>
+        <v>0.07600365686814414</v>
       </c>
       <c r="AI24">
-        <v>0.3020269697679848</v>
+        <v>0.3121389133460489</v>
       </c>
       <c r="AJ24">
-        <v>-0.2416195155541866</v>
+        <v>0.02140577928668543</v>
       </c>
       <c r="AK24">
-        <v>-0.6732357435579351</v>
+        <v>0.1076793170901119</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3443,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="AN24">
-        <v>256.5327868852459</v>
+        <v>0</v>
       </c>
       <c r="AP24">
-        <v>-243.5438557591681</v>
+        <v>2.334242127488827</v>
       </c>
     </row>
     <row r="25">
@@ -3457,7 +3478,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp. (NYSE:SF)</t>
+          <t>Greenhill &amp; Co., Inc. (NYSE:GHL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3466,10 +3487,10 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.126</v>
+        <v>-0.00335</v>
       </c>
       <c r="E25">
-        <v>0.628</v>
+        <v>-0.12</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3478,91 +3499,91 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>-0.01965853916070864</v>
+        <v>-0.02316889040488391</v>
       </c>
       <c r="J25">
-        <v>-0.0150353530616792</v>
+        <v>-0.01656845069651582</v>
       </c>
       <c r="K25">
-        <v>751.9</v>
+        <v>12.3</v>
       </c>
       <c r="L25">
-        <v>0.1667812701018122</v>
+        <v>0.04622322435174746</v>
       </c>
       <c r="M25">
-        <v>220.8</v>
+        <v>48.53</v>
       </c>
       <c r="N25">
-        <v>0.03011662006410694</v>
+        <v>0.2628927410617551</v>
       </c>
       <c r="O25">
-        <v>0.2936560712860753</v>
+        <v>3.945528455284553</v>
       </c>
       <c r="P25">
-        <v>59</v>
+        <v>6.33</v>
       </c>
       <c r="Q25">
-        <v>0.00804746641205756</v>
+        <v>0.03429035752979415</v>
       </c>
       <c r="R25">
-        <v>0.07846788136720309</v>
+        <v>0.5146341463414634</v>
       </c>
       <c r="S25">
-        <v>161.8</v>
+        <v>42.2</v>
       </c>
       <c r="T25">
-        <v>0.7327898550724637</v>
+        <v>0.8695652173913044</v>
       </c>
       <c r="U25">
-        <v>2054.3</v>
+        <v>57.5</v>
       </c>
       <c r="V25">
-        <v>0.2802018686489804</v>
+        <v>0.3114842903575298</v>
       </c>
       <c r="W25">
-        <v>0.2150928283319507</v>
+        <v>0.1524163568773234</v>
       </c>
       <c r="X25">
-        <v>0.03748077098856353</v>
+        <v>0.1061498080023754</v>
       </c>
       <c r="Y25">
-        <v>0.1776120573433871</v>
+        <v>0.04626654887494798</v>
       </c>
       <c r="Z25">
-        <v>1.219437329387812</v>
+        <v>1.623291370774336</v>
       </c>
       <c r="AA25">
-        <v>-0.01833467078393695</v>
+        <v>-0.02689542304275416</v>
       </c>
       <c r="AB25">
-        <v>0.0341795553795473</v>
+        <v>0.07401743058378267</v>
       </c>
       <c r="AC25">
-        <v>-0.05251422616348426</v>
+        <v>-0.1009128536265368</v>
       </c>
       <c r="AD25">
-        <v>1420.7</v>
+        <v>269.2</v>
       </c>
       <c r="AE25">
-        <v>910.6329604911139</v>
+        <v>98.82620868369804</v>
       </c>
       <c r="AF25">
-        <v>2331.332960491114</v>
+        <v>368.026208683698</v>
       </c>
       <c r="AG25">
-        <v>277.032960491114</v>
+        <v>310.526208683698</v>
       </c>
       <c r="AH25">
-        <v>0.2412680597939907</v>
+        <v>0.6659586586750939</v>
       </c>
       <c r="AI25">
-        <v>0.3273133647940166</v>
+        <v>0.8636554175358736</v>
       </c>
       <c r="AJ25">
-        <v>0.03641082478444466</v>
+        <v>0.6271657675105456</v>
       </c>
       <c r="AK25">
-        <v>0.05465958188829604</v>
+        <v>0.8423877667096289</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3571,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="AN25">
-        <v>15.19465240641711</v>
+        <v>19.79411764705882</v>
       </c>
       <c r="AP25">
-        <v>2.962919363541326</v>
+        <v>22.83280946203662</v>
       </c>
     </row>
     <row r="26">
@@ -3585,7 +3606,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Moelis &amp; Company (NYSE:MC)</t>
+          <t>Houlihan Lokey, Inc. (NYSE:HLI)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3594,11 +3615,11 @@
         </is>
       </c>
       <c r="D26">
+        <v>0.187</v>
+      </c>
+      <c r="E26">
         <v>0.214</v>
       </c>
-      <c r="E26">
-        <v>0.632</v>
-      </c>
       <c r="G26">
         <v>0</v>
       </c>
@@ -3606,91 +3627,91 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>-0.01916015772231111</v>
+        <v>-0.0009141834544414997</v>
       </c>
       <c r="J26">
-        <v>-0.01493374679999106</v>
+        <v>-0.0006785955614201608</v>
       </c>
       <c r="K26">
-        <v>392.6</v>
+        <v>370.4</v>
       </c>
       <c r="L26">
-        <v>0.2553329864724246</v>
+        <v>0.1633228978350015</v>
       </c>
       <c r="M26">
-        <v>239.2</v>
+        <v>412.1</v>
       </c>
       <c r="N26">
-        <v>0.06276567829965887</v>
+        <v>0.06886928039038738</v>
       </c>
       <c r="O26">
-        <v>0.6092715231788078</v>
+        <v>1.112580993520518</v>
       </c>
       <c r="P26">
-        <v>128.2</v>
+        <v>129.1</v>
       </c>
       <c r="Q26">
-        <v>0.03363946470742587</v>
+        <v>0.0215749189478258</v>
       </c>
       <c r="R26">
-        <v>0.3265410086602139</v>
+        <v>0.3485421166306695</v>
       </c>
       <c r="S26">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="T26">
-        <v>0.4640468227424749</v>
+        <v>0.6867265226886677</v>
       </c>
       <c r="U26">
-        <v>278.7</v>
+        <v>503.8</v>
       </c>
       <c r="V26">
-        <v>0.07313041196536342</v>
+        <v>0.08419399044085699</v>
       </c>
       <c r="W26">
-        <v>0.8387096774193549</v>
+        <v>0.2576337205258399</v>
       </c>
       <c r="X26">
-        <v>0.03410733467003506</v>
+        <v>0.06641515416070032</v>
       </c>
       <c r="Y26">
-        <v>0.8046023427493199</v>
+        <v>0.1912185663651396</v>
       </c>
       <c r="Z26">
-        <v>2.460540724115177</v>
+        <v>113.5233763114685</v>
       </c>
       <c r="AA26">
-        <v>-0.0367450921650027</v>
+        <v>-0.07703645928239312</v>
       </c>
       <c r="AB26">
-        <v>0.03308722193452699</v>
+        <v>0.06549032430718142</v>
       </c>
       <c r="AC26">
-        <v>-0.0698323140995297</v>
+        <v>-0.1425267835895745</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>0.506</v>
       </c>
       <c r="AE26">
-        <v>242.3032925691278</v>
+        <v>183.8663832816394</v>
       </c>
       <c r="AF26">
-        <v>242.3032925691278</v>
+        <v>184.3723832816394</v>
       </c>
       <c r="AG26">
-        <v>-36.3967074308722</v>
+        <v>-319.4276167183606</v>
       </c>
       <c r="AH26">
-        <v>0.05977921588382974</v>
+        <v>0.02989092584075093</v>
       </c>
       <c r="AI26">
-        <v>0.3238468675232954</v>
+        <v>0.113037523761325</v>
       </c>
       <c r="AJ26">
-        <v>-0.009642525216497472</v>
+        <v>-0.05639241121596265</v>
       </c>
       <c r="AK26">
-        <v>-0.07752172989396723</v>
+        <v>-0.2833632948484592</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -3699,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>0.0145821325648415</v>
       </c>
       <c r="AP26">
-        <v>-1.915616180572221</v>
+        <v>-9.205406821854771</v>
       </c>
     </row>
     <row r="27">
@@ -3713,7 +3734,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Evercore Inc. (NYSE:EVR)</t>
+          <t>BlackStar Enterprise Group, Inc. (OTCPK:BEGI)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3721,116 +3742,92 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D27">
-        <v>0.174</v>
-      </c>
-      <c r="E27">
-        <v>0.51</v>
-      </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27">
-        <v>0</v>
-      </c>
-      <c r="I27">
-        <v>-0.007936116978325925</v>
-      </c>
-      <c r="J27">
-        <v>-0.006210874156950725</v>
-      </c>
       <c r="K27">
-        <v>664.6</v>
-      </c>
-      <c r="L27">
-        <v>0.2124137049347993</v>
+        <v>-1.42</v>
       </c>
       <c r="M27">
-        <v>654</v>
+        <v>-0</v>
       </c>
       <c r="N27">
-        <v>0.1233776033806218</v>
+        <v>-0</v>
       </c>
       <c r="O27">
-        <v>0.9840505567258501</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>117.2</v>
+        <v>-0</v>
       </c>
       <c r="Q27">
-        <v>0.02210987020827045</v>
+        <v>-0</v>
       </c>
       <c r="R27">
-        <v>0.1763466746915438</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>536.8</v>
-      </c>
-      <c r="T27">
-        <v>0.8207951070336391</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>478.8</v>
+        <v>0.099</v>
       </c>
       <c r="V27">
-        <v>0.09032598853003321</v>
+        <v>0.3473684210526316</v>
       </c>
       <c r="W27">
-        <v>0.6845195179730148</v>
+        <v>-11.36</v>
       </c>
       <c r="X27">
-        <v>0.03518204599571655</v>
+        <v>0.1199162936687306</v>
       </c>
       <c r="Y27">
-        <v>0.6493374719772983</v>
+        <v>-11.47991629366873</v>
       </c>
       <c r="Z27">
-        <v>6.483852556525773</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>-0.04027039228080481</v>
+        <v>-21.45833333333341</v>
       </c>
       <c r="AB27">
-        <v>0.03331598912205858</v>
+        <v>0.08253222893561432</v>
       </c>
       <c r="AC27">
-        <v>-0.07358638140286339</v>
+        <v>-21.54086556226903</v>
       </c>
       <c r="AD27">
-        <v>376</v>
+        <v>0.762</v>
       </c>
       <c r="AE27">
-        <v>390.6526140089308</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>766.6526140089308</v>
+        <v>0.762</v>
       </c>
       <c r="AG27">
-        <v>287.8526140089307</v>
+        <v>0.663</v>
       </c>
       <c r="AH27">
-        <v>0.1263549404965822</v>
+        <v>0.7277936962750717</v>
       </c>
       <c r="AI27">
-        <v>0.3364204465422819</v>
+        <v>6</v>
       </c>
       <c r="AJ27">
-        <v>0.0515066213432873</v>
+        <v>0.699367088607595</v>
       </c>
       <c r="AK27">
-        <v>0.1599134446230707</v>
+        <v>23.67857142857141</v>
       </c>
       <c r="AL27">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>7.054409005628518</v>
-      </c>
-      <c r="AP27">
-        <v>5.40061189510189</v>
+        <v>1.07</v>
+      </c>
+      <c r="AO27">
+        <v>-0.4813084112149533</v>
+      </c>
+      <c r="AQ27">
+        <v>-0.4813084112149533</v>
       </c>
     </row>
     <row r="28">
@@ -3841,7 +3838,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Greenhill &amp; Co., Inc. (NYSE:GHL)</t>
+          <t>PJT Partners Inc. (NYSE:PJT)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3850,10 +3847,10 @@
         </is>
       </c>
       <c r="D28">
-        <v>0.0142</v>
+        <v>0.171</v>
       </c>
       <c r="E28">
-        <v>0.112</v>
+        <v>0.54</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3862,91 +3859,82 @@
         <v>0</v>
       </c>
       <c r="I28">
-        <v>-0.02827244744102142</v>
+        <v>-0.001277876367879876</v>
       </c>
       <c r="J28">
-        <v>-0.02263566512240442</v>
+        <v>-0.0010799620899142</v>
       </c>
       <c r="K28">
-        <v>76.7</v>
+        <v>100.9</v>
       </c>
       <c r="L28">
-        <v>0.2332725060827251</v>
+        <v>0.09514380009429516</v>
       </c>
       <c r="M28">
-        <v>38.73</v>
+        <v>147.6</v>
       </c>
       <c r="N28">
-        <v>0.1172215496368039</v>
+        <v>0.08204102051025512</v>
       </c>
       <c r="O28">
-        <v>0.5049543676662321</v>
+        <v>1.462834489593657</v>
       </c>
       <c r="P28">
-        <v>5.13</v>
+        <v>19.8</v>
       </c>
       <c r="Q28">
-        <v>0.01552663438256659</v>
+        <v>0.01100550275137569</v>
       </c>
       <c r="R28">
-        <v>0.06688396349413298</v>
+        <v>0.1962338949454906</v>
       </c>
       <c r="S28">
-        <v>33.6</v>
+        <v>127.8</v>
       </c>
       <c r="T28">
-        <v>0.8675445391169635</v>
+        <v>0.8658536585365854</v>
       </c>
       <c r="U28">
-        <v>93.5</v>
+        <v>189.8</v>
       </c>
       <c r="V28">
-        <v>0.2829903147699758</v>
+        <v>0.1054971930409649</v>
       </c>
       <c r="W28">
-        <v>5.723880597014926</v>
+        <v>1.295250320924262</v>
       </c>
       <c r="X28">
-        <v>0.04901162068463293</v>
+        <v>0.06753858342745714</v>
       </c>
       <c r="Y28">
-        <v>5.674868976330293</v>
-      </c>
-      <c r="Z28">
-        <v>1.933208997970391</v>
-      </c>
-      <c r="AA28">
-        <v>-0.04375947148967678</v>
+        <v>1.227711737496805</v>
       </c>
       <c r="AB28">
-        <v>0.03691932071849721</v>
-      </c>
-      <c r="AC28">
-        <v>-0.08067879220817399</v>
+        <v>0.06499111907422837</v>
       </c>
       <c r="AD28">
-        <v>287.4</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>104.9799035930392</v>
+        <v>155.275939440683</v>
       </c>
       <c r="AF28">
-        <v>392.3799035930392</v>
+        <v>155.275939440683</v>
       </c>
       <c r="AG28">
-        <v>298.8799035930392</v>
+        <v>-34.52406055931698</v>
       </c>
       <c r="AH28">
-        <v>0.5428760562412766</v>
+        <v>0.07945039452599943</v>
       </c>
       <c r="AI28">
-        <v>0.8294157088747928</v>
+        <v>0.1793488734983741</v>
       </c>
       <c r="AJ28">
-        <v>0.4749554242659042</v>
+        <v>-0.01956507497787829</v>
       </c>
       <c r="AK28">
-        <v>0.7873965422402308</v>
+        <v>-0.05107291331683037</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -3955,263 +3943,10 @@
         <v>0</v>
       </c>
       <c r="AN28">
-        <v>24.56410256410256</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>25.54529090538797</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>PJT Partners Inc. (NYSE:PJT)</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>0.184</v>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>-0.008989094093514064</v>
-      </c>
-      <c r="J29">
-        <v>-0.007786539699732919</v>
-      </c>
-      <c r="K29">
-        <v>117.4</v>
-      </c>
-      <c r="L29">
-        <v>0.1171072319201995</v>
-      </c>
-      <c r="M29">
-        <v>127.61</v>
-      </c>
-      <c r="N29">
-        <v>0.07097330367074527</v>
-      </c>
-      <c r="O29">
-        <v>1.086967632027257</v>
-      </c>
-      <c r="P29">
-        <v>4.91</v>
-      </c>
-      <c r="Q29">
-        <v>0.002730812013348165</v>
-      </c>
-      <c r="R29">
-        <v>0.04182282793867121</v>
-      </c>
-      <c r="S29">
-        <v>122.7</v>
-      </c>
-      <c r="T29">
-        <v>0.9615233915837317</v>
-      </c>
-      <c r="U29">
-        <v>261.1</v>
-      </c>
-      <c r="V29">
-        <v>0.1452169076751947</v>
-      </c>
-      <c r="W29">
-        <v>0.7574193548387097</v>
-      </c>
-      <c r="X29">
-        <v>0.03465920705978055</v>
-      </c>
-      <c r="Y29">
-        <v>0.7227601477789292</v>
-      </c>
-      <c r="Z29">
-        <v>30.38170254858257</v>
-      </c>
-      <c r="AA29">
-        <v>-0.236568333040015</v>
-      </c>
-      <c r="AB29">
-        <v>0.03298235787176186</v>
-      </c>
-      <c r="AC29">
-        <v>-0.2695506909117768</v>
-      </c>
-      <c r="AD29">
-        <v>0.091</v>
-      </c>
-      <c r="AE29">
-        <v>189.0578341437393</v>
-      </c>
-      <c r="AF29">
-        <v>189.1488341437393</v>
-      </c>
-      <c r="AG29">
-        <v>-71.95116585626076</v>
-      </c>
-      <c r="AH29">
-        <v>0.09518604288402148</v>
-      </c>
-      <c r="AI29">
-        <v>0.2413077954633455</v>
-      </c>
-      <c r="AJ29">
-        <v>-0.04168547519222096</v>
-      </c>
-      <c r="AK29">
-        <v>-0.1376400312286043</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>0</v>
-      </c>
-      <c r="AN29">
-        <v>0.003159722222222222</v>
-      </c>
-      <c r="AP29">
-        <v>-2.498304370009054</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Global Brokerage, Inc. (OTCPK:GLBR)</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D30">
-        <v>-0.138</v>
-      </c>
-      <c r="G30">
-        <v>0.2053811659192825</v>
-      </c>
-      <c r="H30">
-        <v>0.1381165919282511</v>
-      </c>
-      <c r="I30">
-        <v>-0.2348852923641256</v>
-      </c>
-      <c r="J30">
-        <v>-0.2348852923641256</v>
-      </c>
-      <c r="K30">
-        <v>-36.3</v>
-      </c>
-      <c r="L30">
-        <v>-0.3255605381165919</v>
-      </c>
-      <c r="M30">
-        <v>-0</v>
-      </c>
-      <c r="N30">
-        <v>-0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>-0</v>
-      </c>
-      <c r="Q30">
-        <v>-0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>59.5</v>
-      </c>
-      <c r="V30">
-        <v>2288.461538461539</v>
-      </c>
-      <c r="W30">
-        <v>0.2467709041468389</v>
-      </c>
-      <c r="X30">
-        <v>140.6386418612678</v>
-      </c>
-      <c r="Y30">
-        <v>-140.391870957121</v>
-      </c>
-      <c r="Z30">
-        <v>17.70248569475091</v>
-      </c>
-      <c r="AA30">
-        <v>-4.15805352798332</v>
-      </c>
-      <c r="AB30">
-        <v>0.03589744875984938</v>
-      </c>
-      <c r="AC30">
-        <v>-4.193950976743169</v>
-      </c>
-      <c r="AD30">
-        <v>253.7</v>
-      </c>
-      <c r="AE30">
-        <v>21.99855049300006</v>
-      </c>
-      <c r="AF30">
-        <v>275.698550493</v>
-      </c>
-      <c r="AG30">
-        <v>216.198550493</v>
-      </c>
-      <c r="AH30">
-        <v>0.9999057029925209</v>
-      </c>
-      <c r="AI30">
-        <v>2.990269901411648</v>
-      </c>
-      <c r="AJ30">
-        <v>0.9998797546349815</v>
-      </c>
-      <c r="AK30">
-        <v>6.611869554868584</v>
-      </c>
-      <c r="AL30">
-        <v>36.7</v>
-      </c>
-      <c r="AM30">
-        <v>36.7</v>
-      </c>
-      <c r="AN30">
-        <v>-13.28968046097433</v>
-      </c>
-      <c r="AO30">
-        <v>-0.7547683923705721</v>
-      </c>
-      <c r="AP30">
-        <v>-11.32522527464641</v>
-      </c>
-      <c r="AQ30">
-        <v>-0.7547683923705721</v>
+        <v>-1.162426281458484</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ28"/>
+  <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.1455</v>
+        <v>0.123</v>
       </c>
       <c r="E2">
-        <v>0.244</v>
+        <v>0.0684</v>
       </c>
       <c r="F2">
-        <v>0.225</v>
+        <v>0.0809</v>
       </c>
       <c r="G2">
-        <v>0.008677203682533429</v>
+        <v>0.01066201232455607</v>
       </c>
       <c r="H2">
-        <v>0.004291323140389774</v>
+        <v>0.006840185000480023</v>
       </c>
       <c r="I2">
-        <v>0.003138139706038804</v>
+        <v>0.006623577998943818</v>
       </c>
       <c r="J2">
-        <v>0.002583538736016828</v>
+        <v>0.00536871025283963</v>
       </c>
       <c r="K2">
-        <v>38423.549</v>
+        <v>28367.088</v>
       </c>
       <c r="L2">
-        <v>0.1600542272952828</v>
+        <v>0.1243661901326092</v>
       </c>
       <c r="M2">
-        <v>32541.531</v>
+        <v>36049.593</v>
       </c>
       <c r="N2">
-        <v>0.06338447532263279</v>
+        <v>0.06932313682639867</v>
       </c>
       <c r="O2">
-        <v>0.8469163272762753</v>
+        <v>1.270824590807488</v>
       </c>
       <c r="P2">
-        <v>11022.991</v>
+        <v>12346.393</v>
       </c>
       <c r="Q2">
-        <v>0.02147060938900211</v>
+        <v>0.02374203479222333</v>
       </c>
       <c r="R2">
-        <v>0.2868811259470072</v>
+        <v>0.4352365318569181</v>
       </c>
       <c r="S2">
-        <v>21518.54</v>
+        <v>23703.2</v>
       </c>
       <c r="T2">
-        <v>0.6612639091873089</v>
+        <v>0.6575164385351036</v>
       </c>
       <c r="U2">
-        <v>475486.795</v>
+        <v>416039.724</v>
       </c>
       <c r="V2">
-        <v>0.9261543663669436</v>
+        <v>0.8000417289612433</v>
       </c>
       <c r="W2">
-        <v>0.1474608823175952</v>
+        <v>0.1101194588758938</v>
       </c>
       <c r="X2">
-        <v>0.07848212275421709</v>
+        <v>0.06119215934805841</v>
       </c>
       <c r="Y2">
-        <v>0.06897875956337809</v>
+        <v>0.04892729952783538</v>
       </c>
       <c r="Z2">
-        <v>0.2650458496014069</v>
+        <v>0.2804176438108676</v>
       </c>
       <c r="AA2">
-        <v>-5.921668609696061e-05</v>
+        <v>-0.0001566132608711287</v>
       </c>
       <c r="AB2">
-        <v>0.06522890974559541</v>
+        <v>0.05573851229866451</v>
       </c>
       <c r="AC2">
-        <v>-0.06579062347050191</v>
+        <v>-0.05520337617451926</v>
       </c>
       <c r="AD2">
-        <v>1020465.273</v>
+        <v>1163538.012</v>
       </c>
       <c r="AE2">
-        <v>11937.82462235758</v>
+        <v>12034.1229704336</v>
       </c>
       <c r="AF2">
-        <v>1032403.097622358</v>
+        <v>1175572.134970434</v>
       </c>
       <c r="AG2">
-        <v>556916.3026223576</v>
+        <v>759532.4109704336</v>
       </c>
       <c r="AH2">
-        <v>0.6678753050728022</v>
+        <v>0.6933096448442365</v>
       </c>
       <c r="AI2">
-        <v>0.7653757897975896</v>
+        <v>0.7892423363825257</v>
       </c>
       <c r="AJ2">
-        <v>0.520329161166977</v>
+        <v>0.5935910890972707</v>
       </c>
       <c r="AK2">
-        <v>0.6376438449465098</v>
+        <v>0.7075588220590088</v>
       </c>
       <c r="AL2">
-        <v>117.37</v>
+        <v>169.693</v>
       </c>
       <c r="AM2">
-        <v>116.06</v>
+        <v>118.717</v>
       </c>
       <c r="AN2">
-        <v>298.9813699408756</v>
+        <v>273.6224171628434</v>
       </c>
       <c r="AO2">
-        <v>8.364871773025476</v>
+        <v>10.3579346231135</v>
       </c>
       <c r="AP2">
-        <v>163.168314989235</v>
+        <v>178.6147870201702</v>
       </c>
       <c r="AQ2">
-        <v>8.45928829915561</v>
+        <v>14.8055375388529</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Perella Weinberg Partners (NasdaqGS:PWP)</t>
+          <t>PJT Partners Inc. (NYSE:PJT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,89 +724,92 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.132</v>
+      </c>
       <c r="G3">
-        <v>0.00170015455950541</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01712848757673131</v>
+        <v>0.004684685516945756</v>
       </c>
       <c r="J3">
-        <v>0.01712848757673131</v>
+        <v>0.003686764341738376</v>
       </c>
       <c r="K3">
-        <v>18.9</v>
+        <v>81.5</v>
       </c>
       <c r="L3">
-        <v>0.02921174652241113</v>
+        <v>0.07368896925858952</v>
       </c>
       <c r="M3">
-        <v>144</v>
+        <v>158.8</v>
       </c>
       <c r="N3">
-        <v>0.3434295253994753</v>
+        <v>0.06430711913825221</v>
       </c>
       <c r="O3">
-        <v>7.61904761904762</v>
+        <v>1.948466257668712</v>
       </c>
       <c r="P3">
-        <v>78.8</v>
+        <v>24.5</v>
       </c>
       <c r="Q3">
-        <v>0.187932268065824</v>
+        <v>0.009921438406090548</v>
       </c>
       <c r="R3">
-        <v>4.169312169312169</v>
+        <v>0.3006134969325153</v>
       </c>
       <c r="S3">
-        <v>65.2</v>
+        <v>134.3</v>
       </c>
       <c r="T3">
-        <v>0.4527777777777778</v>
+        <v>0.8457178841309824</v>
       </c>
       <c r="U3">
-        <v>142.9</v>
+        <v>116</v>
       </c>
       <c r="V3">
-        <v>0.3408061054137849</v>
+        <v>0.04697497367781647</v>
       </c>
       <c r="W3">
-        <v>0.1509584664536741</v>
+        <v>0.5495616992582603</v>
       </c>
       <c r="X3">
-        <v>0.06772690118667012</v>
+        <v>0.05733630253819921</v>
       </c>
       <c r="Y3">
-        <v>0.083231565267004</v>
+        <v>0.492225396720061</v>
       </c>
       <c r="AB3">
-        <v>0.06541635223312067</v>
+        <v>0.05611885457069948</v>
       </c>
       <c r="AD3">
         <v>0</v>
       </c>
       <c r="AE3">
-        <v>40.08934268927422</v>
+        <v>134.59368909129</v>
       </c>
       <c r="AF3">
-        <v>40.08934268927422</v>
+        <v>134.59368909129</v>
       </c>
       <c r="AG3">
-        <v>-102.8106573107258</v>
+        <v>18.59368909128997</v>
       </c>
       <c r="AH3">
-        <v>0.08726659276549695</v>
+        <v>0.05168740986398428</v>
       </c>
       <c r="AI3">
-        <v>0.1275555268474662</v>
+        <v>0.1422324703660848</v>
       </c>
       <c r="AJ3">
-        <v>-0.3248471384126959</v>
+        <v>0.007473366661987433</v>
       </c>
       <c r="AK3">
-        <v>-0.5998661042601678</v>
+        <v>0.02239411106645858</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -818,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-5.38275692726313</v>
+        <v>0.5792426508190023</v>
       </c>
     </row>
     <row r="4">
@@ -838,124 +841,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.149</v>
+        <v>0.143</v>
       </c>
       <c r="E4">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F4">
-        <v>0.526</v>
+        <v>0.205</v>
       </c>
       <c r="G4">
-        <v>0.1232031380803176</v>
+        <v>0.1601486317258935</v>
       </c>
       <c r="H4">
-        <v>0.1232031380803176</v>
+        <v>0.1601486317258935</v>
       </c>
       <c r="I4">
-        <v>0.1171648206785676</v>
+        <v>0.1803169137055813</v>
       </c>
       <c r="J4">
-        <v>0.08970387416729413</v>
+        <v>0.1341065417305935</v>
       </c>
       <c r="K4">
-        <v>634.7</v>
+        <v>1167.8</v>
       </c>
       <c r="L4">
-        <v>0.07590470951230598</v>
+        <v>0.1198702551785018</v>
       </c>
       <c r="M4">
-        <v>331</v>
+        <v>1154.5</v>
       </c>
       <c r="N4">
-        <v>0.01923635729644912</v>
+        <v>0.06707373753805396</v>
       </c>
       <c r="O4">
-        <v>0.5215062234126359</v>
+        <v>0.9886110635382771</v>
       </c>
       <c r="P4">
-        <v>80</v>
+        <v>89.5</v>
       </c>
       <c r="Q4">
-        <v>0.004649270645667461</v>
+        <v>0.005199739722525621</v>
       </c>
       <c r="R4">
-        <v>0.1260438002205767</v>
+        <v>0.07663983558828567</v>
       </c>
       <c r="S4">
-        <v>251</v>
+        <v>1065</v>
       </c>
       <c r="T4">
-        <v>0.7583081570996979</v>
+        <v>0.9224772628843655</v>
       </c>
       <c r="U4">
-        <v>1219.4</v>
+        <v>799.2</v>
       </c>
       <c r="V4">
-        <v>0.07086650781658628</v>
+        <v>0.04643164230438521</v>
       </c>
       <c r="W4">
-        <v>0.3926627072506805</v>
+        <v>0.5840460115028757</v>
       </c>
       <c r="X4">
-        <v>0.06927171737826272</v>
+        <v>0.05921602500876158</v>
       </c>
       <c r="Y4">
-        <v>0.3233909898724178</v>
+        <v>0.5248299864941142</v>
       </c>
       <c r="Z4">
-        <v>4.260451117164931</v>
+        <v>4.654696600113496</v>
       </c>
       <c r="AA4">
-        <v>0.3821789709100706</v>
+        <v>0.6242252638463721</v>
       </c>
       <c r="AB4">
-        <v>0.06516091343620253</v>
+        <v>0.05506143507810976</v>
       </c>
       <c r="AC4">
-        <v>0.3170180574738681</v>
+        <v>0.5691638287682623</v>
       </c>
       <c r="AD4">
-        <v>2824.8</v>
+        <v>3230</v>
       </c>
       <c r="AE4">
-        <v>133.4560122497693</v>
+        <v>130.5828164874278</v>
       </c>
       <c r="AF4">
-        <v>2958.256012249769</v>
+        <v>3360.582816487428</v>
       </c>
       <c r="AG4">
-        <v>1738.856012249769</v>
+        <v>2561.382816487428</v>
       </c>
       <c r="AH4">
-        <v>0.1467006424541657</v>
+        <v>0.1633493230643355</v>
       </c>
       <c r="AI4">
-        <v>0.596692536893793</v>
+        <v>0.6164869037822662</v>
       </c>
       <c r="AJ4">
-        <v>0.09178028224881905</v>
+        <v>0.1295342848790541</v>
       </c>
       <c r="AK4">
-        <v>0.4651392233783838</v>
+        <v>0.5506002316709869</v>
       </c>
       <c r="AL4">
-        <v>116.3</v>
+        <v>169.5</v>
       </c>
       <c r="AM4">
-        <v>116.3</v>
+        <v>169.5</v>
       </c>
       <c r="AN4">
-        <v>2.21015569986699</v>
+        <v>1.525599848856981</v>
       </c>
       <c r="AO4">
-        <v>8.446259673258814</v>
+        <v>10.3716814159292</v>
       </c>
       <c r="AP4">
-        <v>1.360500752875181</v>
+        <v>1.20979728721303</v>
       </c>
       <c r="AQ4">
-        <v>8.446259673258814</v>
+        <v>10.3716814159292</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Piper Sandler Companies (NYSE:PIPR)</t>
+          <t>Virtu Financial, Inc. (NasdaqGS:VIRT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,100 +978,106 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.143</v>
+        <v>0.067</v>
+      </c>
+      <c r="E5">
+        <v>-0.0566</v>
+      </c>
+      <c r="F5">
+        <v>-0.0242</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.02327870751056807</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.003329028548106124</v>
+        <v>0.01327124823281463</v>
       </c>
       <c r="J5">
-        <v>0.002411821143063838</v>
+        <v>0.01131869676867638</v>
       </c>
       <c r="K5">
-        <v>186.1</v>
+        <v>164.1</v>
       </c>
       <c r="L5">
-        <v>0.1105894937009746</v>
+        <v>0.09502576871851294</v>
       </c>
       <c r="M5">
-        <v>188.74</v>
+        <v>327.4</v>
       </c>
       <c r="N5">
-        <v>0.1061350728223584</v>
+        <v>0.178604549669958</v>
       </c>
       <c r="O5">
-        <v>1.014185921547555</v>
+        <v>1.995124923826935</v>
       </c>
       <c r="P5">
-        <v>1.44</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.0008097621323736152</v>
+        <v>0.05286127325295947</v>
       </c>
       <c r="R5">
-        <v>0.007737775389575497</v>
+        <v>0.5904936014625229</v>
       </c>
       <c r="S5">
-        <v>187.3</v>
+        <v>230.5</v>
       </c>
       <c r="T5">
-        <v>0.9923704567129384</v>
+        <v>0.704031765424557</v>
       </c>
       <c r="U5">
-        <v>274.5</v>
+        <v>688.8</v>
       </c>
       <c r="V5">
-        <v>0.1543609064837204</v>
+        <v>0.375756914516393</v>
       </c>
       <c r="W5">
-        <v>0.1898592124056315</v>
+        <v>0.1217268748609154</v>
       </c>
       <c r="X5">
-        <v>0.06826951455807484</v>
+        <v>0.1074664598982557</v>
       </c>
       <c r="Y5">
-        <v>0.1215896978475567</v>
+        <v>0.01426041496265971</v>
       </c>
       <c r="Z5">
-        <v>3.714875952210061</v>
+        <v>0.5706101745287346</v>
       </c>
       <c r="AA5">
-        <v>0.008959616365399633</v>
+        <v>0.006458563538612256</v>
       </c>
       <c r="AB5">
-        <v>0.06532267244822948</v>
+        <v>0.04910816805377516</v>
       </c>
       <c r="AC5">
-        <v>-0.05636305608282985</v>
+        <v>-0.04264960451516291</v>
       </c>
       <c r="AD5">
-        <v>126.7</v>
+        <v>6738.7</v>
       </c>
       <c r="AE5">
-        <v>90.98955379623507</v>
+        <v>241.4094071337621</v>
       </c>
       <c r="AF5">
-        <v>217.6895537962351</v>
+        <v>6980.109407133762</v>
       </c>
       <c r="AG5">
-        <v>-56.81044620376491</v>
+        <v>6291.309407133762</v>
       </c>
       <c r="AH5">
-        <v>0.1090634734947407</v>
+        <v>0.7920053960687448</v>
       </c>
       <c r="AI5">
-        <v>0.1543361687510118</v>
+        <v>0.8220782109735324</v>
       </c>
       <c r="AJ5">
-        <v>-0.03300074989039946</v>
+        <v>0.7743712917285509</v>
       </c>
       <c r="AK5">
-        <v>-0.05000965547078889</v>
+        <v>0.8063703949627782</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1077,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>5.323529411764706</v>
+        <v>94.64466292134831</v>
       </c>
       <c r="AP5">
-        <v>-2.386993537973316</v>
+        <v>88.36108717884497</v>
       </c>
     </row>
     <row r="6">
@@ -1091,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Virtu Financial, Inc. (NasdaqGS:VIRT)</t>
+          <t>The Charles Schwab Corporation (NYSE:SCHW)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1100,100 +1109,106 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.302</v>
+        <v>0.155</v>
+      </c>
+      <c r="E6">
+        <v>0.136</v>
+      </c>
+      <c r="F6">
+        <v>0.08470000000000001</v>
       </c>
       <c r="G6">
-        <v>0.01766182535413304</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.004756425931517675</v>
+        <v>0.00243749911715496</v>
       </c>
       <c r="J6">
-        <v>0.003928637787274241</v>
+        <v>0.001876204023613237</v>
       </c>
       <c r="K6">
-        <v>341.5</v>
+        <v>5990</v>
       </c>
       <c r="L6">
-        <v>0.1530840953917877</v>
+        <v>0.3006877164800964</v>
       </c>
       <c r="M6">
-        <v>657.6</v>
+        <v>6587</v>
       </c>
       <c r="N6">
-        <v>0.3228435367470175</v>
+        <v>0.05250864913986895</v>
       </c>
       <c r="O6">
-        <v>1.925622254758419</v>
+        <v>1.099666110183639</v>
       </c>
       <c r="P6">
-        <v>105.9</v>
+        <v>1805</v>
       </c>
       <c r="Q6">
-        <v>0.05199077028818302</v>
+        <v>0.01438866125663632</v>
       </c>
       <c r="R6">
-        <v>0.3101024890190337</v>
+        <v>0.3013355592654424</v>
       </c>
       <c r="S6">
-        <v>551.7</v>
+        <v>4782</v>
       </c>
       <c r="T6">
-        <v>0.8389598540145986</v>
+        <v>0.72597540610293</v>
       </c>
       <c r="U6">
-        <v>836.3</v>
+        <v>33251</v>
       </c>
       <c r="V6">
-        <v>0.4105748932200893</v>
+        <v>0.2650622578639414</v>
       </c>
       <c r="W6">
-        <v>0.2299198815054198</v>
+        <v>0.2239754711337122</v>
       </c>
       <c r="X6">
-        <v>0.1025838905167693</v>
+        <v>0.06416218671992294</v>
       </c>
       <c r="Y6">
-        <v>0.1273359909886504</v>
+        <v>0.1598132844137893</v>
       </c>
       <c r="Z6">
-        <v>0.6346972089230191</v>
+        <v>3.348510186707352</v>
       </c>
       <c r="AA6">
-        <v>0.002493495438452467</v>
+        <v>0.006282488285410244</v>
       </c>
       <c r="AB6">
-        <v>0.05929367322665077</v>
+        <v>0.05476201687270967</v>
       </c>
       <c r="AC6">
-        <v>-0.05680017778819831</v>
+        <v>-0.04847952858729943</v>
       </c>
       <c r="AD6">
-        <v>3422.1</v>
+        <v>70031</v>
       </c>
       <c r="AE6">
-        <v>279.9468251598518</v>
+        <v>917.2129004357803</v>
       </c>
       <c r="AF6">
-        <v>3702.046825159852</v>
+        <v>70948.21290043578</v>
       </c>
       <c r="AG6">
-        <v>2865.746825159852</v>
+        <v>37697.21290043578</v>
       </c>
       <c r="AH6">
-        <v>0.6450742510681367</v>
+        <v>0.361254091210945</v>
       </c>
       <c r="AI6">
-        <v>0.6887597115995193</v>
+        <v>0.6525040832692501</v>
       </c>
       <c r="AJ6">
-        <v>0.5845305459192267</v>
+        <v>0.2310682266840111</v>
       </c>
       <c r="AK6">
-        <v>0.6314099632678336</v>
+        <v>0.4994251079425638</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1202,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>51.38288288288289</v>
+        <v>301.8577586206897</v>
       </c>
       <c r="AP6">
-        <v>43.02923160900679</v>
+        <v>162.4879866398094</v>
       </c>
     </row>
     <row r="7">
@@ -1225,13 +1240,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.148</v>
+        <v>0.171</v>
       </c>
       <c r="E7">
-        <v>0.306</v>
+        <v>0.36</v>
       </c>
       <c r="F7">
-        <v>0.225</v>
+        <v>0.211</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1240,91 +1255,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.0005020384678623753</v>
+        <v>0.0007849145550840699</v>
       </c>
       <c r="J7">
-        <v>0.0004617440605131359</v>
+        <v>0.0007219506410800452</v>
       </c>
       <c r="K7">
-        <v>311</v>
+        <v>576</v>
       </c>
       <c r="L7">
-        <v>0.10997171145686</v>
+        <v>0.1359452442766108</v>
       </c>
       <c r="M7">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="N7">
-        <v>0.008061482237867469</v>
+        <v>0.008453942918977411</v>
       </c>
       <c r="O7">
-        <v>0.1929260450160772</v>
+        <v>0.1302083333333333</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q7">
-        <v>0.005374321491911646</v>
+        <v>0.004621488795707651</v>
       </c>
       <c r="R7">
-        <v>0.1286173633440514</v>
+        <v>0.07118055555555555</v>
       </c>
       <c r="S7">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="T7">
-        <v>0.3333333333333333</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="U7">
-        <v>3184</v>
+        <v>3824</v>
       </c>
       <c r="V7">
-        <v>0.427795990756167</v>
+        <v>0.4310383696289283</v>
       </c>
       <c r="W7">
-        <v>0.1334191334191334</v>
+        <v>0.2151662308554352</v>
       </c>
       <c r="X7">
-        <v>0.09267176364362968</v>
+        <v>0.07267564170493312</v>
       </c>
       <c r="Y7">
-        <v>0.04074736977550374</v>
+        <v>0.1424905891505021</v>
       </c>
       <c r="Z7">
-        <v>0.2758243692626253</v>
+        <v>0.4511588069520605</v>
       </c>
       <c r="AA7">
-        <v>0.0001273602642517992</v>
+        <v>0.0003257143899079484</v>
       </c>
       <c r="AB7">
-        <v>0.06004566921106316</v>
+        <v>0.05143713720376826</v>
       </c>
       <c r="AC7">
-        <v>-0.05991830894681136</v>
+        <v>-0.05111142281386031</v>
       </c>
       <c r="AD7">
-        <v>9765</v>
+        <v>10539</v>
       </c>
       <c r="AE7">
-        <v>117.901176064426</v>
+        <v>133.371585150544</v>
       </c>
       <c r="AF7">
-        <v>9882.901176064426</v>
+        <v>10672.37158515054</v>
       </c>
       <c r="AG7">
-        <v>6698.901176064426</v>
+        <v>6848.371585150544</v>
       </c>
       <c r="AH7">
-        <v>0.5704185403888715</v>
+        <v>0.5460697452742606</v>
       </c>
       <c r="AI7">
-        <v>0.4755303935836696</v>
+        <v>0.445864217439346</v>
       </c>
       <c r="AJ7">
-        <v>0.473698396866331</v>
+        <v>0.4356478348612078</v>
       </c>
       <c r="AK7">
-        <v>0.3806431497652443</v>
+        <v>0.3405054225532937</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1333,10 +1348,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>390.6</v>
+        <v>351.3</v>
       </c>
       <c r="AP7">
-        <v>267.956047042577</v>
+        <v>228.2790528383515</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Raymond James Financial, Inc. (NYSE:RJF)</t>
+          <t>Siebert Financial Corp. (NasdaqCM:SIEB)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,10 +1371,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.111</v>
+        <v>0.18</v>
       </c>
       <c r="E8">
-        <v>0.189</v>
+        <v>-0.0435</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1368,91 +1383,88 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.002446273747595416</v>
+        <v>0.01199663990300809</v>
       </c>
       <c r="J8">
-        <v>0.00182563159501557</v>
+        <v>0.007526193901415451</v>
       </c>
       <c r="K8">
-        <v>1509</v>
+        <v>5.88</v>
       </c>
       <c r="L8">
-        <v>0.1397092861772058</v>
+        <v>0.09018404907975459</v>
       </c>
       <c r="M8">
-        <v>508.536</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.02212998542178899</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.3370019880715706</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>292.536</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.01273030309623795</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.1938608349900597</v>
+        <v>-0</v>
       </c>
       <c r="S8">
-        <v>216</v>
-      </c>
-      <c r="T8">
-        <v>0.4247486903582047</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>6178</v>
+        <v>4.93</v>
       </c>
       <c r="V8">
-        <v>0.268848321329881</v>
+        <v>0.07413533834586465</v>
       </c>
       <c r="W8">
-        <v>0.1830200121285628</v>
+        <v>0.113953488372093</v>
       </c>
       <c r="X8">
-        <v>0.07000044424286712</v>
+        <v>0.1399671755423484</v>
       </c>
       <c r="Y8">
-        <v>0.1130195678856956</v>
+        <v>-0.02601368717025537</v>
       </c>
       <c r="Z8">
-        <v>2.549276139880989</v>
+        <v>0.09635575793489515</v>
       </c>
       <c r="AA8">
-        <v>0.004654039065386066</v>
+        <v>0.0007251921177358713</v>
       </c>
       <c r="AB8">
-        <v>0.06529690605498828</v>
+        <v>0.0522032942106766</v>
       </c>
       <c r="AC8">
-        <v>-0.06064286698960222</v>
+        <v>-0.05147810209294073</v>
       </c>
       <c r="AD8">
-        <v>4325</v>
+        <v>412.7</v>
       </c>
       <c r="AE8">
-        <v>452.8889862611096</v>
+        <v>2.339095391619364</v>
       </c>
       <c r="AF8">
-        <v>4777.888986261109</v>
+        <v>415.0390953916194</v>
       </c>
       <c r="AG8">
-        <v>-1400.111013738891</v>
+        <v>410.1090953916193</v>
       </c>
       <c r="AH8">
-        <v>0.1721303465764013</v>
+        <v>0.8619011402471531</v>
       </c>
       <c r="AI8">
-        <v>0.3362368974789762</v>
+        <v>0.8528683768360609</v>
       </c>
       <c r="AJ8">
-        <v>-0.06488186549815174</v>
+        <v>0.8604726585308692</v>
       </c>
       <c r="AK8">
-        <v>-0.1743190196146685</v>
+        <v>0.8513625740411011</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1461,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>36.96581196581197</v>
+        <v>330.16</v>
       </c>
       <c r="AP8">
-        <v>-11.9667608011871</v>
+        <v>328.0872763132955</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1496,7 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.232</v>
+        <v>0.291</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1493,103 +1505,103 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.003327310374051481</v>
+        <v>-0.001336698314891985</v>
       </c>
       <c r="J9">
-        <v>0.003327310374051481</v>
+        <v>-0.001336698314891985</v>
       </c>
       <c r="K9">
-        <v>-38.2</v>
+        <v>-67.7</v>
       </c>
       <c r="L9">
-        <v>-0.04594659610295887</v>
+        <v>-0.04945576740448535</v>
       </c>
       <c r="M9">
-        <v>123.84</v>
+        <v>212.4</v>
       </c>
       <c r="N9">
-        <v>0.126690537084399</v>
+        <v>0.3308926624084748</v>
       </c>
       <c r="O9">
-        <v>-3.241884816753926</v>
+        <v>-3.137370753323486</v>
       </c>
       <c r="P9">
-        <v>118</v>
+        <v>140.1</v>
       </c>
       <c r="Q9">
-        <v>0.1207161125319693</v>
+        <v>0.2182582956846861</v>
       </c>
       <c r="R9">
-        <v>-3.089005235602094</v>
+        <v>-2.069423929098966</v>
       </c>
       <c r="S9">
-        <v>5.840000000000003</v>
+        <v>72.29999999999998</v>
       </c>
       <c r="T9">
-        <v>0.04715762273901811</v>
+        <v>0.3403954802259886</v>
       </c>
       <c r="U9">
-        <v>231.8</v>
+        <v>252.3</v>
       </c>
       <c r="V9">
-        <v>0.2371355498721228</v>
+        <v>0.3930518772394454</v>
       </c>
       <c r="W9">
-        <v>-0.05405405405405406</v>
+        <v>-0.1318146417445483</v>
       </c>
       <c r="X9">
-        <v>0.161572298490447</v>
+        <v>0.1657397862424738</v>
       </c>
       <c r="Y9">
-        <v>-0.2156263525445011</v>
+        <v>-0.2975544279870221</v>
       </c>
       <c r="Z9">
-        <v>0.2598800386984869</v>
+        <v>0.3029177135328405</v>
       </c>
       <c r="AA9">
-        <v>0.0008647015487703758</v>
+        <v>-0.000404909597230281</v>
       </c>
       <c r="AB9">
-        <v>0.06224343342801249</v>
+        <v>0.0520547869920052</v>
       </c>
       <c r="AC9">
-        <v>-0.06137873187924211</v>
+        <v>-0.05245969658923548</v>
       </c>
       <c r="AD9">
-        <v>4558.3</v>
+        <v>5136.7</v>
       </c>
       <c r="AE9">
-        <v>66.668370775068</v>
+        <v>108.1490316162782</v>
       </c>
       <c r="AF9">
-        <v>4624.968370775068</v>
+        <v>5244.849031616278</v>
       </c>
       <c r="AG9">
-        <v>4393.168370775068</v>
+        <v>4992.549031616278</v>
       </c>
       <c r="AH9">
-        <v>0.8255233344825169</v>
+        <v>0.8909584905773097</v>
       </c>
       <c r="AI9">
-        <v>0.8594249844320753</v>
+        <v>0.9181276173891025</v>
       </c>
       <c r="AJ9">
-        <v>0.8179928581479455</v>
+        <v>0.886075817458257</v>
       </c>
       <c r="AK9">
-        <v>0.8530973364628254</v>
+        <v>0.9143445661009427</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1.31</v>
+        <v>-50.2</v>
       </c>
       <c r="AN9">
-        <v>283.1242236024844</v>
+        <v>259.4292929292929</v>
       </c>
       <c r="AP9">
-        <v>272.8676006692589</v>
+        <v>252.1489409907211</v>
       </c>
       <c r="AQ9">
         <v>-0</v>
@@ -1612,13 +1624,13 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0808</v>
+        <v>0.0539</v>
       </c>
       <c r="E10">
-        <v>0.119</v>
+        <v>0.0452</v>
       </c>
       <c r="F10">
-        <v>0.03</v>
+        <v>0.0428</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1627,91 +1639,91 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>-0.0008835960393987392</v>
+        <v>-0.000803162578066371</v>
       </c>
       <c r="J10">
-        <v>-0.0006897171878093007</v>
+        <v>-0.0006390762900368255</v>
       </c>
       <c r="K10">
-        <v>12489</v>
+        <v>9806</v>
       </c>
       <c r="L10">
-        <v>0.2260493402595522</v>
+        <v>0.1837017609591607</v>
       </c>
       <c r="M10">
-        <v>16958.795</v>
+        <v>11915.225</v>
       </c>
       <c r="N10">
-        <v>0.1180209418545497</v>
+        <v>0.07785067588007498</v>
       </c>
       <c r="O10">
-        <v>1.357898550724637</v>
+        <v>1.215095349785845</v>
       </c>
       <c r="P10">
-        <v>4985.795</v>
+        <v>5334.224999999999</v>
       </c>
       <c r="Q10">
-        <v>0.03469752549008964</v>
+        <v>0.03485230212156237</v>
       </c>
       <c r="R10">
-        <v>0.3992149091200256</v>
+        <v>0.5439756271670405</v>
       </c>
       <c r="S10">
-        <v>11973</v>
+        <v>6580.999999999999</v>
       </c>
       <c r="T10">
-        <v>0.7060053500263432</v>
+        <v>0.552318567211278</v>
       </c>
       <c r="U10">
-        <v>111696</v>
+        <v>108401</v>
       </c>
       <c r="V10">
-        <v>0.777323337028709</v>
+        <v>0.7082611630142115</v>
       </c>
       <c r="W10">
-        <v>0.1272401251107964</v>
+        <v>0.1062854293796946</v>
       </c>
       <c r="X10">
-        <v>0.115703982564252</v>
+        <v>0.0900976002183671</v>
       </c>
       <c r="Y10">
-        <v>0.01153614254654441</v>
+        <v>0.01618782916132747</v>
       </c>
       <c r="Z10">
-        <v>0.1717129488538522</v>
+        <v>0.1633543076376621</v>
       </c>
       <c r="AA10">
-        <v>-0.0001184333721939212</v>
+        <v>-0.0001043958648866113</v>
       </c>
       <c r="AB10">
-        <v>0.06273370426669804</v>
+        <v>0.05295465627566903</v>
       </c>
       <c r="AC10">
-        <v>-0.06285213763889196</v>
+        <v>-0.05305905214055564</v>
       </c>
       <c r="AD10">
-        <v>349616</v>
+        <v>379197</v>
       </c>
       <c r="AE10">
-        <v>4674.088987903705</v>
+        <v>4564.364092085914</v>
       </c>
       <c r="AF10">
-        <v>354290.0889879037</v>
+        <v>383761.3640920859</v>
       </c>
       <c r="AG10">
-        <v>242594.0889879037</v>
+        <v>275360.3640920859</v>
       </c>
       <c r="AH10">
-        <v>0.7114498979533014</v>
+        <v>0.714887473554054</v>
       </c>
       <c r="AI10">
-        <v>0.7763065783176015</v>
+        <v>0.7930275012079476</v>
       </c>
       <c r="AJ10">
-        <v>0.6280148446639279</v>
+        <v>0.6427456216207887</v>
       </c>
       <c r="AK10">
-        <v>0.7038177872324258</v>
+        <v>0.7332806872384039</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1720,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>394.6004514672686</v>
+        <v>435.8586206896552</v>
       </c>
       <c r="AP10">
-        <v>273.8082268486498</v>
+        <v>316.5061656230873</v>
       </c>
     </row>
     <row r="11">
@@ -1734,7 +1746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Siebert Financial Corp. (NasdaqCM:SIEB)</t>
+          <t>The Goldman Sachs Group, Inc. (NYSE:GS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1743,7 +1755,13 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.363</v>
+        <v>0.04190000000000001</v>
+      </c>
+      <c r="E11">
+        <v>0.055</v>
+      </c>
+      <c r="F11">
+        <v>0.0771</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1752,88 +1770,91 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.01537165889890015</v>
+        <v>-0.002497536867496416</v>
       </c>
       <c r="J11">
-        <v>0.01537165889890015</v>
+        <v>-0.001953639922113522</v>
       </c>
       <c r="K11">
-        <v>1.28</v>
+        <v>7834</v>
       </c>
       <c r="L11">
-        <v>0.0252465483234714</v>
+        <v>0.1776175577019</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>11181.02</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.08439231752769673</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>1.427242787847843</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>3537.02</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.02669678749718844</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.4514960428899668</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>7644</v>
+      </c>
+      <c r="T11">
+        <v>0.6836585570904979</v>
       </c>
       <c r="U11">
-        <v>4.49</v>
+        <v>239879</v>
       </c>
       <c r="V11">
-        <v>0.1018140589569161</v>
+        <v>1.810563323938814</v>
       </c>
       <c r="W11">
-        <v>0.03004694835680751</v>
+        <v>0.07214491605809167</v>
       </c>
       <c r="X11">
-        <v>0.3559046855725448</v>
+        <v>0.1217680883861978</v>
       </c>
       <c r="Y11">
-        <v>-0.3258577372157373</v>
+        <v>-0.04962317232810615</v>
       </c>
       <c r="Z11">
-        <v>0.06051178761222373</v>
+        <v>0.106893114996199</v>
       </c>
       <c r="AA11">
-        <v>0.0009301665585377947</v>
+        <v>-0.000208830656855646</v>
       </c>
       <c r="AB11">
-        <v>0.06443799709247988</v>
+        <v>0.0531971967430295</v>
       </c>
       <c r="AC11">
-        <v>-0.06350783053394209</v>
+        <v>-0.05340602739988515</v>
       </c>
       <c r="AD11">
-        <v>629.2</v>
+        <v>644183</v>
       </c>
       <c r="AE11">
-        <v>2.803284469128813</v>
+        <v>2175.781805388985</v>
       </c>
       <c r="AF11">
-        <v>632.0032844691289</v>
+        <v>646358.781805389</v>
       </c>
       <c r="AG11">
-        <v>627.5132844691288</v>
+        <v>406479.781805389</v>
       </c>
       <c r="AH11">
-        <v>0.9347732794485283</v>
+        <v>0.8298914484466933</v>
       </c>
       <c r="AI11">
-        <v>0.9210146596107726</v>
+        <v>0.8459011190532931</v>
       </c>
       <c r="AJ11">
-        <v>0.9343372130662089</v>
+        <v>0.7541811273674324</v>
       </c>
       <c r="AK11">
-        <v>0.9204944347795609</v>
+        <v>0.7753877148698846</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1842,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>469.5522388059701</v>
+        <v>1982.101538461538</v>
       </c>
       <c r="AP11">
-        <v>468.2934958724842</v>
+        <v>1250.707020939658</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1877,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc. (NYSE:GS)</t>
+          <t>Piper Sandler Companies (NYSE:PIPR)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1865,13 +1886,7 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.07870000000000001</v>
-      </c>
-      <c r="E12">
-        <v>0.101</v>
-      </c>
-      <c r="F12">
-        <v>-0.04769999999999999</v>
+        <v>0.107</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1880,91 +1895,91 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>-0.003137245700963243</v>
+        <v>0.001244242086281617</v>
       </c>
       <c r="J12">
-        <v>-0.002562487360718461</v>
+        <v>0.001134548199581726</v>
       </c>
       <c r="K12">
-        <v>13870</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L12">
-        <v>0.2930859606119516</v>
+        <v>0.05650252525252525</v>
       </c>
       <c r="M12">
-        <v>7078.05</v>
+        <v>122.1</v>
       </c>
       <c r="N12">
-        <v>0.05868343750854999</v>
+        <v>0.04617304492512479</v>
       </c>
       <c r="O12">
-        <v>0.5103136265320837</v>
+        <v>1.705307262569832</v>
       </c>
       <c r="P12">
-        <v>2986.05</v>
+        <v>52.9</v>
       </c>
       <c r="Q12">
-        <v>0.0247570557671118</v>
+        <v>0.02000453789139313</v>
       </c>
       <c r="R12">
-        <v>0.2152883922134103</v>
+        <v>0.7388268156424581</v>
       </c>
       <c r="S12">
-        <v>4092</v>
+        <v>69.19999999999999</v>
       </c>
       <c r="T12">
-        <v>0.5781253311293365</v>
+        <v>0.5667485667485667</v>
       </c>
       <c r="U12">
-        <v>284251</v>
+        <v>51.9</v>
       </c>
       <c r="V12">
-        <v>2.356697931668022</v>
+        <v>0.01962638027529874</v>
       </c>
       <c r="W12">
-        <v>0.1439632981815162</v>
+        <v>0.07156421789105447</v>
       </c>
       <c r="X12">
-        <v>0.163801466915972</v>
+        <v>0.05784837179941554</v>
       </c>
       <c r="Y12">
-        <v>-0.01983816873445579</v>
+        <v>0.01371584609163893</v>
       </c>
       <c r="Z12">
-        <v>0.1015008643350825</v>
+        <v>1.743493758240901</v>
       </c>
       <c r="AA12">
-        <v>-0.0002600946819606482</v>
+        <v>0.001978077704394191</v>
       </c>
       <c r="AB12">
-        <v>0.06341035532459104</v>
+        <v>0.05580380421433469</v>
       </c>
       <c r="AC12">
-        <v>-0.06367045000655168</v>
+        <v>-0.0538257265099405</v>
       </c>
       <c r="AD12">
-        <v>581691</v>
+        <v>127.4</v>
       </c>
       <c r="AE12">
-        <v>2267.335077761923</v>
+        <v>118.1164821413197</v>
       </c>
       <c r="AF12">
-        <v>583958.3350777619</v>
+        <v>245.5164821413197</v>
       </c>
       <c r="AG12">
-        <v>299707.3350777619</v>
+        <v>193.6164821413197</v>
       </c>
       <c r="AH12">
-        <v>0.828812349170759</v>
+        <v>0.0849562551923304</v>
       </c>
       <c r="AI12">
-        <v>0.8294010515457423</v>
+        <v>0.1676777205664753</v>
       </c>
       <c r="AJ12">
-        <v>0.7130431856807738</v>
+        <v>0.06822246571141601</v>
       </c>
       <c r="AK12">
-        <v>0.7138925777134415</v>
+        <v>0.1370914271621068</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1973,10 +1988,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>1907.183606557377</v>
+        <v>5.055555555555556</v>
       </c>
       <c r="AP12">
-        <v>982.6470002549571</v>
+        <v>7.683193735766654</v>
       </c>
     </row>
     <row r="13">
@@ -1987,7 +2002,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation (NYSE:SCHW)</t>
+          <t>Raymond James Financial, Inc. (NYSE:RJF)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1996,13 +2011,13 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.19</v>
+        <v>0.0973</v>
       </c>
       <c r="E13">
-        <v>0.244</v>
+        <v>0.152</v>
       </c>
       <c r="F13">
-        <v>0.228</v>
+        <v>0.126</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2011,91 +2026,91 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.001214553696770631</v>
+        <v>0.001186142532658479</v>
       </c>
       <c r="J13">
-        <v>0.0009364452932663608</v>
+        <v>0.0009046938001285503</v>
       </c>
       <c r="K13">
-        <v>6795</v>
+        <v>1739</v>
       </c>
       <c r="L13">
-        <v>0.3409946304009635</v>
+        <v>0.1510860121633362</v>
       </c>
       <c r="M13">
-        <v>2976</v>
+        <v>1212.448</v>
       </c>
       <c r="N13">
-        <v>0.01914753575203941</v>
+        <v>0.05212655365288459</v>
       </c>
       <c r="O13">
-        <v>0.4379690949227373</v>
+        <v>0.6972098907418055</v>
       </c>
       <c r="P13">
-        <v>1521</v>
+        <v>350.448</v>
       </c>
       <c r="Q13">
-        <v>0.009786089341012078</v>
+        <v>0.01506674634668547</v>
       </c>
       <c r="R13">
-        <v>0.223841059602649</v>
+        <v>0.2015227142035653</v>
       </c>
       <c r="S13">
-        <v>1455</v>
+        <v>861.9999999999999</v>
       </c>
       <c r="T13">
-        <v>0.4889112903225806</v>
+        <v>0.7109583256354087</v>
       </c>
       <c r="U13">
-        <v>46486</v>
+        <v>9313</v>
       </c>
       <c r="V13">
-        <v>0.2990901703525887</v>
+        <v>0.4003920944810122</v>
       </c>
       <c r="W13">
-        <v>0.1430887803234501</v>
+        <v>0.1862283144142215</v>
       </c>
       <c r="X13">
-        <v>0.06934219589242689</v>
+        <v>0.05918815680524672</v>
       </c>
       <c r="Y13">
-        <v>0.07374658443102323</v>
+        <v>0.1270401576089747</v>
       </c>
       <c r="Z13">
-        <v>0.455120717331752</v>
+        <v>1.71541733260431</v>
       </c>
       <c r="AA13">
-        <v>0.000426195653613329</v>
+        <v>0.001551927425440174</v>
       </c>
       <c r="AB13">
-        <v>0.06492620862649429</v>
+        <v>0.05578095239610793</v>
       </c>
       <c r="AC13">
-        <v>-0.06450001297288095</v>
+        <v>-0.05422902497066776</v>
       </c>
       <c r="AD13">
-        <v>26428</v>
+        <v>3966</v>
       </c>
       <c r="AE13">
-        <v>833.9879424222581</v>
+        <v>526.7374972455045</v>
       </c>
       <c r="AF13">
-        <v>27261.98794242226</v>
+        <v>4492.737497245505</v>
       </c>
       <c r="AG13">
-        <v>-19224.01205757774</v>
+        <v>-4820.262502754495</v>
       </c>
       <c r="AH13">
-        <v>0.1492281033143174</v>
+        <v>0.161886230630784</v>
       </c>
       <c r="AI13">
-        <v>0.4239614489894778</v>
+        <v>0.3060502613271197</v>
       </c>
       <c r="AJ13">
-        <v>-0.1411447500595925</v>
+        <v>-0.2614104960346296</v>
       </c>
       <c r="AK13">
-        <v>-1.078970930423394</v>
+        <v>-0.8981737052033029</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2104,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>138.3664921465969</v>
+        <v>33.32773109243698</v>
       </c>
       <c r="AP13">
-        <v>-100.6492777883651</v>
+        <v>-40.50640758617223</v>
       </c>
     </row>
     <row r="14">
@@ -2133,91 +2148,91 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>-0.003364945190256922</v>
+        <v>-0.004028241465475514</v>
       </c>
       <c r="J14">
-        <v>-0.002548320225394539</v>
+        <v>-0.002897845230873945</v>
       </c>
       <c r="K14">
-        <v>968.8</v>
+        <v>346</v>
       </c>
       <c r="L14">
-        <v>0.1550377672513122</v>
+        <v>0.07207582543485054</v>
       </c>
       <c r="M14">
-        <v>1048.9</v>
+        <v>538.78</v>
       </c>
       <c r="N14">
-        <v>0.1336212387576754</v>
+        <v>0.06336053813768611</v>
       </c>
       <c r="O14">
-        <v>1.082679603633361</v>
+        <v>1.557167630057803</v>
       </c>
       <c r="P14">
-        <v>222.8</v>
+        <v>252.48</v>
       </c>
       <c r="Q14">
-        <v>0.02838288873601875</v>
+        <v>0.02969165275066444</v>
       </c>
       <c r="R14">
-        <v>0.2299752270850537</v>
+        <v>0.7297109826589595</v>
       </c>
       <c r="S14">
-        <v>826.1000000000001</v>
+        <v>286.3</v>
       </c>
       <c r="T14">
-        <v>0.7875869959004672</v>
+        <v>0.5313857233007906</v>
       </c>
       <c r="U14">
-        <v>9477.5</v>
+        <v>8817.4</v>
       </c>
       <c r="V14">
-        <v>1.207355601416596</v>
+        <v>1.036926405908225</v>
       </c>
       <c r="W14">
-        <v>0.09331625232375576</v>
+        <v>0.03361671119747389</v>
       </c>
       <c r="X14">
-        <v>0.1287240081767549</v>
+        <v>0.09813103119678086</v>
       </c>
       <c r="Y14">
-        <v>-0.0354077558529991</v>
+        <v>-0.06451431999930697</v>
       </c>
       <c r="Z14">
-        <v>0.2444849799501619</v>
+        <v>0.2033353015535006</v>
       </c>
       <c r="AA14">
-        <v>-0.0006230260192121761</v>
+        <v>-0.0005892342338751272</v>
       </c>
       <c r="AB14">
-        <v>0.06469593935343568</v>
+        <v>0.05425592143025389</v>
       </c>
       <c r="AC14">
-        <v>-0.06531896537264785</v>
+        <v>-0.05484515566412902</v>
       </c>
       <c r="AD14">
-        <v>23921.1</v>
+        <v>25955.2</v>
       </c>
       <c r="AE14">
-        <v>482.1343475243873</v>
+        <v>480.687865775076</v>
       </c>
       <c r="AF14">
-        <v>24403.23434752439</v>
+        <v>26435.88786577508</v>
       </c>
       <c r="AG14">
-        <v>14925.73434752439</v>
+        <v>17618.48786577507</v>
       </c>
       <c r="AH14">
-        <v>0.7566182482113495</v>
+        <v>0.7566235456009525</v>
       </c>
       <c r="AI14">
-        <v>0.6991923194086054</v>
+        <v>0.7302451487161812</v>
       </c>
       <c r="AJ14">
-        <v>0.6553406879407313</v>
+        <v>0.6744722263684025</v>
       </c>
       <c r="AK14">
-        <v>0.5870602837207015</v>
+        <v>0.6433864911178597</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2226,10 +2241,10 @@
         <v>0</v>
       </c>
       <c r="AN14">
-        <v>317.2559681697612</v>
+        <v>337.9583333333334</v>
       </c>
       <c r="AP14">
-        <v>197.9540364393155</v>
+        <v>229.407394085613</v>
       </c>
     </row>
     <row r="15">
@@ -2240,7 +2255,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Armada Mercantile Ltd. (OTCPK:AAMT.F)</t>
+          <t>BGC Group, Inc. (NasdaqGS:BGC)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2248,101 +2263,116 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D15">
+        <v>0.209</v>
+      </c>
+      <c r="E15">
+        <v>-0.278</v>
+      </c>
       <c r="G15">
-        <v>0</v>
+        <v>0.02230641976626287</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>0.0003001567477364622</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.0002309235124921395</v>
       </c>
       <c r="K15">
-        <v>0.117</v>
+        <v>18.5</v>
       </c>
       <c r="L15">
-        <v>0.420863309352518</v>
+        <v>0.009872458508991941</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>183.3</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.05115967512350331</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>9.908108108108109</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>16</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.004465656311926094</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.8648648648648649</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>167.3</v>
+      </c>
+      <c r="T15">
+        <v>0.9127114020731042</v>
       </c>
       <c r="U15">
-        <v>0.216</v>
+        <v>559.6</v>
       </c>
       <c r="V15">
-        <v>0.04705882352941176</v>
+        <v>0.1561863295096151</v>
       </c>
       <c r="W15">
-        <v>0.02702078521939954</v>
+        <v>0.02837423312883436</v>
       </c>
       <c r="X15">
-        <v>0.06581346300979396</v>
+        <v>0.06168998227236205</v>
       </c>
       <c r="Y15">
-        <v>-0.03879267779039442</v>
+        <v>-0.0333157491435277</v>
       </c>
       <c r="Z15">
-        <v>0.06553512494106555</v>
+        <v>2.028716023642328</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>0.0004684782300285727</v>
       </c>
       <c r="AB15">
-        <v>0.06578983573774848</v>
+        <v>0.05603007491493808</v>
       </c>
       <c r="AC15">
-        <v>-0.06578983573774848</v>
+        <v>-0.05556159668490951</v>
       </c>
       <c r="AD15">
-        <v>0.005</v>
+        <v>1188.5</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>174.6876813520832</v>
       </c>
       <c r="AF15">
-        <v>0.005</v>
+        <v>1363.187681352083</v>
       </c>
       <c r="AG15">
-        <v>-0.211</v>
+        <v>803.5876813520832</v>
       </c>
       <c r="AH15">
-        <v>0.001088139281828074</v>
+        <v>0.2756092833719107</v>
       </c>
       <c r="AI15">
-        <v>0.001158748551564311</v>
+        <v>0.6143563249318786</v>
       </c>
       <c r="AJ15">
-        <v>-0.04818451701301667</v>
+        <v>0.1831961559514483</v>
       </c>
       <c r="AK15">
-        <v>-0.05147596974871921</v>
+        <v>0.4842967801082411</v>
       </c>
       <c r="AL15">
         <v>0</v>
       </c>
       <c r="AM15">
         <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>33.47887323943662</v>
+      </c>
+      <c r="AP15">
+        <v>22.63627271414319</v>
       </c>
     </row>
     <row r="16">
@@ -2353,7 +2383,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Morgan Group Holding Co. (OTCPK:MGHL)</t>
+          <t>Robinhood Markets, Inc. (NasdaqGS:HOOD)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2361,32 +2391,35 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="F16">
+        <v>0.03</v>
+      </c>
       <c r="G16">
-        <v>0</v>
+        <v>0.4441939120631341</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>-0.0004280728945144812</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>-0.0004280728945144812</v>
       </c>
       <c r="K16">
-        <v>-0.828</v>
+        <v>-737</v>
       </c>
       <c r="L16">
-        <v>-0.3136363636363636</v>
+        <v>-0.415445321307779</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>620</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.05627513093044575</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>-0.841248303934871</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2398,64 +2431,73 @@
         <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>620</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
       </c>
       <c r="U16">
-        <v>2.39</v>
+        <v>4889</v>
       </c>
       <c r="V16">
-        <v>1.991666666666667</v>
+        <v>0.4437566372886279</v>
       </c>
       <c r="W16">
-        <v>-0.2778523489932886</v>
+        <v>-0.1059821685360943</v>
       </c>
       <c r="X16">
-        <v>0.06579141120325535</v>
+        <v>0.06072867842560738</v>
       </c>
       <c r="Y16">
-        <v>-0.343643760196544</v>
+        <v>-0.1667108469617017</v>
       </c>
       <c r="Z16">
-        <v>52.80000000000019</v>
+        <v>0.7906241049445051</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>-0.0003384447490765153</v>
       </c>
       <c r="AB16">
-        <v>0.06579141120325535</v>
+        <v>0.05540337546155572</v>
       </c>
       <c r="AC16">
-        <v>-0.06579141120325535</v>
+        <v>-0.05574182021063223</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>3245</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>153.7970065743434</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>3398.797006574343</v>
       </c>
       <c r="AG16">
-        <v>-2.39</v>
+        <v>-1490.202993425657</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.2357640216366712</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.3408067971637007</v>
       </c>
       <c r="AJ16">
-        <v>2.008403361344538</v>
+        <v>-0.1564173212886691</v>
       </c>
       <c r="AK16">
-        <v>9.958333333333325</v>
+        <v>-0.2931279497388533</v>
       </c>
       <c r="AL16">
         <v>0</v>
       </c>
       <c r="AM16">
         <v>0</v>
+      </c>
+      <c r="AN16">
+        <v>108.1666666666667</v>
+      </c>
+      <c r="AP16">
+        <v>-49.67343311418855</v>
       </c>
     </row>
     <row r="17">
@@ -2466,7 +2508,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BGC Partners, Inc. (NasdaqGS:BGCP)</t>
+          <t>Armada Mercantile Ltd. (OTCPK:AAMT.F)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2475,115 +2517,106 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.109</v>
+        <v>0.292</v>
       </c>
       <c r="E17">
-        <v>-0.106</v>
+        <v>-0.07400000000000001</v>
       </c>
       <c r="G17">
-        <v>0.02078128548716784</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.0007504389977988244</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>-0.000539074075686992</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>122.9</v>
+        <v>0.092</v>
       </c>
       <c r="L17">
-        <v>0.06978196684079037</v>
+        <v>0.359375</v>
       </c>
       <c r="M17">
-        <v>232.4</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.1665114279572974</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>1.890968266883645</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>14.8</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.01060399799383822</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.1204231082180635</v>
+        <v>-0</v>
       </c>
       <c r="S17">
-        <v>217.6</v>
-      </c>
-      <c r="T17">
-        <v>0.9363166953528399</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>473.3</v>
+        <v>0.043</v>
       </c>
       <c r="V17">
-        <v>0.3391129898975425</v>
+        <v>0.007637655417406749</v>
       </c>
       <c r="W17">
-        <v>0.1948010778253289</v>
+        <v>0.0213953488372093</v>
       </c>
       <c r="X17">
-        <v>0.08356502001618692</v>
+        <v>0.05662018730135125</v>
       </c>
       <c r="Y17">
-        <v>0.111236057809142</v>
+        <v>-0.03522483846414195</v>
       </c>
       <c r="Z17">
-        <v>1.442414359565002</v>
+        <v>0.06260699437515285</v>
       </c>
       <c r="AA17">
-        <v>-0.0007775681876401481</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.06585085446916708</v>
+        <v>0.05660556690445565</v>
       </c>
       <c r="AC17">
-        <v>-0.06662842265680723</v>
+        <v>-0.05660556690445565</v>
       </c>
       <c r="AD17">
-        <v>1057.3</v>
+        <v>0.005</v>
       </c>
       <c r="AE17">
-        <v>168.1083658146164</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1225.408365814616</v>
+        <v>0.005</v>
       </c>
       <c r="AG17">
-        <v>752.1083658146165</v>
+        <v>-0.038</v>
       </c>
       <c r="AH17">
-        <v>0.4675153388531385</v>
+        <v>0.0008873114463176575</v>
       </c>
       <c r="AI17">
-        <v>0.6275429486898366</v>
+        <v>0.00115606936416185</v>
       </c>
       <c r="AJ17">
-        <v>0.350174800408396</v>
+        <v>-0.006795422031473534</v>
       </c>
       <c r="AK17">
-        <v>0.5083845564172392</v>
+        <v>-0.00887435777673984</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>32.73374613003096</v>
-      </c>
-      <c r="AP17">
-        <v>23.28508872491073</v>
       </c>
     </row>
     <row r="18">
@@ -2594,7 +2627,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. (NasdaqGS:HOOD)</t>
+          <t>Oppenheimer Holdings Inc. (NYSE:OPY)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2602,98 +2635,104 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D18">
+        <v>0.04940000000000001</v>
+      </c>
+      <c r="E18">
+        <v>-0.00159</v>
+      </c>
       <c r="G18">
-        <v>0.7276116620684513</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>-0.005989766247608192</v>
+        <v>0.005442452620281522</v>
       </c>
       <c r="J18">
-        <v>-0.005989766247608192</v>
+        <v>0.003778459504958962</v>
       </c>
       <c r="K18">
-        <v>-1284.4</v>
+        <v>41.5</v>
       </c>
       <c r="L18">
-        <v>-0.9577212735813886</v>
+        <v>0.0347833375240969</v>
       </c>
       <c r="M18">
-        <v>19.1</v>
+        <v>44.72</v>
       </c>
       <c r="N18">
-        <v>0.002646089052672411</v>
+        <v>0.1043153720550501</v>
       </c>
       <c r="O18">
-        <v>-0.01487075677359078</v>
+        <v>1.077590361445783</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>6.52</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.0152087707021227</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>0.1571084337349397</v>
       </c>
       <c r="S18">
-        <v>19.1</v>
+        <v>38.2</v>
       </c>
       <c r="T18">
-        <v>1</v>
+        <v>0.8542039355992845</v>
       </c>
       <c r="U18">
-        <v>6187</v>
+        <v>30.8</v>
       </c>
       <c r="V18">
-        <v>0.8571388988944613</v>
+        <v>0.07184511313272685</v>
       </c>
       <c r="W18">
-        <v>-0.1739295290198521</v>
+        <v>0.05384715193979499</v>
       </c>
       <c r="X18">
-        <v>0.07035201544660906</v>
+        <v>0.08863380928517813</v>
       </c>
       <c r="Y18">
-        <v>-0.2442815444664612</v>
+        <v>-0.03478665734538314</v>
       </c>
       <c r="Z18">
-        <v>0.3010214408139252</v>
+        <v>0.9644071840671571</v>
       </c>
       <c r="AA18">
-        <v>-0.001803048065993637</v>
+        <v>0.003643973491289256</v>
       </c>
       <c r="AB18">
-        <v>0.06500118877161749</v>
+        <v>0.06077290449134413</v>
       </c>
       <c r="AC18">
-        <v>-0.06680423683761114</v>
+        <v>-0.05712893100005487</v>
       </c>
       <c r="AD18">
-        <v>1423</v>
+        <v>848.9</v>
       </c>
       <c r="AE18">
-        <v>203.1643775733367</v>
+        <v>179.0330488937106</v>
       </c>
       <c r="AF18">
-        <v>1626.164377573337</v>
+        <v>1027.933048893711</v>
       </c>
       <c r="AG18">
-        <v>-4560.835622426664</v>
+        <v>997.1330488937106</v>
       </c>
       <c r="AH18">
-        <v>0.1838644709954288</v>
+        <v>0.7056911482781536</v>
       </c>
       <c r="AI18">
-        <v>0.1895260167536851</v>
+        <v>0.5607214257423685</v>
       </c>
       <c r="AJ18">
-        <v>-1.716300429447146</v>
+        <v>0.6993336629890687</v>
       </c>
       <c r="AK18">
-        <v>-1.905776161958144</v>
+        <v>0.5532150276015669</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2702,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="AN18">
-        <v>43.65030674846626</v>
+        <v>20.06855791962175</v>
       </c>
       <c r="AP18">
-        <v>-139.9029332032719</v>
+        <v>23.57288531663619</v>
       </c>
     </row>
     <row r="19">
@@ -2716,7 +2755,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Evercore Inc. (NYSE:EVR)</t>
+          <t>MDB Capital Holdings, LLC (NasdaqCM:MDBH)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2724,116 +2763,110 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D19">
-        <v>0.136</v>
-      </c>
-      <c r="E19">
-        <v>0.274</v>
-      </c>
       <c r="G19">
-        <v>0</v>
+        <v>0.1184168012924071</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>-0.003263493553030856</v>
+        <v>-0.006836612078606559</v>
       </c>
       <c r="J19">
-        <v>-0.002495310528637088</v>
+        <v>-0.006836612078606559</v>
       </c>
       <c r="K19">
-        <v>631.9</v>
+        <v>-1.95</v>
       </c>
       <c r="L19">
-        <v>0.2074183489249959</v>
+        <v>-0.3150242326332794</v>
       </c>
       <c r="M19">
-        <v>813.8</v>
+        <v>-0</v>
       </c>
       <c r="N19">
-        <v>0.1920970635445189</v>
+        <v>-0</v>
       </c>
       <c r="O19">
-        <v>1.287862003481564</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>125.9</v>
+        <v>-0</v>
       </c>
       <c r="Q19">
-        <v>0.02971862902464357</v>
+        <v>-0</v>
       </c>
       <c r="R19">
-        <v>0.199240386137047</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>687.9</v>
-      </c>
-      <c r="T19">
-        <v>0.8452936839518309</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>473.1</v>
+        <v>24.4</v>
       </c>
       <c r="V19">
-        <v>0.1116750070814843</v>
+        <v>0.2276119402985075</v>
       </c>
       <c r="W19">
-        <v>0.5172724296005239</v>
+        <v>-0.08478260869565217</v>
       </c>
       <c r="X19">
-        <v>0.06920330024341603</v>
+        <v>0.05678980523394239</v>
       </c>
       <c r="Y19">
-        <v>0.4480691293571079</v>
+        <v>-0.1415724139295946</v>
       </c>
       <c r="Z19">
-        <v>2.281490695655996</v>
+        <v>0.481465029712732</v>
       </c>
       <c r="AA19">
-        <v>-0.005693027753857962</v>
+        <v>-0.00329158963756073</v>
       </c>
       <c r="AB19">
-        <v>0.06433857645313538</v>
+        <v>0.05656664691773802</v>
       </c>
       <c r="AC19">
-        <v>-0.07003160420699335</v>
+        <v>-0.05985823655529875</v>
       </c>
       <c r="AD19">
-        <v>369.3</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>344.7111655465425</v>
+        <v>1.456593143832873</v>
       </c>
       <c r="AF19">
-        <v>714.0111655465425</v>
+        <v>1.456593143832873</v>
       </c>
       <c r="AG19">
-        <v>240.9111655465425</v>
+        <v>-22.94340685616713</v>
       </c>
       <c r="AH19">
-        <v>0.1442326993999726</v>
+        <v>0.01340547408756618</v>
       </c>
       <c r="AI19">
-        <v>0.3101953697305172</v>
+        <v>0.03573883466393901</v>
       </c>
       <c r="AJ19">
-        <v>0.05380710802509851</v>
+        <v>-0.2723039942642929</v>
       </c>
       <c r="AK19">
-        <v>0.1317382263997617</v>
+        <v>-1.402700834728396</v>
       </c>
       <c r="AL19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>-0.776</v>
       </c>
       <c r="AN19">
-        <v>6.259322033898306</v>
+        <v>0</v>
       </c>
       <c r="AP19">
-        <v>4.083240094009195</v>
+        <v>-92.14219620950654</v>
+      </c>
+      <c r="AQ19">
+        <v>-0</v>
       </c>
     </row>
     <row r="20">
@@ -2844,7 +2877,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oppenheimer Holdings Inc. (NYSE:OPY)</t>
+          <t>StoneX Group Inc. (NasdaqGS:SNEX)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2853,7 +2886,10 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.0616</v>
+        <v>0.168</v>
+      </c>
+      <c r="E20">
+        <v>0.339</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2862,91 +2898,88 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0.00453720450522413</v>
+        <v>-0.0001163560188975404</v>
       </c>
       <c r="J20">
-        <v>0.003072770961560372</v>
+        <v>-8.591613160081542e-05</v>
       </c>
       <c r="K20">
-        <v>72.8</v>
+        <v>238.5</v>
       </c>
       <c r="L20">
-        <v>0.06346438845785024</v>
+        <v>0.003975238514310859</v>
       </c>
       <c r="M20">
-        <v>72.24000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N20">
-        <v>0.1556225764756571</v>
+        <v>-0</v>
       </c>
       <c r="O20">
-        <v>0.9923076923076924</v>
+        <v>-0</v>
       </c>
       <c r="P20">
-        <v>7.34</v>
+        <v>-0</v>
       </c>
       <c r="Q20">
-        <v>0.01581214993537268</v>
+        <v>-0</v>
       </c>
       <c r="R20">
-        <v>0.1008241758241758</v>
+        <v>-0</v>
       </c>
       <c r="S20">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="T20">
-        <v>0.8983942414174972</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>36.6</v>
+        <v>1108.3</v>
       </c>
       <c r="V20">
-        <v>0.07884532529082293</v>
+        <v>0.4795136935923506</v>
       </c>
       <c r="W20">
-        <v>0.09393548387096774</v>
+        <v>0.2228763666947015</v>
       </c>
       <c r="X20">
-        <v>0.09389240360020656</v>
+        <v>0.09561265416304748</v>
       </c>
       <c r="Y20">
-        <v>4.308027076117826e-05</v>
+        <v>0.127263712531654</v>
       </c>
       <c r="Z20">
-        <v>0.9410350879422312</v>
+        <v>10.65446356911476</v>
       </c>
       <c r="AA20">
-        <v>0.0028915852920383</v>
+        <v>-0.0009153902941401575</v>
       </c>
       <c r="AB20">
-        <v>0.0729712812980399</v>
+        <v>0.06100439804484922</v>
       </c>
       <c r="AC20">
-        <v>-0.0700796960060016</v>
+        <v>-0.06191978833898938</v>
       </c>
       <c r="AD20">
-        <v>461.9</v>
+        <v>6615.3</v>
       </c>
       <c r="AE20">
-        <v>182.476863560287</v>
+        <v>134.4047112609219</v>
       </c>
       <c r="AF20">
-        <v>644.376863560287</v>
+        <v>6749.704711260923</v>
       </c>
       <c r="AG20">
-        <v>607.776863560287</v>
+        <v>5641.404711260922</v>
       </c>
       <c r="AH20">
-        <v>0.5812649395287008</v>
+        <v>0.7449179121242989</v>
       </c>
       <c r="AI20">
-        <v>0.4171596524564231</v>
+        <v>0.8303440605370286</v>
       </c>
       <c r="AJ20">
-        <v>0.5669682660330161</v>
+        <v>0.7093693172428205</v>
       </c>
       <c r="AK20">
-        <v>0.4030145135476979</v>
+        <v>0.8035611317534026</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -2955,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="AN20">
-        <v>11.07673860911271</v>
+        <v>332.427135678392</v>
       </c>
       <c r="AP20">
-        <v>14.57498473765676</v>
+        <v>283.4876739327097</v>
       </c>
     </row>
     <row r="21">
@@ -2969,7 +3002,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cowen Inc. (NasdaqGS:COWN)</t>
+          <t>Evercore Inc. (NYSE:EVR)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2978,10 +3011,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.219</v>
+        <v>0.0699</v>
       </c>
       <c r="E21">
-        <v>0.5770000000000001</v>
+        <v>0.0999</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2990,91 +3023,91 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>0.005465006621529797</v>
+        <v>-0.00550149583275188</v>
       </c>
       <c r="J21">
-        <v>0.00378401172301901</v>
+        <v>-0.00416160375630116</v>
       </c>
       <c r="K21">
-        <v>128.5</v>
+        <v>313.2</v>
       </c>
       <c r="L21">
-        <v>0.09220061706249551</v>
+        <v>0.1266375545851529</v>
       </c>
       <c r="M21">
-        <v>82.59999999999999</v>
+        <v>574.8000000000001</v>
       </c>
       <c r="N21">
-        <v>0.07924021488871832</v>
+        <v>0.08920063936436011</v>
       </c>
       <c r="O21">
-        <v>0.6428015564202334</v>
+        <v>1.835249042145594</v>
       </c>
       <c r="P21">
-        <v>14.6</v>
+        <v>127.2</v>
       </c>
       <c r="Q21">
-        <v>0.01400613967766692</v>
+        <v>0.01973959869023418</v>
       </c>
       <c r="R21">
-        <v>0.1136186770428016</v>
+        <v>0.4061302681992338</v>
       </c>
       <c r="S21">
-        <v>68</v>
+        <v>447.6000000000001</v>
       </c>
       <c r="T21">
-        <v>0.8232445520581114</v>
+        <v>0.778705636743215</v>
       </c>
       <c r="U21">
-        <v>909.9</v>
+        <v>492.6</v>
       </c>
       <c r="V21">
-        <v>0.8728894858019953</v>
+        <v>0.07644438926736914</v>
       </c>
       <c r="W21">
-        <v>0.1308820533713587</v>
+        <v>0.2218444538886528</v>
       </c>
       <c r="X21">
-        <v>0.1140799320781667</v>
+        <v>0.05803212563158595</v>
       </c>
       <c r="Y21">
-        <v>0.01680212129319204</v>
+        <v>0.1638123282570668</v>
       </c>
       <c r="Z21">
-        <v>0.3574398931272527</v>
+        <v>1.645802995523476</v>
       </c>
       <c r="AA21">
-        <v>0.001352556745868186</v>
+        <v>-0.006849179928302199</v>
       </c>
       <c r="AB21">
-        <v>0.07449488152208145</v>
+        <v>0.05569607220122109</v>
       </c>
       <c r="AC21">
-        <v>-0.07314232477621326</v>
+        <v>-0.06254525212952329</v>
       </c>
       <c r="AD21">
-        <v>2398.6</v>
+        <v>372.4</v>
       </c>
       <c r="AE21">
-        <v>87.9171013578696</v>
+        <v>314.5314974678097</v>
       </c>
       <c r="AF21">
-        <v>2486.51710135787</v>
+        <v>686.9314974678098</v>
       </c>
       <c r="AG21">
-        <v>1576.61710135787</v>
+        <v>194.3314974678098</v>
       </c>
       <c r="AH21">
-        <v>0.7046119333324941</v>
+        <v>0.09633259427203437</v>
       </c>
       <c r="AI21">
-        <v>0.6527118884626012</v>
+        <v>0.293380992871543</v>
       </c>
       <c r="AJ21">
-        <v>0.6019880895548365</v>
+        <v>0.02927458880304771</v>
       </c>
       <c r="AK21">
-        <v>0.5437328606661725</v>
+        <v>0.1051104428575397</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3083,10 +3116,10 @@
         <v>0</v>
       </c>
       <c r="AN21">
-        <v>95.18253968253968</v>
+        <v>7.553752535496957</v>
       </c>
       <c r="AP21">
-        <v>62.56417068880435</v>
+        <v>3.941815364458616</v>
       </c>
     </row>
     <row r="22">
@@ -3097,7 +3130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>StoneX Group Inc. (NasdaqGS:SNEX)</t>
+          <t>Stifel Financial Corp. (NYSE:SF)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3106,10 +3139,10 @@
         </is>
       </c>
       <c r="D22">
-        <v>0.175</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="E22">
-        <v>1.004</v>
+        <v>0.141</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3118,88 +3151,91 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>-0.0001096350229081626</v>
+        <v>-0.01193390987466261</v>
       </c>
       <c r="J22">
-        <v>-8.190986018860201e-05</v>
+        <v>-0.008721309136344529</v>
       </c>
       <c r="K22">
-        <v>207.1</v>
+        <v>536.7</v>
       </c>
       <c r="L22">
-        <v>0.003144749589254097</v>
+        <v>0.1249476183824557</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>631.1</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.08947965404792288</v>
       </c>
       <c r="O22">
-        <v>-0</v>
+        <v>1.175889696292156</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>156.8</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.02223167446476677</v>
       </c>
       <c r="R22">
-        <v>-0</v>
+        <v>0.2921557667225638</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>474.3</v>
+      </c>
+      <c r="T22">
+        <v>0.7515449215655206</v>
       </c>
       <c r="U22">
-        <v>1108.5</v>
+        <v>2768.4</v>
       </c>
       <c r="V22">
-        <v>0.5703627476202727</v>
+        <v>0.3925138239047214</v>
       </c>
       <c r="W22">
-        <v>0.2290929203539823</v>
+        <v>0.1181533990841846</v>
       </c>
       <c r="X22">
-        <v>0.1253232064344696</v>
+        <v>0.06140525791771474</v>
       </c>
       <c r="Y22">
-        <v>0.1037697139195126</v>
+        <v>0.05674814116646985</v>
       </c>
       <c r="Z22">
-        <v>8.807783268930462</v>
+        <v>0.8838445132390036</v>
       </c>
       <c r="AA22">
-        <v>-0.0007214442961296022</v>
+        <v>-0.007708281228419306</v>
       </c>
       <c r="AB22">
-        <v>0.0750091139677535</v>
+        <v>0.05605391277126336</v>
       </c>
       <c r="AC22">
-        <v>-0.07573055826388311</v>
+        <v>-0.06376219399968266</v>
       </c>
       <c r="AD22">
-        <v>5593.3</v>
+        <v>1750.3</v>
       </c>
       <c r="AE22">
-        <v>122.1005107081769</v>
+        <v>782.8045823781288</v>
       </c>
       <c r="AF22">
-        <v>5715.400510708177</v>
+        <v>2533.104582378129</v>
       </c>
       <c r="AG22">
-        <v>4606.900510708177</v>
+        <v>-235.2954176218714</v>
       </c>
       <c r="AH22">
-        <v>0.7462429499792138</v>
+        <v>0.2642475429523964</v>
       </c>
       <c r="AI22">
-        <v>0.8422960843770805</v>
+        <v>0.3257717105301088</v>
       </c>
       <c r="AJ22">
-        <v>0.7033005849302054</v>
+        <v>-0.03451241026635924</v>
       </c>
       <c r="AK22">
-        <v>0.811502571123336</v>
+        <v>-0.04699043442452668</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3208,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="AN22">
-        <v>325.1918604651163</v>
+        <v>16.62203228869896</v>
       </c>
       <c r="AP22">
-        <v>267.8430529481498</v>
+        <v>-2.234524383873422</v>
       </c>
     </row>
     <row r="23">
@@ -3222,7 +3258,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stifel Financial Corp. (NYSE:SF)</t>
+          <t>Moelis &amp; Company (NYSE:MC)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3231,10 +3267,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.103</v>
+        <v>0.00732</v>
       </c>
       <c r="E23">
-        <v>0.287</v>
+        <v>-0.579</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3243,91 +3279,91 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>-0.01096175204431182</v>
+        <v>-0.01678941455566433</v>
       </c>
       <c r="J23">
-        <v>-0.008439679004119681</v>
+        <v>-0.008394707277832165</v>
       </c>
       <c r="K23">
-        <v>746.9</v>
+        <v>1.02</v>
       </c>
       <c r="L23">
-        <v>0.1646024330042313</v>
+        <v>0.001204108133632393</v>
       </c>
       <c r="M23">
-        <v>334.1</v>
+        <v>205.5</v>
       </c>
       <c r="N23">
-        <v>0.0538558256496228</v>
+        <v>0.05491715660074827</v>
       </c>
       <c r="O23">
-        <v>0.4473155710269113</v>
+        <v>201.4705882352941</v>
       </c>
       <c r="P23">
-        <v>119.6</v>
+        <v>158.7</v>
       </c>
       <c r="Q23">
-        <v>0.019279128248114</v>
+        <v>0.04241047568145376</v>
       </c>
       <c r="R23">
-        <v>0.1601285312625519</v>
+        <v>155.5882352941176</v>
       </c>
       <c r="S23">
-        <v>214.5</v>
+        <v>46.80000000000001</v>
       </c>
       <c r="T23">
-        <v>0.642023346303502</v>
+        <v>0.2277372262773723</v>
       </c>
       <c r="U23">
-        <v>1414.5</v>
+        <v>147.5</v>
       </c>
       <c r="V23">
-        <v>0.228012766780579</v>
+        <v>0.03941742383752004</v>
       </c>
       <c r="W23">
-        <v>0.1818912402893115</v>
+        <v>0.002370439228445271</v>
       </c>
       <c r="X23">
-        <v>0.07339922549224728</v>
+        <v>0.05726368664043371</v>
       </c>
       <c r="Y23">
-        <v>0.1084920147970642</v>
+        <v>-0.05489324741198844</v>
       </c>
       <c r="Z23">
-        <v>1.218932928378174</v>
+        <v>1.81893700527371</v>
       </c>
       <c r="AA23">
-        <v>-0.01028740264306339</v>
+        <v>-0.01526944371608946</v>
       </c>
       <c r="AB23">
-        <v>0.06582614242779825</v>
+        <v>0.05636927809633401</v>
       </c>
       <c r="AC23">
-        <v>-0.07611354507086164</v>
+        <v>-0.07163872181242348</v>
       </c>
       <c r="AD23">
-        <v>1584.2</v>
+        <v>0</v>
       </c>
       <c r="AE23">
-        <v>747.2002303813467</v>
+        <v>183.6115653505163</v>
       </c>
       <c r="AF23">
-        <v>2331.400230381347</v>
+        <v>183.6115653505163</v>
       </c>
       <c r="AG23">
-        <v>916.9002303813468</v>
+        <v>36.11156535051629</v>
       </c>
       <c r="AH23">
-        <v>0.2731576060282284</v>
+        <v>0.04677272885864898</v>
       </c>
       <c r="AI23">
-        <v>0.3084352224326117</v>
+        <v>0.3257189964451881</v>
       </c>
       <c r="AJ23">
-        <v>0.1287690753058569</v>
+        <v>0.0095580992582907</v>
       </c>
       <c r="AK23">
-        <v>0.1492277714307654</v>
+        <v>0.08676252261299996</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3336,10 +3372,10 @@
         <v>0</v>
       </c>
       <c r="AN23">
-        <v>15.88966900702106</v>
+        <v>0</v>
       </c>
       <c r="AP23">
-        <v>9.196592080053628</v>
+        <v>1.604958460022946</v>
       </c>
     </row>
     <row r="24">
@@ -3350,7 +3386,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Moelis &amp; Company (NYSE:MC)</t>
+          <t>Houlihan Lokey, Inc. (NYSE:HLI)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3359,10 +3395,10 @@
         </is>
       </c>
       <c r="D24">
-        <v>0.108</v>
+        <v>0.123</v>
       </c>
       <c r="E24">
-        <v>0.271</v>
+        <v>0.0818</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3371,91 +3407,91 @@
         <v>0</v>
       </c>
       <c r="I24">
-        <v>-0.01444394795648625</v>
+        <v>-0.02689899692534473</v>
       </c>
       <c r="J24">
-        <v>-0.01098857957991258</v>
+        <v>-0.020234685823709</v>
       </c>
       <c r="K24">
-        <v>229.3</v>
+        <v>251.1</v>
       </c>
       <c r="L24">
-        <v>0.1905909733189261</v>
+        <v>0.1407511210762332</v>
       </c>
       <c r="M24">
-        <v>303.6</v>
+        <v>238.8</v>
       </c>
       <c r="N24">
-        <v>0.1236962190352021</v>
+        <v>0.02880162099575453</v>
       </c>
       <c r="O24">
-        <v>1.324029655473179</v>
+        <v>0.951015531660693</v>
       </c>
       <c r="P24">
-        <v>153.2</v>
+        <v>144</v>
       </c>
       <c r="Q24">
-        <v>0.06241851368970013</v>
+        <v>0.01736781165573138</v>
       </c>
       <c r="R24">
-        <v>0.6681203663323156</v>
+        <v>0.5734767025089605</v>
       </c>
       <c r="S24">
-        <v>150.4</v>
+        <v>94.80000000000001</v>
       </c>
       <c r="T24">
-        <v>0.4953886693017129</v>
+        <v>0.3969849246231156</v>
       </c>
       <c r="U24">
-        <v>148.2</v>
+        <v>493.9</v>
       </c>
       <c r="V24">
-        <v>0.06038135593220338</v>
+        <v>0.05956918178309532</v>
       </c>
       <c r="W24">
-        <v>0.4436919504643964</v>
+        <v>0.173567429321905</v>
       </c>
       <c r="X24">
-        <v>0.06745655249742369</v>
+        <v>0.05724936325476611</v>
       </c>
       <c r="Y24">
-        <v>0.3762353979669727</v>
+        <v>0.1163180660671389</v>
       </c>
       <c r="Z24">
-        <v>2.734395435124837</v>
+        <v>6.150768593249423</v>
       </c>
       <c r="AA24">
-        <v>-0.03004712184181896</v>
+        <v>-0.1244588700587386</v>
       </c>
       <c r="AB24">
-        <v>0.06502583755529896</v>
+        <v>0.05617463297841224</v>
       </c>
       <c r="AC24">
-        <v>-0.09507295939711793</v>
+        <v>-0.1806335030371509</v>
       </c>
       <c r="AD24">
         <v>0</v>
       </c>
       <c r="AE24">
-        <v>201.887568932243</v>
+        <v>397.939052574075</v>
       </c>
       <c r="AF24">
-        <v>201.887568932243</v>
+        <v>397.939052574075</v>
       </c>
       <c r="AG24">
-        <v>53.68756893224301</v>
+        <v>-95.96094742592493</v>
       </c>
       <c r="AH24">
-        <v>0.07600365686814414</v>
+        <v>0.04579729362901488</v>
       </c>
       <c r="AI24">
-        <v>0.3121389133460489</v>
+        <v>0.1946827053391897</v>
       </c>
       <c r="AJ24">
-        <v>0.02140577928668543</v>
+        <v>-0.01170935305368355</v>
       </c>
       <c r="AK24">
-        <v>0.1076793170901119</v>
+        <v>-0.06190473510526524</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -3467,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>2.334242127488827</v>
+        <v>-3.036738842592561</v>
       </c>
     </row>
     <row r="25">
@@ -3478,7 +3514,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Greenhill &amp; Co., Inc. (NYSE:GHL)</t>
+          <t>Perella Weinberg Partners (NasdaqGS:PWP)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3486,104 +3522,98 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D25">
-        <v>-0.00335</v>
-      </c>
-      <c r="E25">
-        <v>-0.12</v>
-      </c>
       <c r="G25">
-        <v>0</v>
+        <v>0.001616031027795734</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
       <c r="I25">
-        <v>-0.02316889040488391</v>
+        <v>-0.0639175706188352</v>
       </c>
       <c r="J25">
-        <v>-0.01656845069651582</v>
+        <v>-0.0639175706188352</v>
       </c>
       <c r="K25">
-        <v>12.3</v>
+        <v>-8.23</v>
       </c>
       <c r="L25">
-        <v>0.04622322435174746</v>
+        <v>-0.01329993535875889</v>
       </c>
       <c r="M25">
-        <v>48.53</v>
+        <v>66.7</v>
       </c>
       <c r="N25">
-        <v>0.2628927410617551</v>
+        <v>0.1222731439046746</v>
       </c>
       <c r="O25">
-        <v>3.945528455284553</v>
+        <v>-8.1044957472661</v>
       </c>
       <c r="P25">
-        <v>6.33</v>
+        <v>13.1</v>
       </c>
       <c r="Q25">
-        <v>0.03429035752979415</v>
+        <v>0.02401466544454629</v>
       </c>
       <c r="R25">
-        <v>0.5146341463414634</v>
+        <v>-1.591737545565006</v>
       </c>
       <c r="S25">
-        <v>42.2</v>
+        <v>53.6</v>
       </c>
       <c r="T25">
-        <v>0.8695652173913044</v>
+        <v>0.8035982008995503</v>
       </c>
       <c r="U25">
-        <v>57.5</v>
+        <v>126.6</v>
       </c>
       <c r="V25">
-        <v>0.3114842903575298</v>
+        <v>0.2320806599450046</v>
       </c>
       <c r="W25">
-        <v>0.1524163568773234</v>
+        <v>-0.05878571428571429</v>
       </c>
       <c r="X25">
-        <v>0.1061498080023754</v>
+        <v>0.06097906077840208</v>
       </c>
       <c r="Y25">
-        <v>0.04626654887494798</v>
+        <v>-0.1197647750641164</v>
       </c>
       <c r="Z25">
-        <v>1.623291370774336</v>
+        <v>4.382096012136691</v>
       </c>
       <c r="AA25">
-        <v>-0.02689542304275416</v>
+        <v>-0.2800929313142631</v>
       </c>
       <c r="AB25">
-        <v>0.07401743058378267</v>
+        <v>0.05534820736358134</v>
       </c>
       <c r="AC25">
-        <v>-0.1009128536265368</v>
+        <v>-0.3354411386778444</v>
       </c>
       <c r="AD25">
-        <v>269.2</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>98.82620868369804</v>
+        <v>178.5109634946761</v>
       </c>
       <c r="AF25">
-        <v>368.026208683698</v>
+        <v>178.5109634946761</v>
       </c>
       <c r="AG25">
-        <v>310.526208683698</v>
+        <v>51.91096349467608</v>
       </c>
       <c r="AH25">
-        <v>0.6659586586750939</v>
+        <v>0.2465583706537183</v>
       </c>
       <c r="AI25">
-        <v>0.8636554175358736</v>
+        <v>0.402676627005684</v>
       </c>
       <c r="AJ25">
-        <v>0.6271657675105456</v>
+        <v>0.08689322203096579</v>
       </c>
       <c r="AK25">
-        <v>0.8423877667096289</v>
+        <v>0.1639064303991128</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -3592,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="AN25">
-        <v>19.79411764705882</v>
+        <v>-0</v>
       </c>
       <c r="AP25">
-        <v>22.83280946203662</v>
+        <v>-13.48336714147431</v>
       </c>
     </row>
     <row r="26">
@@ -3606,7 +3636,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Houlihan Lokey, Inc. (NYSE:HLI)</t>
+          <t>BlackStar Enterprise Group, Inc. (OTCPK:BEGI)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3614,339 +3644,92 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D26">
-        <v>0.187</v>
-      </c>
-      <c r="E26">
-        <v>0.214</v>
-      </c>
-      <c r="G26">
-        <v>0</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>-0.0009141834544414997</v>
-      </c>
-      <c r="J26">
-        <v>-0.0006785955614201608</v>
-      </c>
       <c r="K26">
-        <v>370.4</v>
-      </c>
-      <c r="L26">
-        <v>0.1633228978350015</v>
+        <v>-0.524</v>
       </c>
       <c r="M26">
-        <v>412.1</v>
+        <v>-0</v>
       </c>
       <c r="N26">
-        <v>0.06886928039038738</v>
+        <v>-0</v>
       </c>
       <c r="O26">
-        <v>1.112580993520518</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>129.1</v>
+        <v>-0</v>
       </c>
       <c r="Q26">
-        <v>0.0215749189478258</v>
+        <v>-0</v>
       </c>
       <c r="R26">
-        <v>0.3485421166306695</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>283</v>
-      </c>
-      <c r="T26">
-        <v>0.6867265226886677</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>503.8</v>
+        <v>0.051</v>
       </c>
       <c r="V26">
-        <v>0.08419399044085699</v>
+        <v>0.01108695652173913</v>
       </c>
       <c r="W26">
-        <v>0.2576337205258399</v>
+        <v>0.8238993710691824</v>
       </c>
       <c r="X26">
-        <v>0.06641515416070032</v>
+        <v>0.05924182856459091</v>
       </c>
       <c r="Y26">
-        <v>0.1912185663651396</v>
+        <v>0.7646575425045915</v>
       </c>
       <c r="Z26">
-        <v>113.5233763114685</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>-0.07703645928239312</v>
+        <v>-11.82142857142857</v>
       </c>
       <c r="AB26">
-        <v>0.06549032430718142</v>
+        <v>0.05609626155749377</v>
       </c>
       <c r="AC26">
-        <v>-0.1425267835895745</v>
+        <v>-11.87752483298607</v>
       </c>
       <c r="AD26">
-        <v>0.506</v>
+        <v>0.907</v>
       </c>
       <c r="AE26">
-        <v>183.8663832816394</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>184.3723832816394</v>
+        <v>0.907</v>
       </c>
       <c r="AG26">
-        <v>-319.4276167183606</v>
+        <v>0.856</v>
       </c>
       <c r="AH26">
-        <v>0.02989092584075093</v>
+        <v>0.1646994733974941</v>
       </c>
       <c r="AI26">
-        <v>0.113037523761325</v>
+        <v>-32.39285714285712</v>
       </c>
       <c r="AJ26">
-        <v>-0.05639241121596265</v>
+        <v>0.156891495601173</v>
       </c>
       <c r="AK26">
-        <v>-0.2833632948484592</v>
+        <v>-10.83544303797467</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="AM26">
-        <v>0</v>
-      </c>
-      <c r="AN26">
-        <v>0.0145821325648415</v>
-      </c>
-      <c r="AP26">
-        <v>-9.205406821854771</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>BlackStar Enterprise Group, Inc. (OTCPK:BEGI)</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="K27">
-        <v>-1.42</v>
-      </c>
-      <c r="M27">
-        <v>-0</v>
-      </c>
-      <c r="N27">
-        <v>-0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>-0</v>
-      </c>
-      <c r="Q27">
-        <v>-0</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
-      </c>
-      <c r="S27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0.099</v>
-      </c>
-      <c r="V27">
-        <v>0.3473684210526316</v>
-      </c>
-      <c r="W27">
-        <v>-11.36</v>
-      </c>
-      <c r="X27">
-        <v>0.1199162936687306</v>
-      </c>
-      <c r="Y27">
-        <v>-11.47991629366873</v>
-      </c>
-      <c r="Z27">
-        <v>0</v>
-      </c>
-      <c r="AA27">
-        <v>-21.45833333333341</v>
-      </c>
-      <c r="AB27">
-        <v>0.08253222893561432</v>
-      </c>
-      <c r="AC27">
-        <v>-21.54086556226903</v>
-      </c>
-      <c r="AD27">
-        <v>0.762</v>
-      </c>
-      <c r="AE27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>0.762</v>
-      </c>
-      <c r="AG27">
-        <v>0.663</v>
-      </c>
-      <c r="AH27">
-        <v>0.7277936962750717</v>
-      </c>
-      <c r="AI27">
-        <v>6</v>
-      </c>
-      <c r="AJ27">
-        <v>0.699367088607595</v>
-      </c>
-      <c r="AK27">
-        <v>23.67857142857141</v>
-      </c>
-      <c r="AL27">
-        <v>1.07</v>
-      </c>
-      <c r="AM27">
-        <v>1.07</v>
-      </c>
-      <c r="AO27">
-        <v>-0.4813084112149533</v>
-      </c>
-      <c r="AQ27">
-        <v>-0.4813084112149533</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>PJT Partners Inc. (NYSE:PJT)</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>0.171</v>
-      </c>
-      <c r="E28">
-        <v>0.54</v>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>-0.001277876367879876</v>
-      </c>
-      <c r="J28">
-        <v>-0.0010799620899142</v>
-      </c>
-      <c r="K28">
-        <v>100.9</v>
-      </c>
-      <c r="L28">
-        <v>0.09514380009429516</v>
-      </c>
-      <c r="M28">
-        <v>147.6</v>
-      </c>
-      <c r="N28">
-        <v>0.08204102051025512</v>
-      </c>
-      <c r="O28">
-        <v>1.462834489593657</v>
-      </c>
-      <c r="P28">
-        <v>19.8</v>
-      </c>
-      <c r="Q28">
-        <v>0.01100550275137569</v>
-      </c>
-      <c r="R28">
-        <v>0.1962338949454906</v>
-      </c>
-      <c r="S28">
-        <v>127.8</v>
-      </c>
-      <c r="T28">
-        <v>0.8658536585365854</v>
-      </c>
-      <c r="U28">
-        <v>189.8</v>
-      </c>
-      <c r="V28">
-        <v>0.1054971930409649</v>
-      </c>
-      <c r="W28">
-        <v>1.295250320924262</v>
-      </c>
-      <c r="X28">
-        <v>0.06753858342745714</v>
-      </c>
-      <c r="Y28">
-        <v>1.227711737496805</v>
-      </c>
-      <c r="AB28">
-        <v>0.06499111907422837</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>155.275939440683</v>
-      </c>
-      <c r="AF28">
-        <v>155.275939440683</v>
-      </c>
-      <c r="AG28">
-        <v>-34.52406055931698</v>
-      </c>
-      <c r="AH28">
-        <v>0.07945039452599943</v>
-      </c>
-      <c r="AI28">
-        <v>0.1793488734983741</v>
-      </c>
-      <c r="AJ28">
-        <v>-0.01956507497787829</v>
-      </c>
-      <c r="AK28">
-        <v>-0.05107291331683037</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>0</v>
-      </c>
-      <c r="AN28">
-        <v>0</v>
-      </c>
-      <c r="AP28">
-        <v>-1.162426281458484</v>
+        <v>0.193</v>
+      </c>
+      <c r="AO26">
+        <v>-1.715025906735751</v>
+      </c>
+      <c r="AQ26">
+        <v>-1.715025906735751</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/united_states/united_states_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/united_states/united_states_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08310000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="E2">
-        <v>0.0852</v>
+        <v>0.126</v>
       </c>
       <c r="F2">
-        <v>0.1805</v>
+        <v>0.163</v>
       </c>
       <c r="G2">
-        <v>0.0001637503042926883</v>
+        <v>0.01021602218435273</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.007151034706293555</v>
       </c>
       <c r="I2">
-        <v>-0.0008116075128093385</v>
+        <v>0.004673402208995463</v>
       </c>
       <c r="J2">
-        <v>-0.0006091847844110027</v>
+        <v>0.003896024571637618</v>
       </c>
       <c r="K2">
-        <v>32196.6</v>
+        <v>35610.274</v>
       </c>
       <c r="L2">
-        <v>0.1282774464036489</v>
+        <v>0.1240683582336775</v>
       </c>
       <c r="M2">
-        <v>26880.085</v>
+        <v>29844.016</v>
       </c>
       <c r="N2">
-        <v>0.04535393590098565</v>
+        <v>0.04168527480748471</v>
       </c>
       <c r="O2">
-        <v>0.8348734027816602</v>
+        <v>0.8380731920231785</v>
       </c>
       <c r="P2">
-        <v>12114.685</v>
+        <v>13232.016</v>
       </c>
       <c r="Q2">
-        <v>0.02044073323989237</v>
+        <v>0.01848210452698573</v>
       </c>
       <c r="R2">
-        <v>0.3762721840194306</v>
+        <v>0.3715786067807285</v>
       </c>
       <c r="S2">
-        <v>14765.4</v>
+        <v>16612</v>
       </c>
       <c r="T2">
-        <v>0.5493062986966001</v>
+        <v>0.5566274994625389</v>
       </c>
       <c r="U2">
-        <v>305942.8</v>
+        <v>319867.702</v>
       </c>
       <c r="V2">
-        <v>0.5162078222806242</v>
+        <v>0.4467821307932762</v>
       </c>
       <c r="W2">
         <v>0.14338710552656</v>
       </c>
       <c r="X2">
-        <v>0.0774003491507311</v>
+        <v>0.06628281295838059</v>
       </c>
       <c r="Y2">
-        <v>0.06598675637582888</v>
+        <v>0.07710429256817938</v>
       </c>
       <c r="Z2">
-        <v>0.2558362680675597</v>
+        <v>0.2817626154540249</v>
       </c>
       <c r="AA2">
-        <v>-0.0001134290039439529</v>
+        <v>-2.668198160587436E-05</v>
       </c>
       <c r="AB2">
-        <v>0.06044801473754603</v>
+        <v>0.06137520078794816</v>
       </c>
       <c r="AC2">
-        <v>-0.05860096744847695</v>
+        <v>-0.06116212527553364</v>
       </c>
       <c r="AD2">
-        <v>1280140.4</v>
+        <v>1322329.639</v>
       </c>
       <c r="AE2">
-        <v>10324.03455847145</v>
+        <v>13496.22775268814</v>
       </c>
       <c r="AF2">
-        <v>1290464.434558471</v>
+        <v>1335825.866752688</v>
       </c>
       <c r="AG2">
-        <v>984521.6345584714</v>
+        <v>1015958.164752688</v>
       </c>
       <c r="AH2">
-        <v>0.6852733800439124</v>
+        <v>0.6510626136532075</v>
       </c>
       <c r="AI2">
-        <v>0.8095357895149847</v>
+        <v>0.797251609377465</v>
       </c>
       <c r="AJ2">
-        <v>0.6242230198037478</v>
+        <v>0.5866165520553078</v>
       </c>
       <c r="AK2">
-        <v>0.7642990127875914</v>
+        <v>0.7494135532470957</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>246.6</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>195.95</v>
       </c>
       <c r="AN2">
-        <v>687.8407393476975</v>
+        <v>297.3306585491497</v>
+      </c>
+      <c r="AO2">
+        <v>6.852696674776967</v>
       </c>
       <c r="AP2">
-        <v>528.9998573738495</v>
+        <v>228.4419113623923</v>
+      </c>
+      <c r="AQ2">
+        <v>8.624011227353916</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Raymond James Financial, Inc. (NYSE:RJF)</t>
+          <t>LPL Financial Holdings Inc. (NasdaqGS:LPLA)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,118 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.107</v>
+        <v>0.16</v>
       </c>
       <c r="E3">
-        <v>0.149</v>
+        <v>0.127</v>
       </c>
       <c r="F3">
-        <v>0.163</v>
+        <v>0.128</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1800791900387267</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1800791900387267</v>
       </c>
       <c r="I3">
-        <v>0.001945889456898755</v>
+        <v>0.1483692793522181</v>
       </c>
       <c r="J3">
-        <v>0.001522549904224981</v>
+        <v>0.1108744414008623</v>
       </c>
       <c r="K3">
-        <v>2068</v>
+        <v>1005.4</v>
       </c>
       <c r="L3">
-        <v>0.1616003750879112</v>
+        <v>0.08730007120156991</v>
       </c>
       <c r="M3">
-        <v>1351.2</v>
+        <v>426</v>
       </c>
       <c r="N3">
-        <v>0.04263227141788902</v>
+        <v>0.01742552225435536</v>
       </c>
       <c r="O3">
-        <v>0.6533849129593811</v>
+        <v>0.4237119554406207</v>
       </c>
       <c r="P3">
-        <v>367.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.01158567944393787</v>
+        <v>0.003677357865414429</v>
       </c>
       <c r="R3">
-        <v>0.1775628626692456</v>
+        <v>0.08941714740401831</v>
       </c>
       <c r="S3">
-        <v>984</v>
+        <v>336.1</v>
       </c>
       <c r="T3">
-        <v>0.7282415630550622</v>
+        <v>0.7889671361502348</v>
       </c>
       <c r="U3">
-        <v>10998</v>
+        <v>1475</v>
       </c>
       <c r="V3">
-        <v>0.347002457855198</v>
+        <v>0.06033484818115998</v>
       </c>
       <c r="W3">
-        <v>0.2040453872718303</v>
+        <v>0.4809145699799101</v>
       </c>
       <c r="X3">
-        <v>0.06446579623467288</v>
+        <v>0.06496549012429867</v>
       </c>
       <c r="Y3">
-        <v>0.1395795910371574</v>
+        <v>0.4159490798556115</v>
       </c>
       <c r="Z3">
-        <v>3.243448256047074</v>
+        <v>4.007653276522269</v>
       </c>
       <c r="AA3">
-        <v>0.004938311831603154</v>
+        <v>0.444346318362742</v>
       </c>
       <c r="AB3">
-        <v>0.06146022653711069</v>
+        <v>0.06119684741205553</v>
       </c>
       <c r="AC3">
-        <v>-0.05652191470550753</v>
+        <v>0.3831494709506865</v>
       </c>
       <c r="AD3">
-        <v>4251</v>
+        <v>4547.1</v>
       </c>
       <c r="AE3">
-        <v>515.4922631003332</v>
+        <v>124.4517870612257</v>
       </c>
       <c r="AF3">
-        <v>4766.492263100333</v>
+        <v>4671.551787061226</v>
       </c>
       <c r="AG3">
-        <v>-6231.507736899667</v>
+        <v>3196.551787061226</v>
       </c>
       <c r="AH3">
-        <v>0.1307292564765302</v>
+        <v>0.1604326981813308</v>
       </c>
       <c r="AI3">
-        <v>0.2900474340322043</v>
+        <v>0.6276139998087664</v>
       </c>
       <c r="AJ3">
-        <v>-0.244729944481781</v>
+        <v>0.1156350448447759</v>
       </c>
       <c r="AK3">
-        <v>-1.146447724560884</v>
+        <v>0.5355836755452354</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>246.6</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>246.6</v>
       </c>
       <c r="AN3">
-        <v>33.2109375</v>
+        <v>2.125508343850792</v>
+      </c>
+      <c r="AO3">
+        <v>6.914436334144363</v>
       </c>
       <c r="AP3">
-        <v>-48.68365419452865</v>
+        <v>1.494204546842998</v>
+      </c>
+      <c r="AQ3">
+        <v>6.914436334144363</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Goldman Sachs Group, Inc. (NYSE:GS)</t>
+          <t>Oppenheimer Holdings Inc. (NYSE:OPY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,13 +862,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0793</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="E4">
-        <v>0.0602</v>
-      </c>
-      <c r="F4">
-        <v>0.198</v>
+        <v>0.15</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,91 +874,91 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>-0.002300589176985216</v>
+        <v>0.004059683229048345</v>
       </c>
       <c r="J4">
-        <v>-0.001819219959168574</v>
+        <v>0.002748386486520054</v>
       </c>
       <c r="K4">
-        <v>12173</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L4">
-        <v>0.2464818676979772</v>
+        <v>0.05615432677288348</v>
       </c>
       <c r="M4">
-        <v>12051.96</v>
+        <v>26.83</v>
       </c>
       <c r="N4">
-        <v>0.06393066692977416</v>
+        <v>0.0405225796707446</v>
       </c>
       <c r="O4">
-        <v>0.9900566828226401</v>
+        <v>0.3731571627260084</v>
       </c>
       <c r="P4">
-        <v>3719.96</v>
+        <v>6.53</v>
       </c>
       <c r="Q4">
-        <v>0.01973285040375862</v>
+        <v>0.009862558525902431</v>
       </c>
       <c r="R4">
-        <v>0.3055910621868069</v>
+        <v>0.09082058414464533</v>
       </c>
       <c r="S4">
-        <v>8332</v>
+        <v>20.3</v>
       </c>
       <c r="T4">
-        <v>0.6913398318613736</v>
+        <v>0.7566157286619456</v>
       </c>
       <c r="U4">
-        <v>154689</v>
+        <v>32.2</v>
       </c>
       <c r="V4">
-        <v>0.8205612146654848</v>
+        <v>0.04863313698837034</v>
       </c>
       <c r="W4">
-        <v>0.1147595075136226</v>
+        <v>0.09226228666752215</v>
       </c>
       <c r="X4">
-        <v>0.1120737079812987</v>
+        <v>0.08683245379872877</v>
       </c>
       <c r="Y4">
-        <v>0.002685799532323896</v>
+        <v>0.00542983286879338</v>
       </c>
       <c r="Z4">
-        <v>0.09536727200126356</v>
+        <v>0.7745870087217116</v>
       </c>
       <c r="AA4">
-        <v>-0.000173494044676157</v>
+        <v>0.002128864467404743</v>
       </c>
       <c r="AB4">
-        <v>0.05643943566800928</v>
+        <v>0.05522409567370805</v>
       </c>
       <c r="AC4">
-        <v>-0.05661292971268544</v>
+        <v>-0.05309523120630331</v>
       </c>
       <c r="AD4">
-        <v>739559</v>
+        <v>1084.6</v>
       </c>
       <c r="AE4">
-        <v>2193.095988418844</v>
+        <v>193.5099079676325</v>
       </c>
       <c r="AF4">
-        <v>741752.0959884188</v>
+        <v>1278.109907967632</v>
       </c>
       <c r="AG4">
-        <v>587063.0959884188</v>
+        <v>1245.909907967632</v>
       </c>
       <c r="AH4">
-        <v>0.7973529560475838</v>
+        <v>0.6587482636383664</v>
       </c>
       <c r="AI4">
-        <v>0.8591168216448826</v>
+        <v>0.6040474139068042</v>
       </c>
       <c r="AJ4">
-        <v>0.7569350738453601</v>
+        <v>0.6529892233603475</v>
       </c>
       <c r="AK4">
-        <v>0.8283660455409509</v>
+        <v>0.5979286767335302</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,10 +967,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>2275.566153846154</v>
+        <v>24.70615034168565</v>
       </c>
       <c r="AP4">
-        <v>1806.347987656673</v>
+        <v>28.38063571680256</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Morgan Stanley (NYSE:MS)</t>
+          <t>Virtu Financial, Inc. (NasdaqGS:VIRT)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,106 +990,106 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.08310000000000001</v>
+        <v>0.0828</v>
       </c>
       <c r="E5">
-        <v>0.0608</v>
+        <v>0.363</v>
       </c>
       <c r="F5">
-        <v>0.135</v>
+        <v>0.276</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>0.01973821989528796</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-0.001883552107145254</v>
+        <v>0.01103878590714492</v>
       </c>
       <c r="J5">
-        <v>-0.001445338983340326</v>
+        <v>0.008779104123016825</v>
       </c>
       <c r="K5">
-        <v>11193</v>
+        <v>187.9</v>
       </c>
       <c r="L5">
-        <v>0.192049003122748</v>
+        <v>0.09837696335078534</v>
       </c>
       <c r="M5">
-        <v>10408.05</v>
+        <v>269.1</v>
       </c>
       <c r="N5">
-        <v>0.05138777936539755</v>
+        <v>0.08774618494848051</v>
       </c>
       <c r="O5">
-        <v>0.9298713481640311</v>
+        <v>1.43214475784992</v>
       </c>
       <c r="P5">
-        <v>5719.049999999999</v>
+        <v>90</v>
       </c>
       <c r="Q5">
-        <v>0.02823672826126669</v>
+        <v>0.02934655014999348</v>
       </c>
       <c r="R5">
-        <v>0.5109488072902706</v>
+        <v>0.4789781798829164</v>
       </c>
       <c r="S5">
-        <v>4689</v>
+        <v>179.1</v>
       </c>
       <c r="T5">
-        <v>0.4505166673872628</v>
+        <v>0.6655518394648829</v>
       </c>
       <c r="U5">
-        <v>91084</v>
+        <v>701.4</v>
       </c>
       <c r="V5">
-        <v>0.4497100317271603</v>
+        <v>0.2287074475022825</v>
       </c>
       <c r="W5">
-        <v>0.1237328793623772</v>
+        <v>0.1485023314628942</v>
       </c>
       <c r="X5">
-        <v>0.0892725873981601</v>
+        <v>0.08500640364925277</v>
       </c>
       <c r="Y5">
-        <v>0.03446029196421706</v>
+        <v>0.06349592781364141</v>
       </c>
       <c r="Z5">
-        <v>0.162607257786381</v>
+        <v>0.2964743030051947</v>
       </c>
       <c r="AA5">
-        <v>-0.0002350226086527261</v>
+        <v>0.002602778775881444</v>
       </c>
       <c r="AB5">
-        <v>0.05678368402653941</v>
+        <v>0.05710485747763613</v>
       </c>
       <c r="AC5">
-        <v>-0.05701870663519214</v>
+        <v>-0.05450207870175469</v>
       </c>
       <c r="AD5">
-        <v>424726</v>
+        <v>5198.6</v>
       </c>
       <c r="AE5">
-        <v>5113.885919543199</v>
+        <v>276.0795945867659</v>
       </c>
       <c r="AF5">
-        <v>429839.8859195432</v>
+        <v>5474.679594586766</v>
       </c>
       <c r="AG5">
-        <v>338755.8859195432</v>
+        <v>4773.279594586767</v>
       </c>
       <c r="AH5">
-        <v>0.6797184782776569</v>
+        <v>0.6409521364490983</v>
       </c>
       <c r="AI5">
-        <v>0.8041742408670878</v>
+        <v>0.7941131980671482</v>
       </c>
       <c r="AJ5">
-        <v>0.6258245632863225</v>
+        <v>0.6088305019100199</v>
       </c>
       <c r="AK5">
-        <v>0.7639498115164089</v>
+        <v>0.7707938900567782</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1089,10 +1098,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>465.1982475355969</v>
+        <v>68.13368283093054</v>
       </c>
       <c r="AP5">
-        <v>371.036019627101</v>
+        <v>62.55936559091437</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc. (NYSE:JEF)</t>
+          <t>Raymond James Financial, Inc. (NYSE:RJF)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1111,6 +1120,15 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.107</v>
+      </c>
+      <c r="E6">
+        <v>0.149</v>
+      </c>
+      <c r="F6">
+        <v>0.163</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1118,91 +1136,91 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.0003052647055622531</v>
+        <v>0.001945889456898755</v>
       </c>
       <c r="J6">
-        <v>-0.0002185166822402725</v>
+        <v>0.001522549904224981</v>
       </c>
       <c r="K6">
-        <v>583.2</v>
+        <v>2068</v>
       </c>
       <c r="L6">
-        <v>0.09330304290788084</v>
+        <v>0.1616003750879112</v>
       </c>
       <c r="M6">
-        <v>305.275</v>
+        <v>1351.2</v>
       </c>
       <c r="N6">
-        <v>0.01894811651594242</v>
+        <v>0.04263227141788902</v>
       </c>
       <c r="O6">
-        <v>0.5234482167352537</v>
+        <v>0.6533849129593811</v>
       </c>
       <c r="P6">
-        <v>256.875</v>
+        <v>367.2</v>
       </c>
       <c r="Q6">
-        <v>0.01594397651308725</v>
+        <v>0.01158567944393787</v>
       </c>
       <c r="R6">
-        <v>0.4404578189300411</v>
+        <v>0.1775628626692456</v>
       </c>
       <c r="S6">
-        <v>48.39999999999998</v>
+        <v>984</v>
       </c>
       <c r="T6">
-        <v>0.1585455736630906</v>
+        <v>0.7282415630550622</v>
       </c>
       <c r="U6">
-        <v>10573.5</v>
+        <v>10998</v>
       </c>
       <c r="V6">
-        <v>0.656286659508041</v>
+        <v>0.347002457855198</v>
       </c>
       <c r="W6">
-        <v>0.06013115024539119</v>
+        <v>0.2040453872718303</v>
       </c>
       <c r="X6">
-        <v>0.08582630432810423</v>
+        <v>0.06445379578727985</v>
       </c>
       <c r="Y6">
-        <v>-0.02569515408271304</v>
+        <v>0.1395915914845505</v>
       </c>
       <c r="Z6">
-        <v>0.2442100194120272</v>
+        <v>3.243448256047074</v>
       </c>
       <c r="AA6">
-        <v>-5.336396321174872E-05</v>
+        <v>0.004938311831603154</v>
       </c>
       <c r="AB6">
-        <v>0.05826279867723504</v>
+        <v>0.06144979489928273</v>
       </c>
       <c r="AC6">
-        <v>-0.05831616264044678</v>
+        <v>-0.05651148306767957</v>
       </c>
       <c r="AD6">
-        <v>29280.3</v>
+        <v>4251</v>
       </c>
       <c r="AE6">
-        <v>498.0404378429371</v>
+        <v>515.4922631003332</v>
       </c>
       <c r="AF6">
-        <v>29778.34043784294</v>
+        <v>4766.492263100333</v>
       </c>
       <c r="AG6">
-        <v>19204.84043784294</v>
+        <v>-6231.507736899667</v>
       </c>
       <c r="AH6">
-        <v>0.6489148735247181</v>
+        <v>0.1307292564765302</v>
       </c>
       <c r="AI6">
-        <v>0.7464339401982875</v>
+        <v>0.2900474340322043</v>
       </c>
       <c r="AJ6">
-        <v>0.5438009068920026</v>
+        <v>-0.244729944481781</v>
       </c>
       <c r="AK6">
-        <v>0.6549938934163267</v>
+        <v>-1.146447724560884</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1211,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>299.6960081883316</v>
+        <v>33.2109375</v>
       </c>
       <c r="AP6">
-        <v>196.5695029461918</v>
+        <v>-48.68365419452865</v>
       </c>
     </row>
     <row r="7">
@@ -1225,7 +1243,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Charles Schwab Corporation (NYSE:SCHW)</t>
+          <t>The Goldman Sachs Group, Inc. (NYSE:GS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1234,13 +1252,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.117</v>
+        <v>0.0793</v>
       </c>
       <c r="E7">
-        <v>0.0633</v>
+        <v>0.0602</v>
       </c>
       <c r="F7">
-        <v>0.206</v>
+        <v>0.198</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1249,91 +1267,91 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.003530696868322288</v>
+        <v>-0.002300589176985216</v>
       </c>
       <c r="J7">
-        <v>0.002761357967065008</v>
+        <v>-0.001819219959168574</v>
       </c>
       <c r="K7">
-        <v>5147</v>
+        <v>12173</v>
       </c>
       <c r="L7">
-        <v>0.2747117847993168</v>
+        <v>0.2464818676979772</v>
       </c>
       <c r="M7">
-        <v>1838</v>
+        <v>12051.96</v>
       </c>
       <c r="N7">
-        <v>0.01356663817525026</v>
+        <v>0.06393066692977416</v>
       </c>
       <c r="O7">
-        <v>0.3571012240139887</v>
+        <v>0.9900566828226401</v>
       </c>
       <c r="P7">
-        <v>1838</v>
+        <v>3719.96</v>
       </c>
       <c r="Q7">
-        <v>0.01356663817525026</v>
+        <v>0.01973285040375862</v>
       </c>
       <c r="R7">
-        <v>0.3571012240139887</v>
+        <v>0.3055910621868069</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>8332</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.6913398318613736</v>
       </c>
       <c r="U7">
-        <v>34850</v>
+        <v>154689</v>
       </c>
       <c r="V7">
-        <v>0.2572346792206048</v>
+        <v>0.8205612146654848</v>
       </c>
       <c r="W7">
-        <v>0.1800090931346833</v>
+        <v>0.1147595075136226</v>
       </c>
       <c r="X7">
-        <v>0.06897439397335797</v>
+        <v>0.1120310998794973</v>
       </c>
       <c r="Y7">
-        <v>0.1110346991613253</v>
+        <v>0.002728407634125296</v>
       </c>
       <c r="Z7">
-        <v>0.2953470031936457</v>
+        <v>0.09536727200126356</v>
       </c>
       <c r="AA7">
-        <v>0.0008155588003175479</v>
+        <v>-0.000173494044676157</v>
       </c>
       <c r="AB7">
-        <v>0.05970133105682467</v>
+        <v>0.05643080126213081</v>
       </c>
       <c r="AC7">
-        <v>-0.05888577225650712</v>
+        <v>-0.05660429530680696</v>
       </c>
       <c r="AD7">
-        <v>68104</v>
+        <v>739559</v>
       </c>
       <c r="AE7">
-        <v>824.244317375568</v>
+        <v>2193.095988418844</v>
       </c>
       <c r="AF7">
-        <v>68928.24431737557</v>
+        <v>741752.0959884188</v>
       </c>
       <c r="AG7">
-        <v>34078.24431737557</v>
+        <v>587063.0959884188</v>
       </c>
       <c r="AH7">
-        <v>0.3372097190766186</v>
+        <v>0.7973529560475838</v>
       </c>
       <c r="AI7">
-        <v>0.593476139938202</v>
+        <v>0.8591168216448826</v>
       </c>
       <c r="AJ7">
-        <v>0.2009832376155711</v>
+        <v>0.7569350738453601</v>
       </c>
       <c r="AK7">
-        <v>0.4192014306174235</v>
+        <v>0.8283660455409509</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1342,10 +1360,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>294.8225108225108</v>
+        <v>2275.566153846154</v>
       </c>
       <c r="AP7">
-        <v>147.524867174786</v>
+        <v>1806.347987656673</v>
       </c>
     </row>
     <row r="8">
@@ -1356,7 +1374,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BGC Group, Inc. (NasdaqGS:BGC)</t>
+          <t>Interactive Brokers Group, Inc. (NasdaqGS:IBKR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1365,103 +1383,106 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.009090000000000001</v>
+        <v>0.201</v>
       </c>
       <c r="E8">
-        <v>0.171</v>
+        <v>0.343</v>
+      </c>
+      <c r="F8">
+        <v>0.187</v>
       </c>
       <c r="G8">
-        <v>0.01939045102849594</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.001078122801817872</v>
+        <v>0.001509047307748019</v>
       </c>
       <c r="J8">
-        <v>0.0007345052477814848</v>
+        <v>0.001381228261802206</v>
       </c>
       <c r="K8">
-        <v>121.7</v>
+        <v>698</v>
       </c>
       <c r="L8">
-        <v>0.05741649367805247</v>
+        <v>0.1412097916245195</v>
       </c>
       <c r="M8">
-        <v>382.5</v>
+        <v>130</v>
       </c>
       <c r="N8">
-        <v>0.08797755134898913</v>
+        <v>0.006758267180294972</v>
       </c>
       <c r="O8">
-        <v>3.142974527526705</v>
+        <v>0.1862464183381089</v>
       </c>
       <c r="P8">
-        <v>29.6</v>
+        <v>76</v>
       </c>
       <c r="Q8">
-        <v>0.006808197437725694</v>
+        <v>0.003950986966941676</v>
       </c>
       <c r="R8">
-        <v>0.2432210353327856</v>
+        <v>0.1088825214899714</v>
       </c>
       <c r="S8">
-        <v>352.9</v>
+        <v>54</v>
       </c>
       <c r="T8">
-        <v>0.9226143790849672</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="U8">
-        <v>563.5</v>
+        <v>3595</v>
       </c>
       <c r="V8">
-        <v>0.129608758654001</v>
+        <v>0.1868920808704648</v>
       </c>
       <c r="W8">
-        <v>0.1441772301859969</v>
+        <v>0.2058997050147493</v>
       </c>
       <c r="X8">
-        <v>0.06718293266622437</v>
+        <v>0.07377718442634409</v>
       </c>
       <c r="Y8">
-        <v>0.07699429751977256</v>
+        <v>0.1321225205884052</v>
       </c>
       <c r="Z8">
-        <v>1.8945737893962</v>
+        <v>0.4828231066570664</v>
       </c>
       <c r="AA8">
-        <v>0.001391574390620763</v>
+        <v>0.0006668889203658809</v>
       </c>
       <c r="AB8">
-        <v>0.06119469841826738</v>
+        <v>0.0573107310542767</v>
       </c>
       <c r="AC8">
-        <v>-0.05980312402764662</v>
+        <v>-0.05664384213391083</v>
       </c>
       <c r="AD8">
-        <v>1446.3</v>
+        <v>17025</v>
       </c>
       <c r="AE8">
-        <v>146.5740545463342</v>
+        <v>132.7038957890077</v>
       </c>
       <c r="AF8">
-        <v>1592.874054546334</v>
+        <v>17157.70389578901</v>
       </c>
       <c r="AG8">
-        <v>1029.374054546334</v>
+        <v>13562.70389578901</v>
       </c>
       <c r="AH8">
-        <v>0.2681347021214733</v>
+        <v>0.4714509240443509</v>
       </c>
       <c r="AI8">
-        <v>0.6042829032399094</v>
+        <v>0.5173795221796643</v>
       </c>
       <c r="AJ8">
-        <v>0.1914375818715004</v>
+        <v>0.4135171924488169</v>
       </c>
       <c r="AK8">
-        <v>0.4966885121134435</v>
+        <v>0.4586999363762091</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1470,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="AN8">
-        <v>45.76898734177215</v>
+        <v>500.7352941176471</v>
       </c>
       <c r="AP8">
-        <v>32.5751283084283</v>
+        <v>398.9030557585002</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1505,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>StoneX Group Inc. (NasdaqGS:SNEX)</t>
+          <t>Morgan Stanley (NYSE:MS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1493,10 +1514,13 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.247</v>
+        <v>0.08310000000000001</v>
       </c>
       <c r="E9">
-        <v>0.251</v>
+        <v>0.0608</v>
+      </c>
+      <c r="F9">
+        <v>0.135</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1505,91 +1529,91 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>-6.372142974404654E-05</v>
+        <v>-0.001883552107145254</v>
       </c>
       <c r="J9">
-        <v>-4.693179575613482E-05</v>
+        <v>-0.001445338983340326</v>
       </c>
       <c r="K9">
-        <v>260.8</v>
+        <v>11193</v>
       </c>
       <c r="L9">
-        <v>0.002642235444656413</v>
+        <v>0.192049003122748</v>
       </c>
       <c r="M9">
-        <v>2.3</v>
+        <v>10408.05</v>
       </c>
       <c r="N9">
-        <v>0.000735270611553339</v>
+        <v>0.05138777936539755</v>
       </c>
       <c r="O9">
-        <v>0.008819018404907975</v>
+        <v>0.9298713481640311</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>5719.049999999999</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.02823672826126669</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.5109488072902706</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>4689</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>0.4505166673872628</v>
       </c>
       <c r="U9">
-        <v>1269</v>
+        <v>91084</v>
       </c>
       <c r="V9">
-        <v>0.4056775678526902</v>
+        <v>0.4497100317271603</v>
       </c>
       <c r="W9">
-        <v>0.1891088390979625</v>
+        <v>0.1237328793623772</v>
       </c>
       <c r="X9">
-        <v>0.1089124232937355</v>
+        <v>0.08924463838963392</v>
       </c>
       <c r="Y9">
-        <v>0.08019641580422701</v>
+        <v>0.03448824097274324</v>
       </c>
       <c r="Z9">
-        <v>14.09105673341216</v>
+        <v>0.162607257786381</v>
       </c>
       <c r="AA9">
-        <v>-0.0006613185966006074</v>
+        <v>-0.0002350226086527261</v>
       </c>
       <c r="AB9">
-        <v>0.06336546228722187</v>
+        <v>0.05677473247555802</v>
       </c>
       <c r="AC9">
-        <v>-0.06402678088382248</v>
+        <v>-0.05700975508421074</v>
       </c>
       <c r="AD9">
-        <v>11344.1</v>
+        <v>424726</v>
       </c>
       <c r="AE9">
-        <v>177.9478955894265</v>
+        <v>5113.885919543199</v>
       </c>
       <c r="AF9">
-        <v>11522.04789558943</v>
+        <v>429839.8859195432</v>
       </c>
       <c r="AG9">
-        <v>10253.04789558943</v>
+        <v>338755.8859195432</v>
       </c>
       <c r="AH9">
-        <v>0.7864799712403077</v>
+        <v>0.6797184782776569</v>
       </c>
       <c r="AI9">
-        <v>0.8708275341272752</v>
+        <v>0.8041742408670878</v>
       </c>
       <c r="AJ9">
-        <v>0.7662308178335689</v>
+        <v>0.6258245632863225</v>
       </c>
       <c r="AK9">
-        <v>0.8571243212408229</v>
+        <v>0.7639498115164089</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1598,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>387.1706484641638</v>
+        <v>465.1982475355969</v>
       </c>
       <c r="AP9">
-        <v>349.9333752760896</v>
+        <v>371.036019627101</v>
       </c>
     </row>
     <row r="10">
@@ -1612,124 +1636,2383 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>Siebert Financial Corp. (NasdaqCM:SIEB)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.169</v>
+      </c>
+      <c r="E10">
+        <v>0.0373</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0.004071029095294509</v>
+      </c>
+      <c r="J10">
+        <v>0.00301817674306317</v>
+      </c>
+      <c r="K10">
+        <v>10.7</v>
+      </c>
+      <c r="L10">
+        <v>0.1282973621103117</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>4.44</v>
+      </c>
+      <c r="V10">
+        <v>0.03501577287066247</v>
+      </c>
+      <c r="W10">
+        <v>0.1515580736543909</v>
+      </c>
+      <c r="X10">
+        <v>0.08633860271097149</v>
+      </c>
+      <c r="Y10">
+        <v>0.06521947094341946</v>
+      </c>
+      <c r="Z10">
+        <v>0.1739774824930796</v>
+      </c>
+      <c r="AA10">
+        <v>0.0005250947914772929</v>
+      </c>
+      <c r="AB10">
+        <v>0.058219252903881</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05769415811240371</v>
+      </c>
+      <c r="AD10">
+        <v>236.8</v>
+      </c>
+      <c r="AE10">
+        <v>2.992380867262189</v>
+      </c>
+      <c r="AF10">
+        <v>239.7923808672622</v>
+      </c>
+      <c r="AG10">
+        <v>235.3523808672622</v>
+      </c>
+      <c r="AH10">
+        <v>0.6541117420388711</v>
+      </c>
+      <c r="AI10">
+        <v>0.7421790022519207</v>
+      </c>
+      <c r="AJ10">
+        <v>0.6498711407161083</v>
+      </c>
+      <c r="AK10">
+        <v>0.7385866072197985</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>252.452025586354</v>
+      </c>
+      <c r="AP10">
+        <v>250.9087216068894</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Piper Sandler Companies (NYSE:PIPR)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.145</v>
+      </c>
+      <c r="E11">
+        <v>0.125</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0.003201249539263956</v>
+      </c>
+      <c r="J11">
+        <v>0.002443096789307701</v>
+      </c>
+      <c r="K11">
+        <v>164.1</v>
+      </c>
+      <c r="L11">
+        <v>0.1084098566426637</v>
+      </c>
+      <c r="M11">
+        <v>114.4</v>
+      </c>
+      <c r="N11">
+        <v>0.02392304475115015</v>
+      </c>
+      <c r="O11">
+        <v>0.6971358927483242</v>
+      </c>
+      <c r="P11">
+        <v>51.4</v>
+      </c>
+      <c r="Q11">
+        <v>0.01074864073609368</v>
+      </c>
+      <c r="R11">
+        <v>0.3132236441194394</v>
+      </c>
+      <c r="S11">
+        <v>63.00000000000001</v>
+      </c>
+      <c r="T11">
+        <v>0.5506993006993007</v>
+      </c>
+      <c r="U11">
+        <v>350.2</v>
+      </c>
+      <c r="V11">
+        <v>0.07323295692179005</v>
+      </c>
+      <c r="W11">
+        <v>0.1586426914153132</v>
+      </c>
+      <c r="X11">
+        <v>0.06289214060559978</v>
+      </c>
+      <c r="Y11">
+        <v>0.09575055080971343</v>
+      </c>
+      <c r="Z11">
+        <v>1.662728085487772</v>
+      </c>
+      <c r="AA11">
+        <v>0.004062205647146918</v>
+      </c>
+      <c r="AB11">
+        <v>0.06234583560368286</v>
+      </c>
+      <c r="AC11">
+        <v>-0.05828362995653594</v>
+      </c>
+      <c r="AD11">
+        <v>22.9</v>
+      </c>
+      <c r="AE11">
+        <v>102.2713428620808</v>
+      </c>
+      <c r="AF11">
+        <v>125.1713428620808</v>
+      </c>
+      <c r="AG11">
+        <v>-225.0286571379192</v>
+      </c>
+      <c r="AH11">
+        <v>0.02550784028443467</v>
+      </c>
+      <c r="AI11">
+        <v>0.08416173918957053</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.0493811876808043</v>
+      </c>
+      <c r="AK11">
+        <v>-0.1979019685532729</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0.9051383399209485</v>
+      </c>
+      <c r="AP11">
+        <v>-8.894413325609456</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jefferies Financial Group Inc. (NYSE:JEF)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>-0.0003052647055622531</v>
+      </c>
+      <c r="J12">
+        <v>-0.0002185166822402725</v>
+      </c>
+      <c r="K12">
+        <v>583.2</v>
+      </c>
+      <c r="L12">
+        <v>0.09330304290788084</v>
+      </c>
+      <c r="M12">
+        <v>305.275</v>
+      </c>
+      <c r="N12">
+        <v>0.01894811651594242</v>
+      </c>
+      <c r="O12">
+        <v>0.5234482167352537</v>
+      </c>
+      <c r="P12">
+        <v>256.875</v>
+      </c>
+      <c r="Q12">
+        <v>0.01594397651308725</v>
+      </c>
+      <c r="R12">
+        <v>0.4404578189300411</v>
+      </c>
+      <c r="S12">
+        <v>48.39999999999998</v>
+      </c>
+      <c r="T12">
+        <v>0.1585455736630906</v>
+      </c>
+      <c r="U12">
+        <v>10573.5</v>
+      </c>
+      <c r="V12">
+        <v>0.656286659508041</v>
+      </c>
+      <c r="W12">
+        <v>0.06013115024539119</v>
+      </c>
+      <c r="X12">
+        <v>0.08580057097318124</v>
+      </c>
+      <c r="Y12">
+        <v>-0.02566942072779004</v>
+      </c>
+      <c r="Z12">
+        <v>0.2442100194120272</v>
+      </c>
+      <c r="AA12">
+        <v>-5.336396321174872E-05</v>
+      </c>
+      <c r="AB12">
+        <v>0.05825376407906727</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05830712804227901</v>
+      </c>
+      <c r="AD12">
+        <v>29280.3</v>
+      </c>
+      <c r="AE12">
+        <v>498.0404378429371</v>
+      </c>
+      <c r="AF12">
+        <v>29778.34043784294</v>
+      </c>
+      <c r="AG12">
+        <v>19204.84043784294</v>
+      </c>
+      <c r="AH12">
+        <v>0.6489148735247181</v>
+      </c>
+      <c r="AI12">
+        <v>0.7464339401982875</v>
+      </c>
+      <c r="AJ12">
+        <v>0.5438009068920026</v>
+      </c>
+      <c r="AK12">
+        <v>0.6549938934163267</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>299.6960081883316</v>
+      </c>
+      <c r="AP12">
+        <v>196.5695029461918</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>The Charles Schwab Corporation (NYSE:SCHW)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.117</v>
+      </c>
+      <c r="E13">
+        <v>0.0633</v>
+      </c>
+      <c r="F13">
+        <v>0.206</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0.003530696868322288</v>
+      </c>
+      <c r="J13">
+        <v>0.002761357967065008</v>
+      </c>
+      <c r="K13">
+        <v>5147</v>
+      </c>
+      <c r="L13">
+        <v>0.2747117847993168</v>
+      </c>
+      <c r="M13">
+        <v>1838</v>
+      </c>
+      <c r="N13">
+        <v>0.01356663817525026</v>
+      </c>
+      <c r="O13">
+        <v>0.3571012240139887</v>
+      </c>
+      <c r="P13">
+        <v>1838</v>
+      </c>
+      <c r="Q13">
+        <v>0.01356663817525026</v>
+      </c>
+      <c r="R13">
+        <v>0.3571012240139887</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>34850</v>
+      </c>
+      <c r="V13">
+        <v>0.2572346792206048</v>
+      </c>
+      <c r="W13">
+        <v>0.1800090931346833</v>
+      </c>
+      <c r="X13">
+        <v>0.06895949489848077</v>
+      </c>
+      <c r="Y13">
+        <v>0.1110495982362025</v>
+      </c>
+      <c r="Z13">
+        <v>0.2953470031936457</v>
+      </c>
+      <c r="AA13">
+        <v>0.0008155588003175479</v>
+      </c>
+      <c r="AB13">
+        <v>0.05969145609480132</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05887589729448377</v>
+      </c>
+      <c r="AD13">
+        <v>68104</v>
+      </c>
+      <c r="AE13">
+        <v>824.244317375568</v>
+      </c>
+      <c r="AF13">
+        <v>68928.24431737557</v>
+      </c>
+      <c r="AG13">
+        <v>34078.24431737557</v>
+      </c>
+      <c r="AH13">
+        <v>0.3372097190766186</v>
+      </c>
+      <c r="AI13">
+        <v>0.593476139938202</v>
+      </c>
+      <c r="AJ13">
+        <v>0.2009832376155711</v>
+      </c>
+      <c r="AK13">
+        <v>0.4192014306174235</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>294.8225108225108</v>
+      </c>
+      <c r="AP13">
+        <v>147.524867174786</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BGC Group, Inc. (NasdaqGS:BGC)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.009090000000000001</v>
+      </c>
+      <c r="E14">
+        <v>0.171</v>
+      </c>
+      <c r="G14">
+        <v>0.01939045102849594</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0.001078122801817872</v>
+      </c>
+      <c r="J14">
+        <v>0.0007345052477814848</v>
+      </c>
+      <c r="K14">
+        <v>121.7</v>
+      </c>
+      <c r="L14">
+        <v>0.05741649367805247</v>
+      </c>
+      <c r="M14">
+        <v>382.5</v>
+      </c>
+      <c r="N14">
+        <v>0.08797755134898913</v>
+      </c>
+      <c r="O14">
+        <v>3.142974527526705</v>
+      </c>
+      <c r="P14">
+        <v>29.6</v>
+      </c>
+      <c r="Q14">
+        <v>0.006808197437725694</v>
+      </c>
+      <c r="R14">
+        <v>0.2432210353327856</v>
+      </c>
+      <c r="S14">
+        <v>352.9</v>
+      </c>
+      <c r="T14">
+        <v>0.9226143790849672</v>
+      </c>
+      <c r="U14">
+        <v>563.5</v>
+      </c>
+      <c r="V14">
+        <v>0.129608758654001</v>
+      </c>
+      <c r="W14">
+        <v>0.1441772301859969</v>
+      </c>
+      <c r="X14">
+        <v>0.06716918534168789</v>
+      </c>
+      <c r="Y14">
+        <v>0.07700804484430904</v>
+      </c>
+      <c r="Z14">
+        <v>1.8945737893962</v>
+      </c>
+      <c r="AA14">
+        <v>0.001391574390620763</v>
+      </c>
+      <c r="AB14">
+        <v>0.06118463722850045</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05979306283787969</v>
+      </c>
+      <c r="AD14">
+        <v>1446.3</v>
+      </c>
+      <c r="AE14">
+        <v>146.5740545463342</v>
+      </c>
+      <c r="AF14">
+        <v>1592.874054546334</v>
+      </c>
+      <c r="AG14">
+        <v>1029.374054546334</v>
+      </c>
+      <c r="AH14">
+        <v>0.2681347021214733</v>
+      </c>
+      <c r="AI14">
+        <v>0.6042829032399094</v>
+      </c>
+      <c r="AJ14">
+        <v>0.1914375818715004</v>
+      </c>
+      <c r="AK14">
+        <v>0.4966885121134435</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>45.76898734177215</v>
+      </c>
+      <c r="AP14">
+        <v>32.5751283084283</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Robinhood Markets, Inc. (NasdaqGS:HOOD)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="F15">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G15">
+        <v>0.3351328903654485</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0.001917930822384677</v>
+      </c>
+      <c r="J15">
+        <v>0.001882081648134496</v>
+      </c>
+      <c r="K15">
+        <v>525</v>
+      </c>
+      <c r="L15">
+        <v>0.2180232558139535</v>
+      </c>
+      <c r="M15">
+        <v>255</v>
+      </c>
+      <c r="N15">
+        <v>0.007742076516004845</v>
+      </c>
+      <c r="O15">
+        <v>0.4857142857142857</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>255</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>4611</v>
+      </c>
+      <c r="V15">
+        <v>0.1399949600599935</v>
+      </c>
+      <c r="W15">
+        <v>0.07986005476118041</v>
+      </c>
+      <c r="X15">
+        <v>0.06539644057507328</v>
+      </c>
+      <c r="Y15">
+        <v>0.01446361418610713</v>
+      </c>
+      <c r="Z15">
+        <v>0.493148743397224</v>
+      </c>
+      <c r="AA15">
+        <v>0.0009281461997485031</v>
+      </c>
+      <c r="AB15">
+        <v>0.06134169625747218</v>
+      </c>
+      <c r="AC15">
+        <v>-0.06041355005772368</v>
+      </c>
+      <c r="AD15">
+        <v>7306</v>
+      </c>
+      <c r="AE15">
+        <v>116.9081128984885</v>
+      </c>
+      <c r="AF15">
+        <v>7422.908112898488</v>
+      </c>
+      <c r="AG15">
+        <v>2811.908112898488</v>
+      </c>
+      <c r="AH15">
+        <v>0.1839183202292337</v>
+      </c>
+      <c r="AI15">
+        <v>0.5073443190005762</v>
+      </c>
+      <c r="AJ15">
+        <v>0.07865739478693071</v>
+      </c>
+      <c r="AK15">
+        <v>0.2806321256857394</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>260.9285714285714</v>
+      </c>
+      <c r="AP15">
+        <v>100.4252897463746</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MDB Capital Holdings, LLC (NasdaqCM:MDBH)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G16">
+        <v>0.6391752577319588</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0.003554530904091422</v>
+      </c>
+      <c r="J16">
+        <v>0.003554530904091422</v>
+      </c>
+      <c r="K16">
+        <v>-24.8</v>
+      </c>
+      <c r="L16">
+        <v>-12.78350515463918</v>
+      </c>
+      <c r="M16">
+        <v>-0</v>
+      </c>
+      <c r="N16">
+        <v>-0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>-0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>16.7</v>
+      </c>
+      <c r="V16">
+        <v>0.2663476874003189</v>
+      </c>
+      <c r="W16">
+        <v>-0.635897435897436</v>
+      </c>
+      <c r="X16">
+        <v>0.06304940770440004</v>
+      </c>
+      <c r="Y16">
+        <v>-0.698946843601836</v>
+      </c>
+      <c r="Z16">
+        <v>0.1139465860854671</v>
+      </c>
+      <c r="AA16">
+        <v>0.0004050266616565063</v>
+      </c>
+      <c r="AB16">
+        <v>0.06231572715500008</v>
+      </c>
+      <c r="AC16">
+        <v>-0.06191070049334358</v>
+      </c>
+      <c r="AD16">
+        <v>0</v>
+      </c>
+      <c r="AE16">
+        <v>2.425521050230313</v>
+      </c>
+      <c r="AF16">
+        <v>2.425521050230313</v>
+      </c>
+      <c r="AG16">
+        <v>-14.27447894976969</v>
+      </c>
+      <c r="AH16">
+        <v>0.03724378724524209</v>
+      </c>
+      <c r="AI16">
+        <v>0.07919933986599299</v>
+      </c>
+      <c r="AJ16">
+        <v>-0.2947718194908673</v>
+      </c>
+      <c r="AK16">
+        <v>-1.025058875591129</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>-1.31</v>
+      </c>
+      <c r="AN16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>-29.01316859709286</v>
+      </c>
+      <c r="AQ16">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lazard, Inc. (NYSE:LAZ)</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>0.0358</v>
+      </c>
+      <c r="E17">
+        <v>-0.0445</v>
+      </c>
+      <c r="F17">
+        <v>0.02</v>
+      </c>
+      <c r="G17">
+        <v>-0.002611977030352748</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>-0.00210589836601581</v>
+      </c>
+      <c r="J17">
+        <v>-0.00167788486378544</v>
+      </c>
+      <c r="K17">
+        <v>257.2</v>
+      </c>
+      <c r="L17">
+        <v>0.08439704675963905</v>
+      </c>
+      <c r="M17">
+        <v>221.4</v>
+      </c>
+      <c r="N17">
+        <v>0.04753725254433805</v>
+      </c>
+      <c r="O17">
+        <v>0.8608087091757388</v>
+      </c>
+      <c r="P17">
+        <v>177.5</v>
+      </c>
+      <c r="Q17">
+        <v>0.03811139262249324</v>
+      </c>
+      <c r="R17">
+        <v>0.6901244167962676</v>
+      </c>
+      <c r="S17">
+        <v>43.90000000000001</v>
+      </c>
+      <c r="T17">
+        <v>0.1982836495031617</v>
+      </c>
+      <c r="U17">
+        <v>1165.7</v>
+      </c>
+      <c r="V17">
+        <v>0.2502898612960021</v>
+      </c>
+      <c r="W17">
+        <v>0.7118737890949349</v>
+      </c>
+      <c r="X17">
+        <v>0.0695531784273945</v>
+      </c>
+      <c r="Y17">
+        <v>0.6423206106675404</v>
+      </c>
+      <c r="Z17">
+        <v>1.702905324231925</v>
+      </c>
+      <c r="AA17">
+        <v>-0.002857279067988384</v>
+      </c>
+      <c r="AB17">
+        <v>0.05952016599471641</v>
+      </c>
+      <c r="AC17">
+        <v>-0.06237744506270479</v>
+      </c>
+      <c r="AD17">
+        <v>2145.9</v>
+      </c>
+      <c r="AE17">
+        <v>443.5886263521659</v>
+      </c>
+      <c r="AF17">
+        <v>2589.488626352166</v>
+      </c>
+      <c r="AG17">
+        <v>1423.788626352166</v>
+      </c>
+      <c r="AH17">
+        <v>0.3573241924728772</v>
+      </c>
+      <c r="AI17">
+        <v>0.772062435157546</v>
+      </c>
+      <c r="AJ17">
+        <v>0.2341299890258844</v>
+      </c>
+      <c r="AK17">
+        <v>0.6506402351163307</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>26.07411907654921</v>
+      </c>
+      <c r="AP17">
+        <v>17.29998330926082</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Armada Mercantile Ltd. (OTCPK:AAMT.F)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>0.0329</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>-0.008</v>
+      </c>
+      <c r="L18">
+        <v>-0.05128205128205128</v>
+      </c>
+      <c r="M18">
+        <v>-0</v>
+      </c>
+      <c r="N18">
+        <v>-0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>-0</v>
+      </c>
+      <c r="Q18">
+        <v>-0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0.316</v>
+      </c>
+      <c r="V18">
+        <v>0.06358148893360162</v>
+      </c>
+      <c r="W18">
+        <v>-0.001851851851851852</v>
+      </c>
+      <c r="X18">
+        <v>0.06342060093391874</v>
+      </c>
+      <c r="Y18">
+        <v>-0.0652724527857706</v>
+      </c>
+      <c r="Z18">
+        <v>0.03643157403082672</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0.06368108620108799</v>
+      </c>
+      <c r="AC18">
+        <v>-0.06368108620108799</v>
+      </c>
+      <c r="AD18">
+        <v>0.339</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0.339</v>
+      </c>
+      <c r="AG18">
+        <v>0.02300000000000002</v>
+      </c>
+      <c r="AH18">
+        <v>0.06385383311358071</v>
+      </c>
+      <c r="AI18">
+        <v>0.06919779546846296</v>
+      </c>
+      <c r="AJ18">
+        <v>0.004606449028640101</v>
+      </c>
+      <c r="AK18">
+        <v>0.005018546803403889</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>StoneX Group Inc. (NasdaqGS:SNEX)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>0.247</v>
+      </c>
+      <c r="E19">
+        <v>0.251</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>-6.372142974404654E-05</v>
+      </c>
+      <c r="J19">
+        <v>-4.693179575613482E-05</v>
+      </c>
+      <c r="K19">
+        <v>260.8</v>
+      </c>
+      <c r="L19">
+        <v>0.002642235444656413</v>
+      </c>
+      <c r="M19">
+        <v>2.3</v>
+      </c>
+      <c r="N19">
+        <v>0.000735270611553339</v>
+      </c>
+      <c r="O19">
+        <v>0.008819018404907975</v>
+      </c>
+      <c r="P19">
+        <v>-0</v>
+      </c>
+      <c r="Q19">
+        <v>-0</v>
+      </c>
+      <c r="R19">
+        <v>-0</v>
+      </c>
+      <c r="S19">
+        <v>2.3</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>1269</v>
+      </c>
+      <c r="V19">
+        <v>0.4056775678526902</v>
+      </c>
+      <c r="W19">
+        <v>0.1891088390979625</v>
+      </c>
+      <c r="X19">
+        <v>0.1088718476169167</v>
+      </c>
+      <c r="Y19">
+        <v>0.08023699148104582</v>
+      </c>
+      <c r="Z19">
+        <v>14.09105673341216</v>
+      </c>
+      <c r="AA19">
+        <v>-0.0006613185966006074</v>
+      </c>
+      <c r="AB19">
+        <v>0.06335679856754058</v>
+      </c>
+      <c r="AC19">
+        <v>-0.06401811716414119</v>
+      </c>
+      <c r="AD19">
+        <v>11344.1</v>
+      </c>
+      <c r="AE19">
+        <v>177.9478955894265</v>
+      </c>
+      <c r="AF19">
+        <v>11522.04789558943</v>
+      </c>
+      <c r="AG19">
+        <v>10253.04789558943</v>
+      </c>
+      <c r="AH19">
+        <v>0.7864799712403077</v>
+      </c>
+      <c r="AI19">
+        <v>0.8708275341272752</v>
+      </c>
+      <c r="AJ19">
+        <v>0.7662308178335689</v>
+      </c>
+      <c r="AK19">
+        <v>0.8571243212408229</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>0</v>
+      </c>
+      <c r="AN19">
+        <v>387.1706484641638</v>
+      </c>
+      <c r="AP19">
+        <v>349.9333752760896</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Stifel Financial Corp. (NYSE:SF)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
-      <c r="D10">
+      <c r="D20">
         <v>0.0819</v>
       </c>
-      <c r="E10">
+      <c r="E20">
         <v>0.0852</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>-0.01388020876510198</v>
       </c>
-      <c r="J10">
+      <c r="J20">
         <v>-0.0103885736645511</v>
       </c>
-      <c r="K10">
+      <c r="K20">
         <v>649.9</v>
       </c>
-      <c r="L10">
+      <c r="L20">
         <v>0.1378249989396446</v>
       </c>
-      <c r="M10">
+      <c r="M20">
         <v>540.8</v>
       </c>
-      <c r="N10">
+      <c r="N20">
         <v>0.04980842911877394</v>
       </c>
-      <c r="O10">
+      <c r="O20">
         <v>0.8321280196953377</v>
       </c>
-      <c r="P10">
+      <c r="P20">
         <v>184</v>
       </c>
-      <c r="Q10">
+      <c r="Q20">
         <v>0.01694665487768936</v>
       </c>
-      <c r="R10">
+      <c r="R20">
         <v>0.2831204800738575</v>
       </c>
-      <c r="S10">
+      <c r="S20">
         <v>356.8</v>
       </c>
-      <c r="T10">
+      <c r="T20">
         <v>0.6597633136094674</v>
       </c>
-      <c r="U10">
+      <c r="U20">
         <v>1915.8</v>
       </c>
-      <c r="V10">
+      <c r="V20">
         <v>0.17644783377542</v>
       </c>
-      <c r="W10">
+      <c r="W20">
         <v>0.142596980867123</v>
       </c>
-      <c r="X10">
-        <v>0.06522076709708409</v>
-      </c>
-      <c r="Y10">
-        <v>0.07737621377003893</v>
-      </c>
-      <c r="Z10">
+      <c r="X20">
+        <v>0.06520828127055138</v>
+      </c>
+      <c r="Y20">
+        <v>0.07738869959657164</v>
+      </c>
+      <c r="Z20">
         <v>1.281305186517961</v>
       </c>
-      <c r="AA10">
+      <c r="AA20">
         <v>-0.01331093331691323</v>
       </c>
-      <c r="AB10">
-        <v>0.06141902076176665</v>
-      </c>
-      <c r="AC10">
-        <v>-0.07472995407867988</v>
-      </c>
-      <c r="AD10">
+      <c r="AB20">
+        <v>0.06140870531842414</v>
+      </c>
+      <c r="AC20">
+        <v>-0.07471963863533737</v>
+      </c>
+      <c r="AD20">
         <v>1429.7</v>
       </c>
-      <c r="AE10">
+      <c r="AE20">
         <v>854.7536820548094</v>
       </c>
-      <c r="AF10">
+      <c r="AF20">
         <v>2284.453682054809</v>
       </c>
-      <c r="AG10">
+      <c r="AG20">
         <v>368.6536820548092</v>
       </c>
-      <c r="AH10">
+      <c r="AH20">
         <v>0.1738277545749323</v>
       </c>
-      <c r="AI10">
+      <c r="AI20">
         <v>0.2913266649290078</v>
       </c>
-      <c r="AJ10">
+      <c r="AJ20">
         <v>0.03283853122294064</v>
       </c>
-      <c r="AK10">
+      <c r="AK20">
         <v>0.06221211711367915</v>
       </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-      <c r="AN10">
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
         <v>13.55165876777251</v>
       </c>
-      <c r="AP10">
+      <c r="AP20">
         <v>3.494347697201983</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Evercore Inc. (NYSE:EVR)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>0.0564</v>
+      </c>
+      <c r="E21">
+        <v>-0.0205</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>-0.01617279154340704</v>
+      </c>
+      <c r="J21">
+        <v>-0.01306929432713294</v>
+      </c>
+      <c r="K21">
+        <v>320.6</v>
+      </c>
+      <c r="L21">
+        <v>0.1149474740955864</v>
+      </c>
+      <c r="M21">
+        <v>557</v>
+      </c>
+      <c r="N21">
+        <v>0.05278470096566626</v>
+      </c>
+      <c r="O21">
+        <v>1.737367436057392</v>
+      </c>
+      <c r="P21">
+        <v>133.8</v>
+      </c>
+      <c r="Q21">
+        <v>0.01267970016015466</v>
+      </c>
+      <c r="R21">
+        <v>0.4173424828446662</v>
+      </c>
+      <c r="S21">
+        <v>423.2</v>
+      </c>
+      <c r="T21">
+        <v>0.7597845601436265</v>
+      </c>
+      <c r="U21">
+        <v>533.1</v>
+      </c>
+      <c r="V21">
+        <v>0.05051979189371038</v>
+      </c>
+      <c r="W21">
+        <v>0.2206773127753304</v>
+      </c>
+      <c r="X21">
+        <v>0.06356199126466308</v>
+      </c>
+      <c r="Y21">
+        <v>0.1571153215106673</v>
+      </c>
+      <c r="Z21">
+        <v>1.668483583065628</v>
+      </c>
+      <c r="AA21">
+        <v>-0.02180590302707405</v>
+      </c>
+      <c r="AB21">
+        <v>0.06193623480212532</v>
+      </c>
+      <c r="AC21">
+        <v>-0.08374213782919937</v>
+      </c>
+      <c r="AD21">
+        <v>375.9</v>
+      </c>
+      <c r="AE21">
+        <v>462.5376644685829</v>
+      </c>
+      <c r="AF21">
+        <v>838.4376644685829</v>
+      </c>
+      <c r="AG21">
+        <v>305.3376644685828</v>
+      </c>
+      <c r="AH21">
+        <v>0.07360696814956443</v>
+      </c>
+      <c r="AI21">
+        <v>0.3202053177915715</v>
+      </c>
+      <c r="AJ21">
+        <v>0.02812192429922345</v>
+      </c>
+      <c r="AK21">
+        <v>0.1464212101815145</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>7.930379746835443</v>
+      </c>
+      <c r="AP21">
+        <v>6.441722879084026</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Moelis &amp; Company (NYSE:MC)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>0.0498</v>
+      </c>
+      <c r="E22">
+        <v>-0.197</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>-0.01710244746902815</v>
+      </c>
+      <c r="J22">
+        <v>-0.01424259069151847</v>
+      </c>
+      <c r="K22">
+        <v>41</v>
+      </c>
+      <c r="L22">
+        <v>0.04223756052333368</v>
+      </c>
+      <c r="M22">
+        <v>189.5</v>
+      </c>
+      <c r="N22">
+        <v>0.03633679124081993</v>
+      </c>
+      <c r="O22">
+        <v>4.621951219512195</v>
+      </c>
+      <c r="P22">
+        <v>178.3</v>
+      </c>
+      <c r="Q22">
+        <v>0.03418918141550498</v>
+      </c>
+      <c r="R22">
+        <v>4.348780487804878</v>
+      </c>
+      <c r="S22">
+        <v>11.19999999999999</v>
+      </c>
+      <c r="T22">
+        <v>0.05910290237467013</v>
+      </c>
+      <c r="U22">
+        <v>145.3</v>
+      </c>
+      <c r="V22">
+        <v>0.02786140246591628</v>
+      </c>
+      <c r="W22">
+        <v>0.1116861890493054</v>
+      </c>
+      <c r="X22">
+        <v>0.06305606848387176</v>
+      </c>
+      <c r="Y22">
+        <v>0.0486301205654336</v>
+      </c>
+      <c r="Z22">
+        <v>2.288810655674661</v>
+      </c>
+      <c r="AA22">
+        <v>-0.03259859333916022</v>
+      </c>
+      <c r="AB22">
+        <v>0.06224171535082917</v>
+      </c>
+      <c r="AC22">
+        <v>-0.09484030868998938</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>204.5067287909282</v>
+      </c>
+      <c r="AF22">
+        <v>204.5067287909282</v>
+      </c>
+      <c r="AG22">
+        <v>59.20672879092814</v>
+      </c>
+      <c r="AH22">
+        <v>0.03773460677589645</v>
+      </c>
+      <c r="AI22">
+        <v>0.3410681017594716</v>
+      </c>
+      <c r="AJ22">
+        <v>0.01122549973586776</v>
+      </c>
+      <c r="AK22">
+        <v>0.1303232486749609</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>2.436490896746014</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>B. Riley Financial, Inc. (NasdaqGM:RILY)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>0.247</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0.00579484763817963</v>
+      </c>
+      <c r="J23">
+        <v>0.00579484763817963</v>
+      </c>
+      <c r="K23">
+        <v>-166.2</v>
+      </c>
+      <c r="L23">
+        <v>-0.1360288099525291</v>
+      </c>
+      <c r="M23">
+        <v>129.9</v>
+      </c>
+      <c r="N23">
+        <v>0.9338605319913732</v>
+      </c>
+      <c r="O23">
+        <v>-0.7815884476534297</v>
+      </c>
+      <c r="P23">
+        <v>110.3</v>
+      </c>
+      <c r="Q23">
+        <v>0.7929547088425594</v>
+      </c>
+      <c r="R23">
+        <v>-0.6636582430806258</v>
+      </c>
+      <c r="S23">
+        <v>19.60000000000001</v>
+      </c>
+      <c r="T23">
+        <v>0.1508852963818322</v>
+      </c>
+      <c r="U23">
+        <v>190.7</v>
+      </c>
+      <c r="V23">
+        <v>1.370956146657081</v>
+      </c>
+      <c r="W23">
+        <v>-0.4359916054564533</v>
+      </c>
+      <c r="X23">
+        <v>0.4524034237368866</v>
+      </c>
+      <c r="Y23">
+        <v>-0.8883950291933399</v>
+      </c>
+      <c r="Z23">
+        <v>0.2358824199917279</v>
+      </c>
+      <c r="AA23">
+        <v>0.00136690268437716</v>
+      </c>
+      <c r="AB23">
+        <v>0.1003051152135798</v>
+      </c>
+      <c r="AC23">
+        <v>-0.0989382125292026</v>
+      </c>
+      <c r="AD23">
+        <v>4227.6</v>
+      </c>
+      <c r="AE23">
+        <v>85.59927577836064</v>
+      </c>
+      <c r="AF23">
+        <v>4313.199275778361</v>
+      </c>
+      <c r="AG23">
+        <v>4122.499275778361</v>
+      </c>
+      <c r="AH23">
+        <v>0.9687577156466683</v>
+      </c>
+      <c r="AI23">
+        <v>0.9350300142962845</v>
+      </c>
+      <c r="AJ23">
+        <v>0.9673596715696375</v>
+      </c>
+      <c r="AK23">
+        <v>0.9322282915558461</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>-48.4</v>
+      </c>
+      <c r="AN23">
+        <v>174.6942148760331</v>
+      </c>
+      <c r="AP23">
+        <v>170.3512097429075</v>
+      </c>
+      <c r="AQ23">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Houlihan Lokey, Inc. (NYSE:HLI)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>0.138</v>
+      </c>
+      <c r="E24">
+        <v>0.151</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>-0.02123483176883227</v>
+      </c>
+      <c r="J24">
+        <v>-0.01555174713862793</v>
+      </c>
+      <c r="K24">
+        <v>334.4</v>
+      </c>
+      <c r="L24">
+        <v>0.1577432897778197</v>
+      </c>
+      <c r="M24">
+        <v>263.3</v>
+      </c>
+      <c r="N24">
+        <v>0.02181550035627288</v>
+      </c>
+      <c r="O24">
+        <v>0.7873803827751196</v>
+      </c>
+      <c r="P24">
+        <v>160.7</v>
+      </c>
+      <c r="Q24">
+        <v>0.0133146635292558</v>
+      </c>
+      <c r="R24">
+        <v>0.4805622009569378</v>
+      </c>
+      <c r="S24">
+        <v>102.6</v>
+      </c>
+      <c r="T24">
+        <v>0.389669578427649</v>
+      </c>
+      <c r="U24">
+        <v>691.4</v>
+      </c>
+      <c r="V24">
+        <v>0.05728536629824183</v>
+      </c>
+      <c r="W24">
+        <v>0.2031468319057165</v>
+      </c>
+      <c r="X24">
+        <v>0.0630318861814565</v>
+      </c>
+      <c r="Y24">
+        <v>0.14011494572426</v>
+      </c>
+      <c r="Z24">
+        <v>4.262145582539555</v>
+      </c>
+      <c r="AA24">
+        <v>-0.06628381036767519</v>
+      </c>
+      <c r="AB24">
+        <v>0.06216254091476328</v>
+      </c>
+      <c r="AC24">
+        <v>-0.1284463512824385</v>
+      </c>
+      <c r="AD24">
+        <v>18.5</v>
+      </c>
+      <c r="AE24">
+        <v>431.5785993337377</v>
+      </c>
+      <c r="AF24">
+        <v>450.0785993337377</v>
+      </c>
+      <c r="AG24">
+        <v>-241.3214006662623</v>
+      </c>
+      <c r="AH24">
+        <v>0.03595026707882946</v>
+      </c>
+      <c r="AI24">
+        <v>0.186973496465244</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.020402417741784</v>
+      </c>
+      <c r="AK24">
+        <v>-0.140648333508747</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0.4479418886198547</v>
+      </c>
+      <c r="AP24">
+        <v>-5.843133188045093</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PJT Partners Inc. (NYSE:PJT)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>0.158</v>
+      </c>
+      <c r="E25">
+        <v>0.398</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>-0.03905989878372641</v>
+      </c>
+      <c r="J25">
+        <v>-0.03435989273135458</v>
+      </c>
+      <c r="K25">
+        <v>108</v>
+      </c>
+      <c r="L25">
+        <v>0.08024370309829854</v>
+      </c>
+      <c r="M25">
+        <v>253.3</v>
+      </c>
+      <c r="N25">
+        <v>0.06772002994332156</v>
+      </c>
+      <c r="O25">
+        <v>2.34537037037037</v>
+      </c>
+      <c r="P25">
+        <v>24.2</v>
+      </c>
+      <c r="Q25">
+        <v>0.006469896267778847</v>
+      </c>
+      <c r="R25">
+        <v>0.2240740740740741</v>
+      </c>
+      <c r="S25">
+        <v>229.1</v>
+      </c>
+      <c r="T25">
+        <v>0.9044611133043822</v>
+      </c>
+      <c r="U25">
+        <v>148.8</v>
+      </c>
+      <c r="V25">
+        <v>0.03978184151427655</v>
+      </c>
+      <c r="W25">
+        <v>0.5598755832037325</v>
+      </c>
+      <c r="X25">
+        <v>0.06393561878620263</v>
+      </c>
+      <c r="Y25">
+        <v>0.4959399644175299</v>
+      </c>
+      <c r="Z25">
+        <v>4.306141564034176</v>
+      </c>
+      <c r="AA25">
+        <v>-0.1479585622262418</v>
+      </c>
+      <c r="AB25">
+        <v>0.0617248646179886</v>
+      </c>
+      <c r="AC25">
+        <v>-0.2096834268442304</v>
+      </c>
+      <c r="AD25">
+        <v>0</v>
+      </c>
+      <c r="AE25">
+        <v>408.3535888650869</v>
+      </c>
+      <c r="AF25">
+        <v>408.3535888650869</v>
+      </c>
+      <c r="AG25">
+        <v>259.5535888650869</v>
+      </c>
+      <c r="AH25">
+        <v>0.09842801702204591</v>
+      </c>
+      <c r="AI25">
+        <v>0.3168347377801592</v>
+      </c>
+      <c r="AJ25">
+        <v>0.06488915011104676</v>
+      </c>
+      <c r="AK25">
+        <v>0.2276678845627512</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>0</v>
+      </c>
+      <c r="AP25">
+        <v>8.919367314951439</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Perella Weinberg Partners (NasdaqGS:PWP)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G26">
+        <v>0.0003469010175763182</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>-0.03852971622145975</v>
+      </c>
+      <c r="J26">
+        <v>-0.03852971622145975</v>
+      </c>
+      <c r="K26">
+        <v>-95.90000000000001</v>
+      </c>
+      <c r="L26">
+        <v>-0.1108926919518964</v>
+      </c>
+      <c r="M26">
+        <v>128.2</v>
+      </c>
+      <c r="N26">
+        <v>0.09134307089419308</v>
+      </c>
+      <c r="O26">
+        <v>-1.336809176225234</v>
+      </c>
+      <c r="P26">
+        <v>18.7</v>
+      </c>
+      <c r="Q26">
+        <v>0.01332383327395796</v>
+      </c>
+      <c r="R26">
+        <v>-0.1949947862356621</v>
+      </c>
+      <c r="S26">
+        <v>109.5</v>
+      </c>
+      <c r="T26">
+        <v>0.8541341653666147</v>
+      </c>
+      <c r="U26">
+        <v>260.2</v>
+      </c>
+      <c r="V26">
+        <v>0.1853936587103669</v>
+      </c>
+      <c r="W26">
+        <v>-0.6645876645876646</v>
+      </c>
+      <c r="X26">
+        <v>0.06418354507123193</v>
+      </c>
+      <c r="Y26">
+        <v>-0.7287712096588965</v>
+      </c>
+      <c r="Z26">
+        <v>5.266667908066509</v>
+      </c>
+      <c r="AA26">
+        <v>-0.2029232199304717</v>
+      </c>
+      <c r="AB26">
+        <v>0.06159074909119317</v>
+      </c>
+      <c r="AC26">
+        <v>-0.2645139690216649</v>
+      </c>
+      <c r="AD26">
+        <v>0</v>
+      </c>
+      <c r="AE26">
+        <v>180.902492941592</v>
+      </c>
+      <c r="AF26">
+        <v>180.902492941592</v>
+      </c>
+      <c r="AG26">
+        <v>-79.29750705840803</v>
+      </c>
+      <c r="AH26">
+        <v>0.1141771069835478</v>
+      </c>
+      <c r="AI26">
+        <v>0.4280677373254269</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.05988321837565495</v>
+      </c>
+      <c r="AK26">
+        <v>-0.4882776466179455</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>0</v>
+      </c>
+      <c r="AP26">
+        <v>-27.72640106937344</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dominari Holdings Inc. (NasdaqCM:DOMH)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>2.393</v>
+      </c>
+      <c r="G27">
+        <v>-1.698888888888889</v>
+      </c>
+      <c r="H27">
+        <v>-1.698412698412698</v>
+      </c>
+      <c r="I27">
+        <v>-1.135693247675219</v>
+      </c>
+      <c r="J27">
+        <v>-1.135693247675219</v>
+      </c>
+      <c r="K27">
+        <v>-22.7</v>
+      </c>
+      <c r="L27">
+        <v>-1.801587301587302</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>3.4</v>
+      </c>
+      <c r="V27">
+        <v>0.5501618122977346</v>
+      </c>
+      <c r="W27">
+        <v>-0.3893653516295026</v>
+      </c>
+      <c r="X27">
+        <v>0.07026037751929839</v>
+      </c>
+      <c r="Y27">
+        <v>-0.459625729148801</v>
+      </c>
+      <c r="Z27">
+        <v>0.2183948255434427</v>
+      </c>
+      <c r="AA27">
+        <v>-0.2480295286968953</v>
+      </c>
+      <c r="AB27">
+        <v>0.0600412449158263</v>
+      </c>
+      <c r="AC27">
+        <v>-0.3080707736127216</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>3.783674603538765</v>
+      </c>
+      <c r="AF27">
+        <v>3.783674603538765</v>
+      </c>
+      <c r="AG27">
+        <v>0.3836746035387653</v>
+      </c>
+      <c r="AH27">
+        <v>0.3797469060455798</v>
+      </c>
+      <c r="AI27">
+        <v>0.08990837038789862</v>
+      </c>
+      <c r="AJ27">
+        <v>0.05845423893072174</v>
+      </c>
+      <c r="AK27">
+        <v>0.00991825640844541</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AN27">
+        <v>-0</v>
+      </c>
+      <c r="AP27">
+        <v>-0.02851963157204826</v>
+      </c>
+      <c r="AQ27">
+        <v>15.21276595744681</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Nordicus Partners Corporation (OTCPK:NORD)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Brokerage &amp; Investment Banking</t>
+        </is>
+      </c>
+      <c r="G28">
+        <v>68.60000000000001</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>-185</v>
+      </c>
+      <c r="J28">
+        <v>-185</v>
+      </c>
+      <c r="K28">
+        <v>-0.918</v>
+      </c>
+      <c r="L28">
+        <v>-183.6</v>
+      </c>
+      <c r="M28">
+        <v>0.001</v>
+      </c>
+      <c r="N28">
+        <v>6.464124111182935E-06</v>
+      </c>
+      <c r="O28">
+        <v>-0.001089324618736383</v>
+      </c>
+      <c r="P28">
+        <v>0.001</v>
+      </c>
+      <c r="Q28">
+        <v>6.464124111182935E-06</v>
+      </c>
+      <c r="R28">
+        <v>-0.001089324618736383</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>0</v>
+      </c>
+      <c r="U28">
+        <v>0.046</v>
+      </c>
+      <c r="V28">
+        <v>0.000297349709114415</v>
+      </c>
+      <c r="W28">
+        <v>-0.5275862068965518</v>
+      </c>
+      <c r="X28">
+        <v>0.06256305434111617</v>
+      </c>
+      <c r="Y28">
+        <v>-0.590149261237668</v>
+      </c>
+      <c r="Z28">
+        <v>0.002865329512893983</v>
+      </c>
+      <c r="AA28">
+        <v>-0.5300859598853868</v>
+      </c>
+      <c r="AB28">
+        <v>0.06256305434111617</v>
+      </c>
+      <c r="AC28">
+        <v>-0.592649014226503</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>-0.046</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.0002974381522624698</v>
+      </c>
+      <c r="AK28">
+        <v>-0.002238007200544906</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
